--- a/Canada Life Annual Report Project.xlsx
+++ b/Canada Life Annual Report Project.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GMU058\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C4656C-D954-478A-B0D9-39DF046CB52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE6E9B8-EC0E-4F3C-B717-DEE847C5FF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{3CB541B1-AEC2-4997-AFCF-80587D906177}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{3CB541B1-AEC2-4997-AFCF-80587D906177}"/>
   </bookViews>
   <sheets>
-    <sheet name="2025 (Original)" sheetId="1" r:id="rId1"/>
-    <sheet name="2024 (Original)" sheetId="2" r:id="rId2"/>
-    <sheet name="2023 (Original)" sheetId="13" r:id="rId3"/>
-    <sheet name="2022 (Original)" sheetId="15" r:id="rId4"/>
+    <sheet name="CL 2025 (Original)" sheetId="1" r:id="rId1"/>
+    <sheet name="CL 2024 (Original)" sheetId="2" r:id="rId2"/>
+    <sheet name="CL 2023 (Original)" sheetId="13" r:id="rId3"/>
+    <sheet name="CL 2022 (Original)" sheetId="15" r:id="rId4"/>
+    <sheet name="CL Consolidated Summary" sheetId="16" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_2" localSheetId="0" hidden="1">'2025 (Original)'!$A$21:$C$51</definedName>
-    <definedName name="ExternalData_3" localSheetId="0" hidden="1">'2025 (Original)'!$A$55:$C$103</definedName>
-    <definedName name="ExternalData_4" localSheetId="0" hidden="1">'2025 (Original)'!$A$106:$I$114</definedName>
-    <definedName name="ExternalData_5" localSheetId="0" hidden="1">'2025 (Original)'!$A$118:$C$146</definedName>
+    <definedName name="ExternalData_2" localSheetId="0" hidden="1">'CL 2025 (Original)'!$A$21:$C$51</definedName>
+    <definedName name="ExternalData_3" localSheetId="0" hidden="1">'CL 2025 (Original)'!$A$55:$C$103</definedName>
+    <definedName name="ExternalData_4" localSheetId="0" hidden="1">'CL 2025 (Original)'!$A$106:$I$114</definedName>
+    <definedName name="ExternalData_5" localSheetId="0" hidden="1">'CL 2025 (Original)'!$A$118:$C$146</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,8 +48,54 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Han, Eugene</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{2F1AC64B-51DF-41DB-A3BA-D2F7A4C31212}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Canada Life adopted IFRS 17 beginning in 2023, which introduced the “Insurance revenue” line used in the newer annual reports. Therefore, 2022 Total net premiums is not directly comparable to 2023 to 2025 Insurance revenue because the accounting basis changed.
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="249">
   <si>
     <t>Summary of net earnings attributable to:</t>
   </si>
@@ -92,9 +139,6 @@
     <t>Total equity</t>
   </si>
   <si>
-    <t>Insurance revenue (note 12)</t>
-  </si>
-  <si>
     <t>Insurance service expenses (note 13)</t>
   </si>
   <si>
@@ -786,6 +830,18 @@
   </si>
   <si>
     <t>Total shareholders’ equity</t>
+  </si>
+  <si>
+    <t>Annual Report Item</t>
+  </si>
+  <si>
+    <t>Insurance revenue</t>
+  </si>
+  <si>
+    <t>Insurance service expenses, COGS equivalent</t>
+  </si>
+  <si>
+    <t>Insurance service result (gross profit equivalent)</t>
   </si>
 </sst>
 </file>
@@ -795,7 +851,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -810,6 +866,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -872,7 +934,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -908,72 +970,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="71">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1046,6 +1047,65 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1104,7 +1164,10 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1148,12 +1211,6 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -1175,13 +1232,17 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32C6B56A-ED7A-4BC5-86FB-BC86DC51FC56}" name="Table006__Page_7" displayName="Table006__Page_7" ref="A2:C17" totalsRowShown="0">
   <autoFilter ref="A2:C17" xr:uid="{32C6B56A-ED7A-4BC5-86FB-BC86DC51FC56}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{5C2C5EAF-8FD7-4548-B79E-158A94C36CEC}" name="Financial Highlights (Unaudited) (in Canadian $ Million)" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{F845F529-FD47-4771-A575-3ECAFBD90817}" name="2025" dataDxfId="52"/>
-    <tableColumn id="6" xr3:uid="{2D1DF53C-C68C-4325-9449-0D2B4F3F7A6D}" name="2024" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{5C2C5EAF-8FD7-4548-B79E-158A94C36CEC}" name="Financial Highlights (Unaudited) (in Canadian $ Million)" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{F845F529-FD47-4771-A575-3ECAFBD90817}" name="2025" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{2D1DF53C-C68C-4325-9449-0D2B4F3F7A6D}" name="2024" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1191,8 +1252,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{872B3C60-F251-4571-AC34-BA109A0E39B4}" name="Table017__Page_14" displayName="Table017__Page_14" ref="A118:C147" totalsRowShown="0">
   <autoFilter ref="A118:C147" xr:uid="{872B3C60-F251-4571-AC34-BA109A0E39B4}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{03DD1A9C-855C-4E1B-BC85-F1DA52E562A1}" name="Consolidated Statements of Cash Flow  (in Canadian $ millions)" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{9F529541-D5F9-4E8A-9852-77076A9252D7}" name="2024" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{03DD1A9C-855C-4E1B-BC85-F1DA52E562A1}" name="Consolidated Statements of Cash Flow  (in Canadian $ millions)" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{9F529541-D5F9-4E8A-9852-77076A9252D7}" name="2024" dataDxfId="20"/>
     <tableColumn id="5" xr3:uid="{D60C0FDC-FC22-4E62-9467-CDCB0E581960}" name="2023"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1203,9 +1264,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{AECA25C1-C846-4A7B-A2BF-C9448B60FB0D}" name="Table005__Page_8_1" displayName="Table005__Page_8_1" ref="A2:C20" totalsRowShown="0">
   <autoFilter ref="A2:C20" xr:uid="{AECA25C1-C846-4A7B-A2BF-C9448B60FB0D}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2FBD130F-2F76-40A4-8A35-F73D197CF679}" name="Financial Highlights (unaudited) (in Canadian $ millions)" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{EB1CCD9F-222B-42FF-A665-B40808CDFA23}" name="2023" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{606BD4DE-1AB4-4377-AD4C-304EEE364AE0}" name="2022" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{2FBD130F-2F76-40A4-8A35-F73D197CF679}" name="Financial Highlights (unaudited) (in Canadian $ millions)" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{EB1CCD9F-222B-42FF-A665-B40808CDFA23}" name="2023" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{606BD4DE-1AB4-4377-AD4C-304EEE364AE0}" name="2022" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1215,9 +1276,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{403F03B7-0B2F-429E-9099-05D4B79628EE}" name="Table010__Page_10_1" displayName="Table010__Page_10_1" ref="A23:C54" totalsRowShown="0">
   <autoFilter ref="A23:C54" xr:uid="{403F03B7-0B2F-429E-9099-05D4B79628EE}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{348E9B7F-8015-4CEA-9CB7-F5A11E794924}" name="Consolidated Statements of Earnings (in Canadian $ millions)" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{9CB5D784-9668-43E2-912F-CCC0C5A46AFC}" name="2023" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{7DFA6E59-95B4-4F39-8D95-F85AC0C103B7}" name="2022" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{348E9B7F-8015-4CEA-9CB7-F5A11E794924}" name="Consolidated Statements of Earnings (in Canadian $ millions)" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{9CB5D784-9668-43E2-912F-CCC0C5A46AFC}" name="2023" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{7DFA6E59-95B4-4F39-8D95-F85AC0C103B7}" name="2022" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1227,10 +1288,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{C8294548-29F4-4247-8D91-46256870F255}" name="Table012__Page_12" displayName="Table012__Page_12" ref="A57:D105" totalsRowShown="0">
   <autoFilter ref="A57:D105" xr:uid="{C8294548-29F4-4247-8D91-46256870F255}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A77F868F-A01A-4E28-831C-123758FFEE1B}" name="Consolidated Balance Sheets (in Canadian $ millions)" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{BF1169F7-EA41-4E34-B1BE-468D058EC001}" name="2023" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{0DED70B6-5DBC-4722-9AEA-0F35DB477359}" name="2022" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{391AF299-CDE1-44A4-94F3-25223ECFCF43}" name="2021" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{A77F868F-A01A-4E28-831C-123758FFEE1B}" name="Consolidated Balance Sheets (in Canadian $ millions)" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{BF1169F7-EA41-4E34-B1BE-468D058EC001}" name="2023" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{0DED70B6-5DBC-4722-9AEA-0F35DB477359}" name="2022" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{391AF299-CDE1-44A4-94F3-25223ECFCF43}" name="2021" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1240,15 +1301,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{010BDDA1-0210-42C8-BA1E-98C8F4E39148}" name="Table014__Page_13" displayName="Table014__Page_13" ref="A108:I119" totalsRowShown="0">
   <autoFilter ref="A108:I119" xr:uid="{010BDDA1-0210-42C8-BA1E-98C8F4E39148}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{12AD67BC-57B1-41C3-A7A2-ECD190ADFB8A}" name="Consolidated Statements of Changes in Equity (in Canadian $ millions)" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{D69CD2BD-7405-43A8-B2F6-D33B29AE7319}" name="Share capital" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{D7419A9F-70E7-4602-A940-77D76211462A}" name="Contributed surplus" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{6F1EC460-0E36-4BAA-BD61-804EA1A7B604}" name="Accumulated surplus" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{ECC52595-0035-4144-8E9B-C830D055A87F}" name="Accumulated other comprehensive income (loss)" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{DD90BFCF-0719-4732-B663-A0F6DDCBB014}" name="Total shareholders' equity" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{45A80F18-CA21-485E-9774-7188CBDBD23A}" name="Non-controlling interests" dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{5EFFD87C-8A6F-4E32-BC35-2981FB121A78}" name="Participating account surplus" dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{E2F54086-E050-49D8-8244-5234819E6F63}" name="Total equity" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{12AD67BC-57B1-41C3-A7A2-ECD190ADFB8A}" name="Consolidated Statements of Changes in Equity (in Canadian $ millions)" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{D69CD2BD-7405-43A8-B2F6-D33B29AE7319}" name="Share capital" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{D7419A9F-70E7-4602-A940-77D76211462A}" name="Contributed surplus" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{6F1EC460-0E36-4BAA-BD61-804EA1A7B604}" name="Accumulated surplus" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{ECC52595-0035-4144-8E9B-C830D055A87F}" name="Accumulated other comprehensive income (loss)" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{DD90BFCF-0719-4732-B663-A0F6DDCBB014}" name="Total shareholders' equity" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{45A80F18-CA21-485E-9774-7188CBDBD23A}" name="Non-controlling interests" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{5EFFD87C-8A6F-4E32-BC35-2981FB121A78}" name="Participating account surplus" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{E2F54086-E050-49D8-8244-5234819E6F63}" name="Total equity" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1258,7 +1319,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{070ABDE2-BBC3-4908-AB0F-44D6EF66AED5}" name="Table016__Page_14" displayName="Table016__Page_14" ref="A122:C152" totalsRowShown="0">
   <autoFilter ref="A122:C152" xr:uid="{070ABDE2-BBC3-4908-AB0F-44D6EF66AED5}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7B75C2BC-A013-41C7-861B-9EDA9E0AE1BA}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{7B75C2BC-A013-41C7-861B-9EDA9E0AE1BA}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{D08EF108-C608-416D-A0FA-78700D08B198}" name="2023"/>
     <tableColumn id="7" xr3:uid="{0A748248-90C6-42D4-A30D-90D2E6522606}" name="2022"/>
   </tableColumns>
@@ -1270,7 +1331,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{DA35DAB2-1EB1-4099-B43A-7BBB210BD1B2}" name="Table005__Page_6" displayName="Table005__Page_6" ref="A2:C26" totalsRowShown="0">
   <autoFilter ref="A2:C26" xr:uid="{DA35DAB2-1EB1-4099-B43A-7BBB210BD1B2}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{742648AB-0CC3-4711-89DE-BEA31617073E}" name="Financial Highlight (unaudited)  (in Canadian $ millions)" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{742648AB-0CC3-4711-89DE-BEA31617073E}" name="Financial Highlight (unaudited)  (in Canadian $ millions)" dataDxfId="70"/>
     <tableColumn id="4" xr3:uid="{8EFD586F-8504-433C-ACA7-A80E443245D8}" name="2022"/>
     <tableColumn id="6" xr3:uid="{F3762B59-FF64-4412-994B-4F79CC8C4273}" name="2021"/>
   </tableColumns>
@@ -1282,8 +1343,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{D352CFDF-76E1-4D3C-8C7B-7F57348B216F}" name="Table009__Page_8" displayName="Table009__Page_8" ref="A29:C63" totalsRowShown="0">
   <autoFilter ref="A29:C63" xr:uid="{D352CFDF-76E1-4D3C-8C7B-7F57348B216F}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E02CB553-D5D4-402A-8C54-8DE755972EFF}" name="Consolidated Statements of Earnings  (in Canadian $ millions)" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{63FC9382-AFA6-415E-82F8-8CF40DE991D2}" name="2022" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{E02CB553-D5D4-402A-8C54-8DE755972EFF}" name="Consolidated Statements of Earnings  (in Canadian $ millions)" dataDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{63FC9382-AFA6-415E-82F8-8CF40DE991D2}" name="2022" dataDxfId="68"/>
     <tableColumn id="6" xr3:uid="{75F17EC1-69D4-4F5D-8315-089CA34D666C}" name="2021"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1294,7 +1355,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{BB04493A-D9FF-4D74-A5D0-111BD2A4656C}" name="Table011__Page_10" displayName="Table011__Page_10" ref="A66:C112" totalsRowShown="0">
   <autoFilter ref="A66:C112" xr:uid="{BB04493A-D9FF-4D74-A5D0-111BD2A4656C}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{893DB4C7-64EE-4ADA-8217-9192AD5B689E}" name="Consolidated Balance Sheets" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{893DB4C7-64EE-4ADA-8217-9192AD5B689E}" name="Consolidated Balance Sheets" dataDxfId="67"/>
     <tableColumn id="4" xr3:uid="{DFF048A5-755F-448B-87C0-4E919F682AF0}" name="2022"/>
     <tableColumn id="6" xr3:uid="{5DD01DB6-24AF-4D26-80A0-169FFD04A979}" name="2021"/>
   </tableColumns>
@@ -1306,15 +1367,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{215DB435-83EB-4E91-B08B-67EC402A3AFF}" name="Table013__Page_11_1" displayName="Table013__Page_11_1" ref="A115:I124" totalsRowShown="0">
   <autoFilter ref="A115:I124" xr:uid="{215DB435-83EB-4E91-B08B-67EC402A3AFF}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{09504AB0-770E-4D43-ACD1-DE5F040CED87}" name="Consolidated Statements of Changes in Equity" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{BFA1FFA7-6E3B-4F23-85D7-277A408FB401}" name="Share capital" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{701F6E9A-D8E6-4794-950B-B6C0DCDFFB6C}" name="Contributed surplus" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{C6BCA9CA-AA5E-4ECD-A8ED-3425059521DC}" name="Accumulated surplus" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{C387DAE6-44DC-4C88-B247-97FF4BBC177F}" name="Accumulated other comprehensive loss comprehensive loss" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{3D9F6865-2163-45E5-9E9F-FE1EFA6E0A4E}" name="Total shareholders’ equity" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{A62F3586-FEAD-4757-955C-167BA489C2DA}" name="Non-controlling interests" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{5EC6C0BE-4B74-4A04-B001-36C6B2FE1058}" name="Participating account surplus" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{63AE17E1-9D3F-402A-8E50-6A25D991559F}" name="Total equity" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{09504AB0-770E-4D43-ACD1-DE5F040CED87}" name="Consolidated Statements of Changes in Equity" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{BFA1FFA7-6E3B-4F23-85D7-277A408FB401}" name="Share capital" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{701F6E9A-D8E6-4794-950B-B6C0DCDFFB6C}" name="Contributed surplus" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{C6BCA9CA-AA5E-4ECD-A8ED-3425059521DC}" name="Accumulated surplus" dataDxfId="63"/>
+    <tableColumn id="9" xr3:uid="{C387DAE6-44DC-4C88-B247-97FF4BBC177F}" name="Accumulated other comprehensive loss comprehensive loss" dataDxfId="62"/>
+    <tableColumn id="11" xr3:uid="{3D9F6865-2163-45E5-9E9F-FE1EFA6E0A4E}" name="Total shareholders’ equity" dataDxfId="61"/>
+    <tableColumn id="13" xr3:uid="{A62F3586-FEAD-4757-955C-167BA489C2DA}" name="Non-controlling interests" dataDxfId="60"/>
+    <tableColumn id="15" xr3:uid="{5EC6C0BE-4B74-4A04-B001-36C6B2FE1058}" name="Participating account surplus" dataDxfId="59"/>
+    <tableColumn id="17" xr3:uid="{63AE17E1-9D3F-402A-8E50-6A25D991559F}" name="Total equity" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1324,9 +1385,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{34C03A14-B5FE-4A4C-A2DD-6F7C99CBB8B6}" name="Table010__Page_9" displayName="Table010__Page_9" ref="A21:C51" totalsRowShown="0">
   <autoFilter ref="A21:C51" xr:uid="{34C03A14-B5FE-4A4C-A2DD-6F7C99CBB8B6}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{AF140A9C-2544-462A-8D05-83FCA92FCC29}" name="Consolidated Statements Of Earnings (in Canadian $ Million)" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{16B7134F-532D-42E5-B2C1-83A349FA9ED6}" name="2025" dataDxfId="49"/>
-    <tableColumn id="5" xr3:uid="{A04CC424-6000-4365-8CE5-358C2FA21877}" name="2024" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{AF140A9C-2544-462A-8D05-83FCA92FCC29}" name="Consolidated Statements Of Earnings (in Canadian $ Million)" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{16B7134F-532D-42E5-B2C1-83A349FA9ED6}" name="2025" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{A04CC424-6000-4365-8CE5-358C2FA21877}" name="2024" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1336,9 +1397,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{395EA000-7795-40F0-80C9-309E26D34DB3}" name="Table015__Page_12_1" displayName="Table015__Page_12_1" ref="A127:C161" totalsRowShown="0">
   <autoFilter ref="A127:C161" xr:uid="{395EA000-7795-40F0-80C9-309E26D34DB3}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D9D5A221-D279-446F-84E7-045892C71C4C}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{0B41E5F3-DDED-491F-B3FE-F07FAA1FC2F1}" name="2022" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{597E5080-187F-4732-87DD-297275C991F1}" name="2021" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D9D5A221-D279-446F-84E7-045892C71C4C}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="57"/>
+    <tableColumn id="4" xr3:uid="{0B41E5F3-DDED-491F-B3FE-F07FAA1FC2F1}" name="2022" dataDxfId="56"/>
+    <tableColumn id="6" xr3:uid="{597E5080-187F-4732-87DD-297275C991F1}" name="2021" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1348,8 +1409,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FABD7B52-E650-435A-863F-F68E89A607E8}" name="Table013__Page_11" displayName="Table013__Page_11" ref="A55:C103" totalsRowShown="0">
   <autoFilter ref="A55:C103" xr:uid="{FABD7B52-E650-435A-863F-F68E89A607E8}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D6729C5B-6996-4AD6-921A-4FCB66DC5B45}" name="Consolidated Balance Sheet  (in Canadian $ Million)" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{1B220B5B-DEB0-4054-AD07-3C5B3F8AACD1}" name="2025" dataDxfId="46"/>
+    <tableColumn id="1" xr3:uid="{D6729C5B-6996-4AD6-921A-4FCB66DC5B45}" name="Consolidated Balance Sheet  (in Canadian $ Million)" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{1B220B5B-DEB0-4054-AD07-3C5B3F8AACD1}" name="2025" dataDxfId="47"/>
     <tableColumn id="5" xr3:uid="{E50E6906-CAA9-42F6-9EB9-A1F697BB2F20}" name="2024"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1360,15 +1421,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CF654234-2B8F-4830-BE0E-554991835BD9}" name="Table015__Page_12" displayName="Table015__Page_12" ref="A106:I114" totalsRowShown="0">
   <autoFilter ref="A106:I114" xr:uid="{CF654234-2B8F-4830-BE0E-554991835BD9}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C372BC7B-EDAA-425F-B029-CC348E8759F1}" name="Consolidated Statements of Change in Equity" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{87A431C1-44DD-4CAE-8CF0-67ED9C3536FA}" name="Share Capital" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{1ACAEC2D-550E-4F1E-899C-D23FDA3C7A2F}" name="Contributed Surplus" dataDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{DA9BD253-8ABA-4C4C-90D8-B886FCF7BB0C}" name="Accumulated Surplus" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{35415082-274B-4DFF-B6E0-53920A2A9F6D}" name="Accumulated Other Comprehensive Income" dataDxfId="41"/>
-    <tableColumn id="10" xr3:uid="{2F102C70-C964-49EB-A16F-A1842CC2B96F}" name="Total Shareholder's Equity" dataDxfId="40"/>
-    <tableColumn id="12" xr3:uid="{ECFC45BF-2FD7-4257-A71D-CD62160491EA}" name="Non-controlling Interest" dataDxfId="39"/>
-    <tableColumn id="14" xr3:uid="{E959836E-9965-4D14-BCC3-3BCC273F49C9}" name="Participating Account Surplus" dataDxfId="38"/>
-    <tableColumn id="16" xr3:uid="{C57C220A-153E-480B-8F20-BD9766EBCC5D}" name="Total Equity" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{C372BC7B-EDAA-425F-B029-CC348E8759F1}" name="Consolidated Statements of Change in Equity" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{87A431C1-44DD-4CAE-8CF0-67ED9C3536FA}" name="Share Capital" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{1ACAEC2D-550E-4F1E-899C-D23FDA3C7A2F}" name="Contributed Surplus" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{DA9BD253-8ABA-4C4C-90D8-B886FCF7BB0C}" name="Accumulated Surplus" dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{35415082-274B-4DFF-B6E0-53920A2A9F6D}" name="Accumulated Other Comprehensive Income" dataDxfId="42"/>
+    <tableColumn id="10" xr3:uid="{2F102C70-C964-49EB-A16F-A1842CC2B96F}" name="Total Shareholder's Equity" dataDxfId="41"/>
+    <tableColumn id="12" xr3:uid="{ECFC45BF-2FD7-4257-A71D-CD62160491EA}" name="Non-controlling Interest" dataDxfId="40"/>
+    <tableColumn id="14" xr3:uid="{E959836E-9965-4D14-BCC3-3BCC273F49C9}" name="Participating Account Surplus" dataDxfId="39"/>
+    <tableColumn id="16" xr3:uid="{C57C220A-153E-480B-8F20-BD9766EBCC5D}" name="Total Equity" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1378,7 +1439,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3AAC487E-DBF0-4C56-AF4F-056F3601ED72}" name="Table017__Page_13" displayName="Table017__Page_13" ref="A118:C146" totalsRowShown="0">
   <autoFilter ref="A118:C146" xr:uid="{3AAC487E-DBF0-4C56-AF4F-056F3601ED72}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2F45C01F-02D6-4CB5-9364-F722A27B3859}" name="Consolidated Statements of Cash Flow" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{2F45C01F-02D6-4CB5-9364-F722A27B3859}" name="Consolidated Statements of Cash Flow" dataDxfId="37"/>
     <tableColumn id="3" xr3:uid="{712741C7-204F-4298-8050-873B208D5060}" name="2025"/>
     <tableColumn id="5" xr3:uid="{2534FEF1-3F52-460C-AB74-977F2325376E}" name="2024"/>
   </tableColumns>
@@ -1390,8 +1451,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{80062148-2C94-44FA-AA84-D3AF2950CAE1}" name="Table005__Page_8" displayName="Table005__Page_8" ref="A2:C21" totalsRowShown="0">
   <autoFilter ref="A2:C21" xr:uid="{80062148-2C94-44FA-AA84-D3AF2950CAE1}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A504AF7D-4077-4F75-AD8E-F00D66A4E1EB}" name="Financial Highlights (in Canadian $ millions)" dataDxfId="70"/>
-    <tableColumn id="5" xr3:uid="{6DE21333-8B6D-493E-A3FB-12219341B858}" name="2024" dataDxfId="69"/>
+    <tableColumn id="1" xr3:uid="{A504AF7D-4077-4F75-AD8E-F00D66A4E1EB}" name="Financial Highlights (in Canadian $ millions)" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{6DE21333-8B6D-493E-A3FB-12219341B858}" name="2024" dataDxfId="35"/>
     <tableColumn id="7" xr3:uid="{1D1F864D-619C-4D8B-BDCB-F9F994AD3F85}" name="2023"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1402,9 +1463,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F2E5B2C2-C7D4-4C68-B8DF-B451C6AD2FA5}" name="Table010__Page_10" displayName="Table010__Page_10" ref="A24:C54" totalsRowShown="0">
   <autoFilter ref="A24:C54" xr:uid="{F2E5B2C2-C7D4-4C68-B8DF-B451C6AD2FA5}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B00DF7C4-46F0-426A-99DA-8CD1485C8167}" name="Consolidated Satatements of Earnings (in Canadian $ millions)" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{6DBC8D88-3782-41F5-8C7F-4912F53C3845}" name="2024" dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{0DA8B320-B9A4-43AB-B84E-C184D12EEBCE}" name="2023" dataDxfId="66"/>
+    <tableColumn id="1" xr3:uid="{B00DF7C4-46F0-426A-99DA-8CD1485C8167}" name="Consolidated Satatements of Earnings (in Canadian $ millions)" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{6DBC8D88-3782-41F5-8C7F-4912F53C3845}" name="2024" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{0DA8B320-B9A4-43AB-B84E-C184D12EEBCE}" name="2023" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1414,7 +1475,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{09288B11-3956-44BF-B015-CDD67BF6122B}" name="Table013__Page_12" displayName="Table013__Page_12" ref="A57:C104" totalsRowShown="0">
   <autoFilter ref="A57:C104" xr:uid="{09288B11-3956-44BF-B015-CDD67BF6122B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{9A2A315A-17C4-44C5-839B-27077EDAFBE8}" name="Consolidated Balance Sheet  (in Canadian $ millions)" dataDxfId="65"/>
+    <tableColumn id="1" xr3:uid="{9A2A315A-17C4-44C5-839B-27077EDAFBE8}" name="Consolidated Balance Sheet  (in Canadian $ millions)" dataDxfId="31"/>
     <tableColumn id="3" xr3:uid="{AC35110F-0BC5-4C19-B333-64D500DD652D}" name="2024"/>
     <tableColumn id="5" xr3:uid="{FC18CAD8-EF52-4B84-B287-4440BF8988D1}" name="2023"/>
   </tableColumns>
@@ -1426,15 +1487,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{95B36E1D-5C8B-415A-8BB2-72AC852DFE1F}" name="Table015__Page_13" displayName="Table015__Page_13" ref="A107:I115" totalsRowShown="0">
   <autoFilter ref="A107:I115" xr:uid="{95B36E1D-5C8B-415A-8BB2-72AC852DFE1F}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{346EBBBA-D3E8-43C4-B112-84CFBA884811}" name="Consolidated Statements of Changes in Equity  (in Canadian $ millions)" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{A3F2222E-550B-4C91-822F-4D93B86D0518}" name="Share capital" dataDxfId="63"/>
-    <tableColumn id="4" xr3:uid="{5DE7CF1E-A17D-4E32-B7FB-FD3FCA7A27C6}" name="Contributed surplus" dataDxfId="62"/>
-    <tableColumn id="6" xr3:uid="{7CD3F9B9-2C9F-423A-9B10-5566ED617B23}" name="Accumulated surplus" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{81A55F20-6E2D-49CB-A777-7EA2FA186E54}" name="Accumulated other comprehensive income (loss)" dataDxfId="60"/>
-    <tableColumn id="10" xr3:uid="{436743AE-2B63-4A1B-B86F-48A200522D06}" name="Total shareholder's equity" dataDxfId="59"/>
-    <tableColumn id="12" xr3:uid="{185E9850-C6B0-4386-B196-713B0971812A}" name="Non-controlling interests" dataDxfId="58"/>
-    <tableColumn id="14" xr3:uid="{F07A79B8-D988-4A89-BC52-58700AEF495C}" name="Participating account surplus" dataDxfId="57"/>
-    <tableColumn id="16" xr3:uid="{DAC2842E-0699-4DFF-A5A2-CA0460B0936F}" name="Total equity" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{346EBBBA-D3E8-43C4-B112-84CFBA884811}" name="Consolidated Statements of Changes in Equity  (in Canadian $ millions)" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{A3F2222E-550B-4C91-822F-4D93B86D0518}" name="Share capital" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{5DE7CF1E-A17D-4E32-B7FB-FD3FCA7A27C6}" name="Contributed surplus" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{7CD3F9B9-2C9F-423A-9B10-5566ED617B23}" name="Accumulated surplus" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{81A55F20-6E2D-49CB-A777-7EA2FA186E54}" name="Accumulated other comprehensive income (loss)" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{436743AE-2B63-4A1B-B86F-48A200522D06}" name="Total shareholder's equity" dataDxfId="25"/>
+    <tableColumn id="12" xr3:uid="{185E9850-C6B0-4386-B196-713B0971812A}" name="Non-controlling interests" dataDxfId="24"/>
+    <tableColumn id="14" xr3:uid="{F07A79B8-D988-4A89-BC52-58700AEF495C}" name="Participating account surplus" dataDxfId="23"/>
+    <tableColumn id="16" xr3:uid="{DAC2842E-0699-4DFF-A5A2-CA0460B0936F}" name="Total equity" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1774,13 +1835,13 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" t="s">
         <v>187</v>
-      </c>
-      <c r="C2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1869,7 +1930,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B11" s="1">
         <v>529301</v>
@@ -1880,7 +1941,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B12" s="1">
         <v>723435</v>
@@ -1946,13 +2007,13 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -1964,7 +2025,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>246</v>
       </c>
       <c r="B23" s="1">
         <v>22131</v>
@@ -1975,7 +2036,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" s="1">
         <v>-17002</v>
@@ -1986,7 +2047,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" s="10">
         <v>-1679</v>
@@ -2005,14 +2066,14 @@
     </row>
     <row r="27" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" s="1">
         <v>5837</v>
@@ -2023,7 +2084,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="10">
         <v>1328</v>
@@ -2042,7 +2103,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B31" s="1">
         <v>-6116</v>
@@ -2053,7 +2114,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B32" s="1">
         <v>-303</v>
@@ -2064,7 +2125,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B33" s="10">
         <v>-143</v>
@@ -2083,14 +2144,14 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" s="1">
         <v>5044</v>
@@ -2101,7 +2162,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B37" s="1">
         <v>-5044</v>
@@ -2112,15 +2173,15 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B38" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2138,7 +2199,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B41" s="1">
         <v>-3408</v>
@@ -2149,7 +2210,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B42" s="1">
         <v>-194</v>
@@ -2160,7 +2221,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B43" s="1">
         <v>-107</v>
@@ -2171,7 +2232,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B44" s="1">
         <v>-346</v>
@@ -2182,7 +2243,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B45" s="1">
         <v>3014</v>
@@ -2193,7 +2254,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B46" s="1">
         <v>248</v>
@@ -2204,7 +2265,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B47" s="1">
         <v>2766</v>
@@ -2215,10 +2276,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C48" s="1">
         <v>-3</v>
@@ -2237,7 +2298,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B50" s="1">
         <v>42</v>
@@ -2248,7 +2309,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B51" s="1">
         <v>2724</v>
@@ -2259,23 +2320,23 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B55" t="s">
+        <v>186</v>
+      </c>
+      <c r="C55" t="s">
         <v>187</v>
-      </c>
-      <c r="C55" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B57" s="1">
         <v>4679</v>
@@ -2286,7 +2347,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B58" s="1">
         <v>104567</v>
@@ -2297,7 +2358,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B59" s="1">
         <v>26009</v>
@@ -2308,7 +2369,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B60" s="1">
         <v>16990</v>
@@ -2319,7 +2380,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B61" s="10">
         <v>8277</v>
@@ -2341,7 +2402,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B64" s="1">
         <v>1256</v>
@@ -2352,7 +2413,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B65" s="1">
         <v>6399</v>
@@ -2363,7 +2424,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B66" s="1">
         <v>6905</v>
@@ -2374,7 +2435,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B67" s="1">
         <v>2983</v>
@@ -2385,7 +2446,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B68" s="1">
         <v>1290</v>
@@ -2396,7 +2457,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B69" s="1">
         <v>641</v>
@@ -2407,7 +2468,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B70" s="1">
         <v>321</v>
@@ -2418,7 +2479,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B71" s="1">
         <v>3926</v>
@@ -2429,7 +2490,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B72" s="1">
         <v>2981</v>
@@ -2440,7 +2501,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B73" s="1">
         <v>315</v>
@@ -2451,7 +2512,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B74" s="1">
         <v>1156</v>
@@ -2462,7 +2523,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B75" s="10">
         <v>316957</v>
@@ -2488,14 +2549,14 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B79" s="1">
         <v>147329</v>
@@ -2506,7 +2567,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B80" s="1">
         <v>4422</v>
@@ -2517,7 +2578,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B81" s="1">
         <v>787</v>
@@ -2528,7 +2589,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B82" s="1">
         <v>827</v>
@@ -2539,7 +2600,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B83" s="1">
         <v>1000</v>
@@ -2550,7 +2611,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B84" s="1">
         <v>2130</v>
@@ -2561,7 +2622,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B85" s="1">
         <v>2236</v>
@@ -2572,7 +2633,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B86" s="1">
         <v>5006</v>
@@ -2583,7 +2644,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B87" s="1">
         <v>400</v>
@@ -2594,7 +2655,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B88" s="1">
         <v>538</v>
@@ -2605,7 +2666,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B89" s="1">
         <v>56153</v>
@@ -2616,7 +2677,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B90" s="10">
         <v>260804</v>
@@ -2627,7 +2688,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B91" s="1">
         <v>481632</v>
@@ -2642,14 +2703,14 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B94" s="1">
         <v>3082</v>
@@ -2660,10 +2721,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C95" s="1">
         <v>10</v>
@@ -2671,21 +2732,21 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B98" s="1">
         <v>7995</v>
@@ -2696,7 +2757,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B99" s="1">
         <v>11332</v>
@@ -2707,7 +2768,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B100" s="1">
         <v>1154</v>
@@ -2718,7 +2779,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B101" s="10">
         <v>457</v>
@@ -2740,7 +2801,7 @@
     </row>
     <row r="103" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B103" s="11">
         <v>505652</v>
@@ -2752,36 +2813,36 @@
     <row r="104" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B106" t="s">
+        <v>197</v>
+      </c>
+      <c r="C106" t="s">
         <v>198</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>199</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
         <v>200</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>201</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>202</v>
       </c>
-      <c r="G106" t="s">
+      <c r="H106" t="s">
         <v>203</v>
       </c>
-      <c r="H106" t="s">
+      <c r="I106" t="s">
         <v>204</v>
-      </c>
-      <c r="I106" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B107" s="3">
         <v>7995</v>
@@ -2810,25 +2871,25 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D108" s="3">
         <v>2724</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F108" s="3">
         <v>2724</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H108" s="4">
         <v>42</v>
@@ -2839,16 +2900,16 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E109" s="7">
         <v>443</v>
@@ -2857,7 +2918,7 @@
         <v>443</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H109" s="7">
         <v>-3</v>
@@ -2894,28 +2955,28 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D111" s="3">
         <v>-3150</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F111" s="3">
         <v>-3150</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I111" s="4">
         <v>-3150</v>
@@ -2923,28 +2984,28 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C112" s="4">
         <v>12</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F112" s="4">
         <v>12</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I112" s="4">
         <v>12</v>
@@ -2952,28 +3013,28 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G113" s="7">
         <v>-10</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I113" s="7">
         <v>-10</v>
@@ -2981,7 +3042,7 @@
     </row>
     <row r="114" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B114" s="8">
         <v>7995</v>
@@ -2999,7 +3060,7 @@
         <v>20938</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H114" s="8">
         <v>3082</v>
@@ -3011,23 +3072,23 @@
     <row r="115" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B118" t="s">
+        <v>186</v>
+      </c>
+      <c r="C118" t="s">
         <v>187</v>
-      </c>
-      <c r="C118" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B120">
         <v>3014</v>
@@ -3038,7 +3099,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B121">
         <v>-554</v>
@@ -3049,12 +3110,12 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B123">
         <v>5118</v>
@@ -3065,7 +3126,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B124">
         <v>-261</v>
@@ -3076,7 +3137,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B125">
         <v>147</v>
@@ -3087,7 +3148,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B126">
         <v>351</v>
@@ -3098,7 +3159,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B127">
         <v>-376</v>
@@ -3109,7 +3170,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B128">
         <v>-1328</v>
@@ -3120,7 +3181,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B129">
         <v>37806</v>
@@ -3131,7 +3192,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B130">
         <v>-40045</v>
@@ -3142,7 +3203,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B131" s="5">
         <v>-621</v>
@@ -3161,12 +3222,12 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B134">
         <v>-3150</v>
@@ -3177,12 +3238,12 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B137">
         <v>-22</v>
@@ -3193,7 +3254,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B139">
         <v>78</v>
@@ -3204,7 +3265,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B140">
         <v>157</v>
@@ -3215,7 +3276,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B141" s="5">
         <v>4522</v>
@@ -3226,7 +3287,7 @@
     </row>
     <row r="142" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B142" s="6">
         <v>4679</v>
@@ -3237,12 +3298,12 @@
     </row>
     <row r="143" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B144">
         <v>5172</v>
@@ -3253,7 +3314,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B145">
         <v>114</v>
@@ -3264,7 +3325,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B146">
         <v>447</v>
@@ -3304,13 +3365,13 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -3405,7 +3466,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B13" s="1">
         <v>576201</v>
@@ -3416,7 +3477,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B14" s="1">
         <v>654853</v>
@@ -3486,7 +3547,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B21" s="13">
         <v>1.3</v>
@@ -3497,13 +3558,13 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -3515,7 +3576,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>246</v>
       </c>
       <c r="B26" s="1">
         <v>21007</v>
@@ -3526,7 +3587,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" s="1">
         <v>-16165</v>
@@ -3537,7 +3598,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28" s="10">
         <v>-1584</v>
@@ -3556,14 +3617,14 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" s="1">
         <v>5719</v>
@@ -3574,7 +3635,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B32" s="10">
         <v>1280</v>
@@ -3593,7 +3654,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B34" s="1">
         <v>-5851</v>
@@ -3604,7 +3665,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B35" s="1">
         <v>26</v>
@@ -3615,7 +3676,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B36" s="10">
         <v>-159</v>
@@ -3634,14 +3695,14 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B39" s="1">
         <v>6828</v>
@@ -3652,7 +3713,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B40" s="10">
         <v>-6828</v>
@@ -3663,15 +3724,15 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -3689,7 +3750,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B44" s="1">
         <v>-3088</v>
@@ -3700,7 +3761,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B45" s="1">
         <v>-185</v>
@@ -3711,7 +3772,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B46" s="1">
         <v>-105</v>
@@ -3722,7 +3783,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B47" s="10">
         <v>-49</v>
@@ -3733,7 +3794,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B48" s="1">
         <v>3699</v>
@@ -3744,7 +3805,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B49" s="10">
         <v>455</v>
@@ -3755,7 +3816,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B50" s="1">
         <v>3244</v>
@@ -3766,7 +3827,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B51" s="10">
         <v>-3</v>
@@ -3788,7 +3849,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B53" s="10">
         <v>107</v>
@@ -3799,7 +3860,7 @@
     </row>
     <row r="54" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B54" s="11">
         <v>3140</v>
@@ -3811,23 +3872,23 @@
     <row r="55" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B57" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B59" s="1">
         <v>4522</v>
@@ -3838,7 +3899,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B60" s="1">
         <v>100863</v>
@@ -3849,7 +3910,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B61" s="1">
         <v>25477</v>
@@ -3860,7 +3921,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B62" s="1">
         <v>14794</v>
@@ -3871,7 +3932,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B63" s="10">
         <v>8235</v>
@@ -3890,7 +3951,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B65" s="1">
         <v>858</v>
@@ -3901,7 +3962,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B66" s="1">
         <v>6544</v>
@@ -3912,7 +3973,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B67" s="1">
         <v>6827</v>
@@ -3923,7 +3984,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B68" s="1">
         <v>2866</v>
@@ -3934,7 +3995,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B69" s="1">
         <v>1458</v>
@@ -3945,7 +4006,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B70" s="1">
         <v>589</v>
@@ -3956,7 +4017,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B71" s="1">
         <v>277</v>
@@ -3967,7 +4028,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B72" s="1">
         <v>3704</v>
@@ -3978,7 +4039,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B73" s="1">
         <v>2647</v>
@@ -3989,7 +4050,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B74" s="1">
         <v>185</v>
@@ -4000,7 +4061,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B75" s="1">
         <v>958</v>
@@ -4011,7 +4072,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B76" s="10">
         <v>280400</v>
@@ -4038,14 +4099,14 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B80" s="1">
         <v>140310</v>
@@ -4056,7 +4117,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B81" s="1">
         <v>4687</v>
@@ -4067,7 +4128,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B82" s="1">
         <v>628</v>
@@ -4078,7 +4139,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B83" s="1">
         <v>807</v>
@@ -4089,7 +4150,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B84" s="1">
         <v>1000</v>
@@ -4100,7 +4161,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B85" s="1">
         <v>2074</v>
@@ -4111,7 +4172,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B86" s="1">
         <v>2028</v>
@@ -4122,7 +4183,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B87" s="1">
         <v>4534</v>
@@ -4133,7 +4194,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B88" s="1">
         <v>227</v>
@@ -4144,7 +4205,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B89" s="1">
         <v>547</v>
@@ -4155,7 +4216,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B90" s="1">
         <v>51934</v>
@@ -4166,7 +4227,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B91" s="10">
         <v>228466</v>
@@ -4177,7 +4238,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B92" s="1">
         <v>437242</v>
@@ -4193,14 +4254,14 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B95" s="1">
         <v>3043</v>
@@ -4211,7 +4272,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B96" s="1">
         <v>10</v>
@@ -4222,21 +4283,21 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B99" s="1">
         <v>7995</v>
@@ -4247,7 +4308,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B100" s="1">
         <v>11758</v>
@@ -4258,7 +4319,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B101" s="1">
         <v>711</v>
@@ -4269,7 +4330,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B102" s="1">
         <v>445</v>
@@ -4291,7 +4352,7 @@
     </row>
     <row r="104" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B104" s="11">
         <v>461204</v>
@@ -4303,22 +4364,22 @@
     <row r="105" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B107" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C107" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D107" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E107" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F107" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G107" t="s">
         <v>10</v>
@@ -4332,7 +4393,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B108" s="15">
         <v>7995</v>
@@ -4344,7 +4405,7 @@
         <v>11456</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F108" s="15">
         <v>19813</v>
@@ -4361,19 +4422,19 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D109" s="15">
         <v>3140</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F109" s="15">
         <v>3140</v>
@@ -4390,16 +4451,16 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E110" s="16">
         <v>782</v>
@@ -4408,7 +4469,7 @@
         <v>782</v>
       </c>
       <c r="G110" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H110" s="16">
         <v>92</v>
@@ -4445,28 +4506,28 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D112" s="15">
         <v>-2838</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F112" s="15">
         <v>-2838</v>
       </c>
       <c r="G112" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H112" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I112" s="15">
         <v>-2838</v>
@@ -4474,28 +4535,28 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C113" s="15">
         <v>12</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F113" s="15">
         <v>12</v>
       </c>
       <c r="G113" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H113" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I113" s="15">
         <v>12</v>
@@ -4503,28 +4564,28 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E114" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F114" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G114" s="16">
         <v>-3</v>
       </c>
       <c r="H114" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I114" s="16">
         <v>-3</v>
@@ -4532,7 +4593,7 @@
     </row>
     <row r="115" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B115" s="17">
         <v>7995</v>
@@ -4562,23 +4623,23 @@
     <row r="116" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B118" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C118" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B120" s="1">
         <v>3699</v>
@@ -4589,7 +4650,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B121" s="1">
         <v>-602</v>
@@ -4600,14 +4661,14 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B123" s="1">
         <v>6256</v>
@@ -4618,7 +4679,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B124" s="1">
         <v>-326</v>
@@ -4629,7 +4690,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B125" s="1">
         <v>133</v>
@@ -4640,7 +4701,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B126" s="1">
         <v>206</v>
@@ -4651,7 +4712,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B127" s="1">
         <v>58</v>
@@ -4662,7 +4723,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B128" s="1">
         <v>-1280</v>
@@ -4673,7 +4734,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B129" s="1">
         <v>31916</v>
@@ -4684,7 +4745,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B130" s="1">
         <v>-35642</v>
@@ -4695,7 +4756,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B131" s="10">
         <v>-1071</v>
@@ -4714,14 +4775,14 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B134" s="1">
         <v>-2838</v>
@@ -4736,14 +4797,14 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B137" s="1">
         <v>-103</v>
@@ -4754,10 +4815,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C138" s="10">
         <v>-560</v>
@@ -4773,7 +4834,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B140" s="1">
         <v>172</v>
@@ -4784,7 +4845,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B141" s="1">
         <v>578</v>
@@ -4795,7 +4856,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B142" s="10">
         <v>3944</v>
@@ -4806,7 +4867,7 @@
     </row>
     <row r="143" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B143" s="11">
         <v>4522</v>
@@ -4817,14 +4878,14 @@
     </row>
     <row r="144" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B145" s="1">
         <v>4675</v>
@@ -4835,7 +4896,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B146" s="1">
         <v>112</v>
@@ -4846,7 +4907,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B147" s="1">
         <v>417</v>
@@ -4886,13 +4947,13 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" t="s">
         <v>108</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -4991,7 +5052,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B13" s="1">
         <v>499941</v>
@@ -5002,7 +5063,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B14" s="1">
         <v>567652</v>
@@ -5073,18 +5134,18 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" t="s">
         <v>108</v>
-      </c>
-      <c r="C23" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -5094,7 +5155,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>246</v>
       </c>
       <c r="B26" s="1">
         <v>20188</v>
@@ -5105,7 +5166,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" s="1">
         <v>-15622</v>
@@ -5116,7 +5177,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28" s="10">
         <v>-1564</v>
@@ -5135,14 +5196,14 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B31" s="1">
         <v>4877</v>
@@ -5153,7 +5214,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B32" s="10">
         <v>4267</v>
@@ -5172,7 +5233,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B34" s="1">
         <v>-9032</v>
@@ -5183,7 +5244,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B35" s="1">
         <v>266</v>
@@ -5194,7 +5255,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B36" s="1">
         <v>-178</v>
@@ -5213,14 +5274,14 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B39" s="1">
         <v>4808</v>
@@ -5231,7 +5292,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B40" s="10">
         <v>-4808</v>
@@ -5242,15 +5303,15 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -5268,7 +5329,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B44" s="1">
         <v>-2635</v>
@@ -5279,7 +5340,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B45" s="1">
         <v>-160</v>
@@ -5290,7 +5351,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B46" s="1">
         <v>-105</v>
@@ -5301,18 +5362,18 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B47" s="10">
         <v>-126</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B48" s="1">
         <v>2339</v>
@@ -5323,7 +5384,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B49" s="1">
         <v>-80</v>
@@ -5334,7 +5395,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B50" s="1">
         <v>2419</v>
@@ -5345,7 +5406,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B51" s="10">
         <v>1</v>
@@ -5367,7 +5428,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B53" s="10">
         <v>24</v>
@@ -5378,7 +5439,7 @@
     </row>
     <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B54" s="11">
         <v>2394</v>
@@ -5390,34 +5451,34 @@
     <row r="55" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>219</v>
+      </c>
+      <c r="B57" t="s">
+        <v>107</v>
+      </c>
+      <c r="C57" t="s">
+        <v>108</v>
+      </c>
+      <c r="D57" t="s">
         <v>220</v>
-      </c>
-      <c r="B57" t="s">
-        <v>108</v>
-      </c>
-      <c r="C57" t="s">
-        <v>109</v>
-      </c>
-      <c r="D57" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C58" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D58" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B60" s="1">
         <v>3944</v>
@@ -5431,7 +5492,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B61" s="1">
         <v>91904</v>
@@ -5445,7 +5506,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B62" s="1">
         <v>24449</v>
@@ -5459,7 +5520,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B63" s="1">
         <v>13589</v>
@@ -5473,7 +5534,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B64" s="10">
         <v>7849</v>
@@ -5498,7 +5559,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B67" s="1">
         <v>902</v>
@@ -5512,7 +5573,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B68" s="1">
         <v>6546</v>
@@ -5526,7 +5587,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B69" s="1">
         <v>7072</v>
@@ -5540,7 +5601,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B70" s="1">
         <v>2484</v>
@@ -5554,7 +5615,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B71" s="1">
         <v>1486</v>
@@ -5568,7 +5629,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B72" s="1">
         <v>544</v>
@@ -5582,7 +5643,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B73" s="1">
         <v>252</v>
@@ -5596,7 +5657,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B74" s="1">
         <v>3117</v>
@@ -5610,7 +5671,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B75" s="1">
         <v>2344</v>
@@ -5624,7 +5685,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B76" s="1">
         <v>144</v>
@@ -5638,7 +5699,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B77" s="1">
         <v>804</v>
@@ -5652,7 +5713,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B78" s="10">
         <v>243186</v>
@@ -5683,7 +5744,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -5691,7 +5752,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B82" s="1">
         <v>129689</v>
@@ -5705,7 +5766,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B83" s="1">
         <v>4953</v>
@@ -5719,7 +5780,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B84" s="1">
         <v>475</v>
@@ -5733,7 +5794,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B85" s="1">
         <v>748</v>
@@ -5747,7 +5808,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B86" s="1">
         <v>1000</v>
@@ -5761,7 +5822,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B87" s="1">
         <v>1208</v>
@@ -5775,7 +5836,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B88" s="1">
         <v>1672</v>
@@ -5789,7 +5850,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B89" s="1">
         <v>4401</v>
@@ -5803,7 +5864,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B90" s="1">
         <v>97</v>
@@ -5817,7 +5878,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B91" s="1">
         <v>514</v>
@@ -5831,7 +5892,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B92" s="1">
         <v>47410</v>
@@ -5845,7 +5906,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B93" s="10">
         <v>195776</v>
@@ -5859,7 +5920,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B94" s="1">
         <v>387943</v>
@@ -5873,7 +5934,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -5881,7 +5942,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B96" s="1">
         <v>2844</v>
@@ -5895,7 +5956,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B97" s="1">
         <v>16</v>
@@ -5909,7 +5970,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -5917,7 +5978,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -5925,7 +5986,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B100" s="1">
         <v>7995</v>
@@ -5939,7 +6000,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B101" s="1">
         <v>11456</v>
@@ -5953,7 +6014,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B102" s="1">
         <v>-71</v>
@@ -5967,7 +6028,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B103" s="10">
         <v>433</v>
@@ -5995,7 +6056,7 @@
     </row>
     <row r="105" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B105" s="11">
         <v>410616</v>
@@ -6010,22 +6071,22 @@
     <row r="106" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B108" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C108" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D108" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E108" t="s">
+        <v>227</v>
+      </c>
+      <c r="F108" t="s">
         <v>228</v>
-      </c>
-      <c r="F108" t="s">
-        <v>229</v>
       </c>
       <c r="G108" t="s">
         <v>10</v>
@@ -6039,7 +6100,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B109" s="15">
         <v>7884</v>
@@ -6051,7 +6112,7 @@
         <v>12054</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F109" s="15">
         <v>20004</v>
@@ -6068,28 +6129,28 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D110" s="16">
         <v>-31</v>
       </c>
       <c r="E110" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F110" s="16">
         <v>-31</v>
       </c>
       <c r="G110" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H110" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I110" s="16">
         <v>-31</v>
@@ -6097,7 +6158,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B111" s="15">
         <v>7884</v>
@@ -6129,16 +6190,16 @@
         <v>3</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D112" s="15">
         <v>2394</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F112" s="15">
         <v>2394</v>
@@ -6155,16 +6216,16 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E113" s="16">
         <v>288</v>
@@ -6173,7 +6234,7 @@
         <v>288</v>
       </c>
       <c r="G113" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H113" s="16">
         <v>87</v>
@@ -6210,28 +6271,28 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D115" s="15">
         <v>-2934</v>
       </c>
       <c r="E115" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F115" s="15">
         <v>-2934</v>
       </c>
       <c r="G115" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H115" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I115" s="15">
         <v>-2934</v>
@@ -6239,28 +6300,28 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C116" s="15">
         <v>8</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F116" s="15">
         <v>8</v>
       </c>
       <c r="G116" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H116" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I116" s="15">
         <v>8</v>
@@ -6268,28 +6329,28 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B117" s="15">
         <v>111</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E117" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F117" s="15">
         <v>111</v>
       </c>
       <c r="G117" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H117" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I117" s="15">
         <v>111</v>
@@ -6297,19 +6358,19 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D118" s="16">
         <v>-27</v>
       </c>
       <c r="E118" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F118" s="16">
         <v>-27</v>
@@ -6318,7 +6379,7 @@
         <v>-36</v>
       </c>
       <c r="H118" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I118" s="16">
         <v>-63</v>
@@ -6326,7 +6387,7 @@
     </row>
     <row r="119" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B119" s="17">
         <v>7995</v>
@@ -6338,7 +6399,7 @@
         <v>11456</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F119" s="17">
         <v>19813</v>
@@ -6356,28 +6417,28 @@
     <row r="120" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B122" t="s">
+        <v>107</v>
+      </c>
+      <c r="C122" t="s">
         <v>108</v>
-      </c>
-      <c r="C122" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C123" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B125">
         <v>2339</v>
@@ -6388,7 +6449,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B126">
         <v>-360</v>
@@ -6399,12 +6460,12 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B128">
         <v>9242</v>
@@ -6415,7 +6476,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B129">
         <v>289</v>
@@ -6426,7 +6487,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B130">
         <v>206</v>
@@ -6437,7 +6498,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B131">
         <v>100</v>
@@ -6448,7 +6509,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B132">
         <v>-439</v>
@@ -6459,7 +6520,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B133">
         <v>-4267</v>
@@ -6470,7 +6531,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B134">
         <v>24224</v>
@@ -6481,7 +6542,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B135">
         <v>-27299</v>
@@ -6492,7 +6553,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B136" s="5">
         <v>-199</v>
@@ -6511,12 +6572,12 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B139">
         <v>-2934</v>
@@ -6527,12 +6588,12 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B142">
         <v>-185</v>
@@ -6543,7 +6604,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B143">
         <v>-560</v>
@@ -6562,7 +6623,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B145">
         <v>26</v>
@@ -6573,7 +6634,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B146">
         <v>183</v>
@@ -6584,7 +6645,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B147" s="5">
         <v>3761</v>
@@ -6595,7 +6656,7 @@
     </row>
     <row r="148" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B148" s="18">
         <v>3944</v>
@@ -6606,12 +6667,12 @@
     </row>
     <row r="149" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B150">
         <v>4210</v>
@@ -6622,7 +6683,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B151">
         <v>112</v>
@@ -6633,7 +6694,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B152">
         <v>400</v>
@@ -6680,18 +6741,18 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="20" t="s">
-        <v>236</v>
+      <c r="A3" s="2" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -6703,7 +6764,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B5" s="1">
         <v>1809</v>
@@ -6714,7 +6775,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B6" s="1">
         <v>1625</v>
@@ -6725,7 +6786,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B7" s="10">
         <v>184</v>
@@ -6757,13 +6818,13 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="22"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B11" s="1">
         <v>54322</v>
@@ -6774,7 +6835,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B12" s="1">
         <v>98025</v>
@@ -6796,7 +6857,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B14" s="10">
         <v>48246</v>
@@ -6818,7 +6879,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B16" s="10">
         <v>65410</v>
@@ -6829,7 +6890,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B17" s="1">
         <v>459392</v>
@@ -6840,7 +6901,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B18" s="1">
         <v>37689</v>
@@ -6851,7 +6912,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B19" s="10">
         <v>497081</v>
@@ -6861,9 +6922,9 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="20"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
@@ -6911,7 +6972,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B25" s="1">
         <v>9268</v>
@@ -6922,7 +6983,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B26" s="13">
         <v>1.2</v>
@@ -6933,29 +6994,28 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C29" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B30" s="19"/>
+        <v>120</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B32" s="1">
         <v>58060</v>
@@ -6966,7 +7026,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B33" s="10">
         <v>-3738</v>
@@ -6977,7 +7037,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B34" s="12">
         <v>54322</v>
@@ -6988,14 +7048,14 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B36" s="1">
         <v>-4898</v>
@@ -7006,7 +7066,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B37" s="10">
         <v>-16011</v>
@@ -7017,7 +7077,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B38" s="1">
         <v>-11113</v>
@@ -7047,21 +7107,21 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B43" s="1">
         <v>48611</v>
@@ -7072,7 +7132,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B44" s="10">
         <v>-2537</v>
@@ -7083,7 +7143,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B45" s="1">
         <v>46074</v>
@@ -7094,14 +7154,14 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B47" s="1">
         <v>-12410</v>
@@ -7112,7 +7172,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B48" s="10">
         <v>1169</v>
@@ -7123,7 +7183,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B49" s="1">
         <v>-11241</v>
@@ -7134,7 +7194,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B50" s="10">
         <v>2172</v>
@@ -7145,7 +7205,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B51" s="1">
         <v>37005</v>
@@ -7156,7 +7216,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B52" s="1">
         <v>2148</v>
@@ -7167,7 +7227,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B53" s="1">
         <v>3249</v>
@@ -7178,7 +7238,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B54" s="1">
         <v>474</v>
@@ -7189,7 +7249,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B55" s="1">
         <v>109</v>
@@ -7200,7 +7260,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B56" s="10">
         <v>168</v>
@@ -7211,7 +7271,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B57" s="1">
         <v>3381</v>
@@ -7222,7 +7282,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B58" s="10">
         <v>199</v>
@@ -7233,7 +7293,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B59" s="1">
         <v>3182</v>
@@ -7244,7 +7304,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B60" s="10">
         <v>3</v>
@@ -7266,7 +7326,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B62" s="10">
         <v>184</v>
@@ -7277,7 +7337,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B63" s="12">
         <v>2995</v>
@@ -7288,23 +7348,23 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B66" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C66" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B68" s="1">
         <v>3761</v>
@@ -7315,7 +7375,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B69" s="1">
         <v>87814</v>
@@ -7326,7 +7386,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B70" s="1">
         <v>24012</v>
@@ -7337,7 +7397,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B71" s="1">
         <v>12663</v>
@@ -7348,7 +7408,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B72" s="1">
         <v>8315</v>
@@ -7359,7 +7419,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B73" s="10">
         <v>3660</v>
@@ -7378,7 +7438,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B75" s="1">
         <v>7041</v>
@@ -7389,7 +7449,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B76" s="1">
         <v>6877</v>
@@ -7400,7 +7460,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B77" s="1">
         <v>6372</v>
@@ -7411,7 +7471,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B78" s="1">
         <v>2450</v>
@@ -7422,7 +7482,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B79" s="1">
         <v>1120</v>
@@ -7433,7 +7493,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B80" s="1">
         <v>532</v>
@@ -7444,7 +7504,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B81" s="1">
         <v>257</v>
@@ -7455,7 +7515,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B82" s="1">
         <v>2091</v>
@@ -7466,7 +7526,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B83" s="1">
         <v>4825</v>
@@ -7477,7 +7537,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B84" s="1">
         <v>254</v>
@@ -7488,7 +7548,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B85" s="1">
         <v>315</v>
@@ -7499,7 +7559,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B86" s="1">
         <v>221623</v>
@@ -7520,20 +7580,20 @@
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88" s="20"/>
+      <c r="A88" s="2"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B90" s="1">
         <v>134389</v>
@@ -7544,7 +7604,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B91" s="1">
         <v>1568</v>
@@ -7555,7 +7615,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B92" s="1">
         <v>747</v>
@@ -7566,7 +7626,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B93" s="1">
         <v>1000</v>
@@ -7577,7 +7637,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B94" s="1">
         <v>1646</v>
@@ -7588,7 +7648,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B95" s="1">
         <v>1575</v>
@@ -7599,7 +7659,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B96" s="1">
         <v>2047</v>
@@ -7610,7 +7670,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B97" s="1">
         <v>2935</v>
@@ -7621,7 +7681,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B98" s="1">
         <v>50</v>
@@ -7632,7 +7692,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B99" s="1">
         <v>892</v>
@@ -7643,7 +7703,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B100" s="10">
         <v>221623</v>
@@ -7654,7 +7714,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B101" s="12">
         <v>368472</v>
@@ -7665,14 +7725,14 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B103" s="1">
         <v>3147</v>
@@ -7683,7 +7743,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B104" s="1">
         <v>51</v>
@@ -7701,14 +7761,14 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B107" s="1">
         <v>7884</v>
@@ -7719,7 +7779,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B108" s="1">
         <v>14258</v>
@@ -7730,7 +7790,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B109" s="1">
         <v>-255</v>
@@ -7741,7 +7801,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B110" s="10">
         <v>425</v>
@@ -7763,7 +7823,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B112" s="12">
         <v>393982</v>
@@ -7774,22 +7834,22 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B115" t="s">
-        <v>69</v>
-      </c>
-      <c r="C115" s="23" t="s">
-        <v>73</v>
+        <v>68</v>
+      </c>
+      <c r="C115" t="s">
+        <v>72</v>
       </c>
       <c r="D115" t="s">
-        <v>71</v>
-      </c>
-      <c r="E115" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="E115" t="s">
+        <v>243</v>
+      </c>
+      <c r="F115" t="s">
         <v>244</v>
-      </c>
-      <c r="F115" t="s">
-        <v>245</v>
       </c>
       <c r="G115" t="s">
         <v>10</v>
@@ -7803,7 +7863,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B116" s="15">
         <v>7884</v>
@@ -7861,7 +7921,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B118" s="16" t="s">
         <v>11</v>
@@ -7916,7 +7976,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B120" s="15" t="s">
         <v>11</v>
@@ -7945,7 +8005,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B121" s="15" t="s">
         <v>11</v>
@@ -7974,7 +8034,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B122" s="15" t="s">
         <v>11</v>
@@ -8003,7 +8063,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B123" s="15" t="s">
         <v>11</v>
@@ -8032,7 +8092,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B124" s="15">
         <v>7884</v>
@@ -8061,25 +8121,25 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B127" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C127" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A128" s="20" t="s">
-        <v>114</v>
+      <c r="A128" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B129" s="1">
         <v>3381</v>
@@ -8090,7 +8150,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B130" s="1">
         <v>-326</v>
@@ -8101,14 +8161,14 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B132" s="1">
         <v>-12992</v>
@@ -8119,7 +8179,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B133" s="1">
         <v>-491</v>
@@ -8130,7 +8190,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B134" s="1">
         <v>-354</v>
@@ -8141,7 +8201,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B135" s="1">
         <v>1972</v>
@@ -8152,7 +8212,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B136" s="1">
         <v>16011</v>
@@ -8163,7 +8223,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B137" s="10">
         <v>-860</v>
@@ -8182,14 +8242,14 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B140" s="1">
         <v>-1770</v>
@@ -8199,20 +8259,19 @@
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A141" s="19"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B143" s="1">
         <v>15714</v>
@@ -8223,7 +8282,7 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B144" s="1">
         <v>2398</v>
@@ -8234,7 +8293,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B145" s="1">
         <v>4129</v>
@@ -8245,7 +8304,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B146" s="1">
         <v>55</v>
@@ -8256,7 +8315,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B147" s="1">
         <v>-156</v>
@@ -8267,7 +8326,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B148" s="1">
         <v>-6</v>
@@ -8278,7 +8337,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B149" s="1">
         <v>-17493</v>
@@ -8289,7 +8348,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B150" s="1">
         <v>-4018</v>
@@ -8300,7 +8359,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B151" s="1">
         <v>-3980</v>
@@ -8311,7 +8370,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B152" s="10">
         <v>-710</v>
@@ -8330,7 +8389,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B154" s="1">
         <v>-14</v>
@@ -8341,7 +8400,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B155" s="1">
         <v>490</v>
@@ -8352,7 +8411,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B156" s="10">
         <v>3271</v>
@@ -8363,7 +8422,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B157" s="12">
         <v>3761</v>
@@ -8374,14 +8433,14 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B159" s="1">
         <v>3661</v>
@@ -8392,7 +8451,7 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B160" s="1">
         <v>116</v>
@@ -8403,7 +8462,7 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B161" s="1">
         <v>352</v>
@@ -8421,6 +8480,73 @@
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB2D2CB0-3C74-48F6-A0FC-1C79BE7E1C5C}">
+  <dimension ref="A2:F5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B2">
+        <v>2021</v>
+      </c>
+      <c r="C2">
+        <v>2022</v>
+      </c>
+      <c r="D2">
+        <v>2023</v>
+      </c>
+      <c r="E2">
+        <v>2024</v>
+      </c>
+      <c r="F2">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" cm="1">
+        <f t="array" ref="C3">_xlfn.XLOOKUP(A3,Table010__Page_10_1[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],Table010__Page_10_1[[#All],[2022]],"Not Found",0)</f>
+        <v>19424</v>
+      </c>
+      <c r="D3" s="1" cm="1">
+        <f t="array" ref="D3">_xlfn.XLOOKUP(A3,Table010__Page_10_1[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],Table010__Page_10_1[[#All],[2023]],"Not Found", 0)</f>
+        <v>20188</v>
+      </c>
+      <c r="E3" s="1" cm="1">
+        <f t="array" ref="E3">_xlfn.XLOOKUP(A3,Table010__Page_10[[#All],[Consolidated Satatements of Earnings (in Canadian $ millions)]],Table010__Page_10[[#All],[2024]],"Not Found", 0)</f>
+        <v>21007</v>
+      </c>
+      <c r="F3" s="1">
+        <f>_xlfn.XLOOKUP(A3,Table010__Page_9[Consolidated Statements Of Earnings (in Canadian $ Million)],Table010__Page_9[2025],"Not Found",0)</f>
+        <v>22131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Canada Life Annual Report Project.xlsx
+++ b/Canada Life Annual Report Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GMU058\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE6E9B8-EC0E-4F3C-B717-DEE847C5FF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00970483-80E7-419D-9B3C-93B76A3434B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{3CB541B1-AEC2-4997-AFCF-80587D906177}"/>
   </bookViews>
@@ -20,10 +20,10 @@
     <sheet name="CL Consolidated Summary" sheetId="16" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_2" localSheetId="0" hidden="1">'CL 2025 (Original)'!$A$21:$C$51</definedName>
-    <definedName name="ExternalData_3" localSheetId="0" hidden="1">'CL 2025 (Original)'!$A$55:$C$103</definedName>
-    <definedName name="ExternalData_4" localSheetId="0" hidden="1">'CL 2025 (Original)'!$A$106:$I$114</definedName>
-    <definedName name="ExternalData_5" localSheetId="0" hidden="1">'CL 2025 (Original)'!$A$118:$C$146</definedName>
+    <definedName name="ExternalData_2" localSheetId="0" hidden="1">'CL 2025 (Original)'!$A$24:$C$54</definedName>
+    <definedName name="ExternalData_3" localSheetId="0" hidden="1">'CL 2025 (Original)'!$A$58:$C$106</definedName>
+    <definedName name="ExternalData_4" localSheetId="0" hidden="1">'CL 2025 (Original)'!$A$109:$I$117</definedName>
+    <definedName name="ExternalData_5" localSheetId="0" hidden="1">'CL 2025 (Original)'!$A$121:$C$149</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +54,7 @@
     <author>Han, Eugene</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{2F1AC64B-51DF-41DB-A3BA-D2F7A4C31212}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{2F1AC64B-51DF-41DB-A3BA-D2F7A4C31212}">
       <text>
         <r>
           <rPr>
@@ -63,8 +63,190 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Canada Life adopted IFRS 17 beginning in 2023, which introduced the “Insurance revenue” line used in the newer annual reports. Therefore, 2022 Total net premiums is not directly comparable to 2023 to 2025 Insurance revenue because the accounting basis changed.
+          <t xml:space="preserve">Canada Life adopted IFRS 17 beginning in 2023, which introduced the “Insurance revenue” line used in the newer annual reports. Therefore, 2022 Total net premiums is not directly comparable to 2023 to 2025 Insurance revenue because the accounting basis changed. Since 2023, restated the 2022 annual, we will be dropping the 2021.
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{87F8FDE5-D62D-4E7F-A4BA-16BB35468722}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">For insurance companies, the cost of revenue (COGS) is close to the insurance service expenses
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{30CFD3FD-CCDC-4029-927A-6AAD5D42226B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">The insurance service result is the gross profit equivalent. 
+Gross profit is mainly used for mainly for manufacturing or retail companies, while Canada Life (CL) is an insurer operating under IFRS 17.
+Canada Life’s annual reports do not contain a line specifically called “Operating Income.” For an insurance company, the closest reported operating subtotal is generally Insurance service result, but it does not include all investment income, fee income, or administrative expenses.
+Insurance service result = insurance revenue - insurance service expenses - Net expense from reinsurance contracts.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{52185BAC-91F8-4007-BE14-C8BC8372536E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">This is the "Operating Expenses" equivalent. 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>NOTE:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve"> Canada Life also reports Insurance service expenses, which are different from operating and administrative expenses: Insurance service expenses relate directly to fulfilling insurance contracts, while operating and administrative expenses represent broader business operating costs. Both appear in the Consolidated Statements of Earnings, but in separate sections.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{1659F652-C2DB-4293-8464-90B77BE23056}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Canada Life uses the term“Net earnings” instead of“Net income.”</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A11" authorId="0" shapeId="0" xr:uid="{BC8F9592-D229-4214-BF29-23C47D38A133}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Canada Life does not report a single line called “Total debt.” The closest directly reported debt amount is“Debentures and other debt instruments”
+Canada Life also reports Preferred shares of $1,000 million in each of 2023, 2024, and 2025 within liabilities. However, preferred shares should not automatically be included in total debt unless your assignment specifically defines debt to include preferred capital.
+Do not use Total liabilities as total debt. Total liabilities also include insurance-contract liabilities, investment-contract liabilities, accounts payable, taxes, derivatives, and segregated-fund contract liabilities. For a standard financial comparison, Debentures and other debt instruments is the safest match for Total Debt.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{49202555-5642-4FDD-9E1A-C531441A6D5B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>For Canada Life, the annual reports do not explicitly label a line as "Operating Cash Flow". Instead, the net cash provided by operating activities is the subtotal at the bottom of the Operations section</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Important note for insurers
+For insurers such as Canada Life, operating cash flow is often less useful than for industrial companies because large policyholder liabilities and investment portfolio movements can create significant swings in cash flow. Analysts typically focus more on: Net earnings, Insurance service result, LICAT ratio, Contractual Service Margin (CSM), Book value / shareholder equity</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A13" authorId="0" shapeId="0" xr:uid="{6E6F5986-C5FF-4C2E-90CF-37E0CC3DF7DD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">CSM (Contractual Service Margin)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>The future profits that Canada Life expects to earn from insurance contracts that have already been sold.
+Example -Suppose Canada Life sells a long-term life insurance policy today.
+The company expects:
+Premiums received over time = $10,000
+Claims and expenses = $8,000
+Under IFRS 17, Canada Life cannot recognize the entire $2,000 profit immediately. Then the company gradually recognizes that profit over the life of the contract.
+A larger CSM means: More future earnings already locked in,  Greater earnings visibility, More profitable business written, Strong future cash generation potential
+For many insurers, CSM is viewed almost like an "order backlog."</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A17" authorId="0" shapeId="0" xr:uid="{07E7F086-D1ED-4C08-B9ED-98813F81BF49}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>LICAT is Canada's regulatory capital ratio for life insurers, established by the Office of the Superintendent of Financial Institutions (OSFI).</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+A higher ratio means the insurer has a larger cushion against adverse events such as: Market crashes, Interest rate shocks, Higher-than-expected death claims, Disability claims, Longevity risk, Credit losses, Operational failures.
+Why investors care - A high LICAT ratio means: Greater ability to withstand recessions, Better claim-paying ability, Lower insolvency risk, More flexibility to pay dividends, More room for growth and acquisitions, For insurers, a LICAT of around 120%-130%+ is generally considered strong.</t>
         </r>
       </text>
     </comment>
@@ -95,7 +277,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="247">
   <si>
     <t>Summary of net earnings attributable to:</t>
   </si>
@@ -139,9 +321,6 @@
     <t>Total equity</t>
   </si>
   <si>
-    <t>Insurance service expenses (note 13)</t>
-  </si>
-  <si>
     <t>Net expense from reinsurance contracts</t>
   </si>
   <si>
@@ -172,9 +351,6 @@
     <t>Other income and expenses</t>
   </si>
   <si>
-    <t>Operating and administrative expenses (note 13)</t>
-  </si>
-  <si>
     <t>Amortization of finite life intangible assets (note 9)</t>
   </si>
   <si>
@@ -265,9 +441,6 @@
     <t>Reinsurance contract held liabilities (note 15)</t>
   </si>
   <si>
-    <t>Debentures and other debt instruments (note 18)</t>
-  </si>
-  <si>
     <t>Preferred shares (note 23)</t>
   </si>
   <si>
@@ -397,9 +570,6 @@
     <t>Restructuring expenses (note 4)</t>
   </si>
   <si>
-    <t>Cash and cash e?uivalents (note 5)</t>
-  </si>
-  <si>
     <t>Accumulated other comprehensive income (loss) (note 27)</t>
   </si>
   <si>
@@ -727,9 +897,6 @@
     <t>Financial Highlights (in Canadian $ millions)</t>
   </si>
   <si>
-    <t>Consolidated Satatements of Earnings (in Canadian $ millions)</t>
-  </si>
-  <si>
     <t>Consolidated Balance Sheet  (in Canadian $ millions)</t>
   </si>
   <si>
@@ -832,16 +999,25 @@
     <t>Total shareholders’ equity</t>
   </si>
   <si>
-    <t>Annual Report Item</t>
-  </si>
-  <si>
     <t>Insurance revenue</t>
   </si>
   <si>
-    <t>Insurance service expenses, COGS equivalent</t>
-  </si>
-  <si>
-    <t>Insurance service result (gross profit equivalent)</t>
+    <t>Financial item (CAD $ millions)</t>
+  </si>
+  <si>
+    <t>Insurance service expenses</t>
+  </si>
+  <si>
+    <t>Operating and administrative expenses</t>
+  </si>
+  <si>
+    <t>Cash and cash equivalents</t>
+  </si>
+  <si>
+    <t>Debentures and other debt instruments</t>
+  </si>
+  <si>
+    <t>Operating cash flow</t>
   </si>
 </sst>
 </file>
@@ -851,7 +1027,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -872,6 +1048,33 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -931,10 +1134,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -970,11 +1174,86 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="71">
+  <dxfs count="75">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1163,62 +1442,6 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1232,28 +1455,24 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32C6B56A-ED7A-4BC5-86FB-BC86DC51FC56}" name="Table006__Page_7" displayName="Table006__Page_7" ref="A2:C17" totalsRowShown="0">
-  <autoFilter ref="A2:C17" xr:uid="{32C6B56A-ED7A-4BC5-86FB-BC86DC51FC56}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32C6B56A-ED7A-4BC5-86FB-BC86DC51FC56}" name="CL2025_Financial_Highlights" displayName="CL2025_Financial_Highlights" ref="A2:C21" totalsRowShown="0">
+  <autoFilter ref="A2:C21" xr:uid="{32C6B56A-ED7A-4BC5-86FB-BC86DC51FC56}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{5C2C5EAF-8FD7-4548-B79E-158A94C36CEC}" name="Financial Highlights (Unaudited) (in Canadian $ Million)" dataDxfId="54"/>
-    <tableColumn id="4" xr3:uid="{F845F529-FD47-4771-A575-3ECAFBD90817}" name="2025" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{2D1DF53C-C68C-4325-9449-0D2B4F3F7A6D}" name="2024" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{5C2C5EAF-8FD7-4548-B79E-158A94C36CEC}" name="Financial Highlights (Unaudited) (in Canadian $ Million)" dataDxfId="74"/>
+    <tableColumn id="4" xr3:uid="{F845F529-FD47-4771-A575-3ECAFBD90817}" name="2025" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{2D1DF53C-C68C-4325-9449-0D2B4F3F7A6D}" name="2024" dataDxfId="72"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{872B3C60-F251-4571-AC34-BA109A0E39B4}" name="Table017__Page_14" displayName="Table017__Page_14" ref="A118:C147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{872B3C60-F251-4571-AC34-BA109A0E39B4}" name="CL2024_Consolidated_Statements_Of_Cash_Flow" displayName="CL2024_Consolidated_Statements_Of_Cash_Flow" ref="A118:C147" totalsRowShown="0">
   <autoFilter ref="A118:C147" xr:uid="{872B3C60-F251-4571-AC34-BA109A0E39B4}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{03DD1A9C-855C-4E1B-BC85-F1DA52E562A1}" name="Consolidated Statements of Cash Flow  (in Canadian $ millions)" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{9F529541-D5F9-4E8A-9852-77076A9252D7}" name="2024" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{03DD1A9C-855C-4E1B-BC85-F1DA52E562A1}" name="Consolidated Statements of Cash Flow  (in Canadian $ millions)" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{9F529541-D5F9-4E8A-9852-77076A9252D7}" name="2024" dataDxfId="40"/>
     <tableColumn id="5" xr3:uid="{D60C0FDC-FC22-4E62-9467-CDCB0E581960}" name="2023"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1261,65 +1480,65 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{AECA25C1-C846-4A7B-A2BF-C9448B60FB0D}" name="Table005__Page_8_1" displayName="Table005__Page_8_1" ref="A2:C20" totalsRowShown="0">
-  <autoFilter ref="A2:C20" xr:uid="{AECA25C1-C846-4A7B-A2BF-C9448B60FB0D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{AECA25C1-C846-4A7B-A2BF-C9448B60FB0D}" name="CL2023_Financial_Highlights" displayName="CL2023_Financial_Highlights" ref="A2:C21" totalsRowShown="0">
+  <autoFilter ref="A2:C21" xr:uid="{AECA25C1-C846-4A7B-A2BF-C9448B60FB0D}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2FBD130F-2F76-40A4-8A35-F73D197CF679}" name="Financial Highlights (unaudited) (in Canadian $ millions)" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{EB1CCD9F-222B-42FF-A665-B40808CDFA23}" name="2023" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{606BD4DE-1AB4-4377-AD4C-304EEE364AE0}" name="2022" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{2FBD130F-2F76-40A4-8A35-F73D197CF679}" name="Financial Highlights (unaudited) (in Canadian $ millions)" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{EB1CCD9F-222B-42FF-A665-B40808CDFA23}" name="2023" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{606BD4DE-1AB4-4377-AD4C-304EEE364AE0}" name="2022" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{403F03B7-0B2F-429E-9099-05D4B79628EE}" name="Table010__Page_10_1" displayName="Table010__Page_10_1" ref="A23:C54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{403F03B7-0B2F-429E-9099-05D4B79628EE}" name="CL2023_Consolidated_Statements_Of_Earnings" displayName="CL2023_Consolidated_Statements_Of_Earnings" ref="A23:C54" totalsRowShown="0">
   <autoFilter ref="A23:C54" xr:uid="{403F03B7-0B2F-429E-9099-05D4B79628EE}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{348E9B7F-8015-4CEA-9CB7-F5A11E794924}" name="Consolidated Statements of Earnings (in Canadian $ millions)" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{9CB5D784-9668-43E2-912F-CCC0C5A46AFC}" name="2023" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{7DFA6E59-95B4-4F39-8D95-F85AC0C103B7}" name="2022" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{348E9B7F-8015-4CEA-9CB7-F5A11E794924}" name="Consolidated Statements of Earnings (in Canadian $ millions)" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{9CB5D784-9668-43E2-912F-CCC0C5A46AFC}" name="2023" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{7DFA6E59-95B4-4F39-8D95-F85AC0C103B7}" name="2022" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{C8294548-29F4-4247-8D91-46256870F255}" name="Table012__Page_12" displayName="Table012__Page_12" ref="A57:D105" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{C8294548-29F4-4247-8D91-46256870F255}" name="CL2023_Consolidated_Balance_Sheets" displayName="CL2023_Consolidated_Balance_Sheets" ref="A57:D105" totalsRowShown="0">
   <autoFilter ref="A57:D105" xr:uid="{C8294548-29F4-4247-8D91-46256870F255}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A77F868F-A01A-4E28-831C-123758FFEE1B}" name="Consolidated Balance Sheets (in Canadian $ millions)" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{BF1169F7-EA41-4E34-B1BE-468D058EC001}" name="2023" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{0DED70B6-5DBC-4722-9AEA-0F35DB477359}" name="2022" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{391AF299-CDE1-44A4-94F3-25223ECFCF43}" name="2021" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{A77F868F-A01A-4E28-831C-123758FFEE1B}" name="Consolidated Balance Sheets (in Canadian $ millions)" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{BF1169F7-EA41-4E34-B1BE-468D058EC001}" name="2023" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{0DED70B6-5DBC-4722-9AEA-0F35DB477359}" name="2022" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{391AF299-CDE1-44A4-94F3-25223ECFCF43}" name="2021" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{010BDDA1-0210-42C8-BA1E-98C8F4E39148}" name="Table014__Page_13" displayName="Table014__Page_13" ref="A108:I119" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{010BDDA1-0210-42C8-BA1E-98C8F4E39148}" name="CL2023_Consolidated_Statements_Of_Changes_In_Equity" displayName="CL2023_Consolidated_Statements_Of_Changes_In_Equity" ref="A108:I119" totalsRowShown="0">
   <autoFilter ref="A108:I119" xr:uid="{010BDDA1-0210-42C8-BA1E-98C8F4E39148}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{12AD67BC-57B1-41C3-A7A2-ECD190ADFB8A}" name="Consolidated Statements of Changes in Equity (in Canadian $ millions)" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{D69CD2BD-7405-43A8-B2F6-D33B29AE7319}" name="Share capital" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{D7419A9F-70E7-4602-A940-77D76211462A}" name="Contributed surplus" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{6F1EC460-0E36-4BAA-BD61-804EA1A7B604}" name="Accumulated surplus" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{ECC52595-0035-4144-8E9B-C830D055A87F}" name="Accumulated other comprehensive income (loss)" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{DD90BFCF-0719-4732-B663-A0F6DDCBB014}" name="Total shareholders' equity" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{45A80F18-CA21-485E-9774-7188CBDBD23A}" name="Non-controlling interests" dataDxfId="3"/>
-    <tableColumn id="13" xr3:uid="{5EFFD87C-8A6F-4E32-BC35-2981FB121A78}" name="Participating account surplus" dataDxfId="2"/>
-    <tableColumn id="15" xr3:uid="{E2F54086-E050-49D8-8244-5234819E6F63}" name="Total equity" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{12AD67BC-57B1-41C3-A7A2-ECD190ADFB8A}" name="Consolidated Statements of Changes in Equity (in Canadian $ millions)" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{D69CD2BD-7405-43A8-B2F6-D33B29AE7319}" name="Share capital" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{D7419A9F-70E7-4602-A940-77D76211462A}" name="Contributed surplus" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{6F1EC460-0E36-4BAA-BD61-804EA1A7B604}" name="Accumulated surplus" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{ECC52595-0035-4144-8E9B-C830D055A87F}" name="Accumulated other comprehensive income (loss)" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{DD90BFCF-0719-4732-B663-A0F6DDCBB014}" name="Total shareholders' equity" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{45A80F18-CA21-485E-9774-7188CBDBD23A}" name="Non-controlling interests" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{5EFFD87C-8A6F-4E32-BC35-2981FB121A78}" name="Participating account surplus" dataDxfId="22"/>
+    <tableColumn id="15" xr3:uid="{E2F54086-E050-49D8-8244-5234819E6F63}" name="Total equity" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{070ABDE2-BBC3-4908-AB0F-44D6EF66AED5}" name="Table016__Page_14" displayName="Table016__Page_14" ref="A122:C152" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{070ABDE2-BBC3-4908-AB0F-44D6EF66AED5}" name="CL2023_Consolidated_Statements_Of_Cash_Flows" displayName="CL2023_Consolidated_Statements_Of_Cash_Flows" ref="A122:C152" totalsRowShown="0">
   <autoFilter ref="A122:C152" xr:uid="{070ABDE2-BBC3-4908-AB0F-44D6EF66AED5}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7B75C2BC-A013-41C7-861B-9EDA9E0AE1BA}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{7B75C2BC-A013-41C7-861B-9EDA9E0AE1BA}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="20"/>
     <tableColumn id="5" xr3:uid="{D08EF108-C608-416D-A0FA-78700D08B198}" name="2023"/>
     <tableColumn id="7" xr3:uid="{0A748248-90C6-42D4-A30D-90D2E6522606}" name="2022"/>
   </tableColumns>
@@ -1328,10 +1547,10 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{DA35DAB2-1EB1-4099-B43A-7BBB210BD1B2}" name="Table005__Page_6" displayName="Table005__Page_6" ref="A2:C26" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{DA35DAB2-1EB1-4099-B43A-7BBB210BD1B2}" name="CL2022_Financial_Highlight" displayName="CL2022_Financial_Highlight" ref="A2:C26" totalsRowShown="0">
   <autoFilter ref="A2:C26" xr:uid="{DA35DAB2-1EB1-4099-B43A-7BBB210BD1B2}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{742648AB-0CC3-4711-89DE-BEA31617073E}" name="Financial Highlight (unaudited)  (in Canadian $ millions)" dataDxfId="70"/>
+    <tableColumn id="1" xr3:uid="{742648AB-0CC3-4711-89DE-BEA31617073E}" name="Financial Highlight (unaudited)  (in Canadian $ millions)" dataDxfId="19"/>
     <tableColumn id="4" xr3:uid="{8EFD586F-8504-433C-ACA7-A80E443245D8}" name="2022"/>
     <tableColumn id="6" xr3:uid="{F3762B59-FF64-4412-994B-4F79CC8C4273}" name="2021"/>
   </tableColumns>
@@ -1340,11 +1559,11 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{D352CFDF-76E1-4D3C-8C7B-7F57348B216F}" name="Table009__Page_8" displayName="Table009__Page_8" ref="A29:C63" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{D352CFDF-76E1-4D3C-8C7B-7F57348B216F}" name="CL2022_Consolidated_Statements_Of_Earnings" displayName="CL2022_Consolidated_Statements_Of_Earnings" ref="A29:C63" totalsRowShown="0">
   <autoFilter ref="A29:C63" xr:uid="{D352CFDF-76E1-4D3C-8C7B-7F57348B216F}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E02CB553-D5D4-402A-8C54-8DE755972EFF}" name="Consolidated Statements of Earnings  (in Canadian $ millions)" dataDxfId="69"/>
-    <tableColumn id="4" xr3:uid="{63FC9382-AFA6-415E-82F8-8CF40DE991D2}" name="2022" dataDxfId="68"/>
+    <tableColumn id="1" xr3:uid="{E02CB553-D5D4-402A-8C54-8DE755972EFF}" name="Consolidated Statements of Earnings  (in Canadian $ millions)" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{63FC9382-AFA6-415E-82F8-8CF40DE991D2}" name="2022" dataDxfId="17"/>
     <tableColumn id="6" xr3:uid="{75F17EC1-69D4-4F5D-8315-089CA34D666C}" name="2021"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1352,10 +1571,10 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{BB04493A-D9FF-4D74-A5D0-111BD2A4656C}" name="Table011__Page_10" displayName="Table011__Page_10" ref="A66:C112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{BB04493A-D9FF-4D74-A5D0-111BD2A4656C}" name="CL2022_Consolidated_Balance_Sheets" displayName="CL2022_Consolidated_Balance_Sheets" ref="A66:C112" totalsRowShown="0">
   <autoFilter ref="A66:C112" xr:uid="{BB04493A-D9FF-4D74-A5D0-111BD2A4656C}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{893DB4C7-64EE-4ADA-8217-9192AD5B689E}" name="Consolidated Balance Sheets" dataDxfId="67"/>
+    <tableColumn id="1" xr3:uid="{893DB4C7-64EE-4ADA-8217-9192AD5B689E}" name="Consolidated Balance Sheets" dataDxfId="16"/>
     <tableColumn id="4" xr3:uid="{DFF048A5-755F-448B-87C0-4E919F682AF0}" name="2022"/>
     <tableColumn id="6" xr3:uid="{5DD01DB6-24AF-4D26-80A0-169FFD04A979}" name="2021"/>
   </tableColumns>
@@ -1364,53 +1583,75 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{215DB435-83EB-4E91-B08B-67EC402A3AFF}" name="Table013__Page_11_1" displayName="Table013__Page_11_1" ref="A115:I124" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{215DB435-83EB-4E91-B08B-67EC402A3AFF}" name="CL2022_Consolidated_Statements_Of_Changes_In_Equity" displayName="CL2022_Consolidated_Statements_Of_Changes_In_Equity" ref="A115:I124" totalsRowShown="0">
   <autoFilter ref="A115:I124" xr:uid="{215DB435-83EB-4E91-B08B-67EC402A3AFF}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{09504AB0-770E-4D43-ACD1-DE5F040CED87}" name="Consolidated Statements of Changes in Equity" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{BFA1FFA7-6E3B-4F23-85D7-277A408FB401}" name="Share capital" dataDxfId="65"/>
-    <tableColumn id="5" xr3:uid="{701F6E9A-D8E6-4794-950B-B6C0DCDFFB6C}" name="Contributed surplus" dataDxfId="64"/>
-    <tableColumn id="7" xr3:uid="{C6BCA9CA-AA5E-4ECD-A8ED-3425059521DC}" name="Accumulated surplus" dataDxfId="63"/>
-    <tableColumn id="9" xr3:uid="{C387DAE6-44DC-4C88-B247-97FF4BBC177F}" name="Accumulated other comprehensive loss comprehensive loss" dataDxfId="62"/>
-    <tableColumn id="11" xr3:uid="{3D9F6865-2163-45E5-9E9F-FE1EFA6E0A4E}" name="Total shareholders’ equity" dataDxfId="61"/>
-    <tableColumn id="13" xr3:uid="{A62F3586-FEAD-4757-955C-167BA489C2DA}" name="Non-controlling interests" dataDxfId="60"/>
-    <tableColumn id="15" xr3:uid="{5EC6C0BE-4B74-4A04-B001-36C6B2FE1058}" name="Participating account surplus" dataDxfId="59"/>
-    <tableColumn id="17" xr3:uid="{63AE17E1-9D3F-402A-8E50-6A25D991559F}" name="Total equity" dataDxfId="58"/>
+    <tableColumn id="1" xr3:uid="{09504AB0-770E-4D43-ACD1-DE5F040CED87}" name="Consolidated Statements of Changes in Equity" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{BFA1FFA7-6E3B-4F23-85D7-277A408FB401}" name="Share capital" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{701F6E9A-D8E6-4794-950B-B6C0DCDFFB6C}" name="Contributed surplus" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{C6BCA9CA-AA5E-4ECD-A8ED-3425059521DC}" name="Accumulated surplus" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{C387DAE6-44DC-4C88-B247-97FF4BBC177F}" name="Accumulated other comprehensive loss comprehensive loss" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{3D9F6865-2163-45E5-9E9F-FE1EFA6E0A4E}" name="Total shareholders’ equity" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{A62F3586-FEAD-4757-955C-167BA489C2DA}" name="Non-controlling interests" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{5EC6C0BE-4B74-4A04-B001-36C6B2FE1058}" name="Participating account surplus" dataDxfId="8"/>
+    <tableColumn id="17" xr3:uid="{63AE17E1-9D3F-402A-8E50-6A25D991559F}" name="Total equity" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{34C03A14-B5FE-4A4C-A2DD-6F7C99CBB8B6}" name="Table010__Page_9" displayName="Table010__Page_9" ref="A21:C51" totalsRowShown="0">
-  <autoFilter ref="A21:C51" xr:uid="{34C03A14-B5FE-4A4C-A2DD-6F7C99CBB8B6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{34C03A14-B5FE-4A4C-A2DD-6F7C99CBB8B6}" name="CL2025_Consolidated_Statements_Of_Earnings" displayName="CL2025_Consolidated_Statements_Of_Earnings" ref="A24:C54" totalsRowShown="0">
+  <autoFilter ref="A24:C54" xr:uid="{34C03A14-B5FE-4A4C-A2DD-6F7C99CBB8B6}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{AF140A9C-2544-462A-8D05-83FCA92FCC29}" name="Consolidated Statements Of Earnings (in Canadian $ Million)" dataDxfId="51"/>
-    <tableColumn id="3" xr3:uid="{16B7134F-532D-42E5-B2C1-83A349FA9ED6}" name="2025" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{A04CC424-6000-4365-8CE5-358C2FA21877}" name="2024" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{AF140A9C-2544-462A-8D05-83FCA92FCC29}" name="Consolidated Statements Of Earnings (in Canadian $ Million)" dataDxfId="71"/>
+    <tableColumn id="3" xr3:uid="{16B7134F-532D-42E5-B2C1-83A349FA9ED6}" name="2025" dataDxfId="70"/>
+    <tableColumn id="5" xr3:uid="{A04CC424-6000-4365-8CE5-358C2FA21877}" name="2024" dataDxfId="69"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{395EA000-7795-40F0-80C9-309E26D34DB3}" name="Table015__Page_12_1" displayName="Table015__Page_12_1" ref="A127:C161" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{395EA000-7795-40F0-80C9-309E26D34DB3}" name="CL2022_Consolidated_Statements_Of_Cash_Flows" displayName="CL2022_Consolidated_Statements_Of_Cash_Flows" ref="A127:C161" totalsRowShown="0">
   <autoFilter ref="A127:C161" xr:uid="{395EA000-7795-40F0-80C9-309E26D34DB3}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D9D5A221-D279-446F-84E7-045892C71C4C}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{0B41E5F3-DDED-491F-B3FE-F07FAA1FC2F1}" name="2022" dataDxfId="56"/>
-    <tableColumn id="6" xr3:uid="{597E5080-187F-4732-87DD-297275C991F1}" name="2021" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{D9D5A221-D279-446F-84E7-045892C71C4C}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{0B41E5F3-DDED-491F-B3FE-F07FAA1FC2F1}" name="2022" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{597E5080-187F-4732-87DD-297275C991F1}" name="2021" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{62B2A73A-1EEC-46AC-91EE-7CD6FB19EA63}" name="CL_Annual_Financial_Item" displayName="CL_Annual_Financial_Item" ref="A1:E17" totalsRowShown="0">
+  <autoFilter ref="A1:E17" xr:uid="{62B2A73A-1EEC-46AC-91EE-7CD6FB19EA63}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{C65EBD19-CB55-4FE0-9E64-CCC55F3C53D5}" name="Financial item (CAD $ millions)"/>
+    <tableColumn id="2" xr3:uid="{64F0E65D-5B27-41C2-9D64-A1370C90CAE6}" name="2022" dataDxfId="3">
+      <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A2,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{5DB1D296-8814-4B6A-9833-E4A1CCA5D2FA}" name="2023" dataDxfId="2">
+      <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A2,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{59F5E5CB-387A-45BC-B330-F894B4F6DE82}" name="2024" dataDxfId="1">
+      <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A2,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{553985D8-0F6B-4CAB-A4A1-B67873C194FD}" name="2025" dataDxfId="0">
+      <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A2,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FABD7B52-E650-435A-863F-F68E89A607E8}" name="Table013__Page_11" displayName="Table013__Page_11" ref="A55:C103" totalsRowShown="0">
-  <autoFilter ref="A55:C103" xr:uid="{FABD7B52-E650-435A-863F-F68E89A607E8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FABD7B52-E650-435A-863F-F68E89A607E8}" name="CL2025_Consolidated_Balance_Sheet" displayName="CL2025_Consolidated_Balance_Sheet" ref="A58:C106" totalsRowShown="0">
+  <autoFilter ref="A58:C106" xr:uid="{FABD7B52-E650-435A-863F-F68E89A607E8}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D6729C5B-6996-4AD6-921A-4FCB66DC5B45}" name="Consolidated Balance Sheet  (in Canadian $ Million)" dataDxfId="48"/>
-    <tableColumn id="3" xr3:uid="{1B220B5B-DEB0-4054-AD07-3C5B3F8AACD1}" name="2025" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{D6729C5B-6996-4AD6-921A-4FCB66DC5B45}" name="Consolidated Balance Sheet  (in Canadian $ Million)" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{1B220B5B-DEB0-4054-AD07-3C5B3F8AACD1}" name="2025" dataDxfId="67"/>
     <tableColumn id="5" xr3:uid="{E50E6906-CAA9-42F6-9EB9-A1F697BB2F20}" name="2024"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1418,28 +1659,28 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CF654234-2B8F-4830-BE0E-554991835BD9}" name="Table015__Page_12" displayName="Table015__Page_12" ref="A106:I114" totalsRowShown="0">
-  <autoFilter ref="A106:I114" xr:uid="{CF654234-2B8F-4830-BE0E-554991835BD9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CF654234-2B8F-4830-BE0E-554991835BD9}" name="CL2025_Consolidated_Statements_Of_Change_In_Equity" displayName="CL2025_Consolidated_Statements_Of_Change_In_Equity" ref="A109:I117" totalsRowShown="0">
+  <autoFilter ref="A109:I117" xr:uid="{CF654234-2B8F-4830-BE0E-554991835BD9}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C372BC7B-EDAA-425F-B029-CC348E8759F1}" name="Consolidated Statements of Change in Equity" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{87A431C1-44DD-4CAE-8CF0-67ED9C3536FA}" name="Share Capital" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{1ACAEC2D-550E-4F1E-899C-D23FDA3C7A2F}" name="Contributed Surplus" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{DA9BD253-8ABA-4C4C-90D8-B886FCF7BB0C}" name="Accumulated Surplus" dataDxfId="43"/>
-    <tableColumn id="8" xr3:uid="{35415082-274B-4DFF-B6E0-53920A2A9F6D}" name="Accumulated Other Comprehensive Income" dataDxfId="42"/>
-    <tableColumn id="10" xr3:uid="{2F102C70-C964-49EB-A16F-A1842CC2B96F}" name="Total Shareholder's Equity" dataDxfId="41"/>
-    <tableColumn id="12" xr3:uid="{ECFC45BF-2FD7-4257-A71D-CD62160491EA}" name="Non-controlling Interest" dataDxfId="40"/>
-    <tableColumn id="14" xr3:uid="{E959836E-9965-4D14-BCC3-3BCC273F49C9}" name="Participating Account Surplus" dataDxfId="39"/>
-    <tableColumn id="16" xr3:uid="{C57C220A-153E-480B-8F20-BD9766EBCC5D}" name="Total Equity" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{C372BC7B-EDAA-425F-B029-CC348E8759F1}" name="Consolidated Statements of Change in Equity" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{87A431C1-44DD-4CAE-8CF0-67ED9C3536FA}" name="Share Capital" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{1ACAEC2D-550E-4F1E-899C-D23FDA3C7A2F}" name="Contributed Surplus" dataDxfId="64"/>
+    <tableColumn id="6" xr3:uid="{DA9BD253-8ABA-4C4C-90D8-B886FCF7BB0C}" name="Accumulated Surplus" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{35415082-274B-4DFF-B6E0-53920A2A9F6D}" name="Accumulated Other Comprehensive Income" dataDxfId="62"/>
+    <tableColumn id="10" xr3:uid="{2F102C70-C964-49EB-A16F-A1842CC2B96F}" name="Total Shareholder's Equity" dataDxfId="61"/>
+    <tableColumn id="12" xr3:uid="{ECFC45BF-2FD7-4257-A71D-CD62160491EA}" name="Non-controlling Interest" dataDxfId="60"/>
+    <tableColumn id="14" xr3:uid="{E959836E-9965-4D14-BCC3-3BCC273F49C9}" name="Participating Account Surplus" dataDxfId="59"/>
+    <tableColumn id="16" xr3:uid="{C57C220A-153E-480B-8F20-BD9766EBCC5D}" name="Total Equity" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3AAC487E-DBF0-4C56-AF4F-056F3601ED72}" name="Table017__Page_13" displayName="Table017__Page_13" ref="A118:C146" totalsRowShown="0">
-  <autoFilter ref="A118:C146" xr:uid="{3AAC487E-DBF0-4C56-AF4F-056F3601ED72}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3AAC487E-DBF0-4C56-AF4F-056F3601ED72}" name="CL2025_Consolidated_Statements_Of_Cash_Flow" displayName="CL2025_Consolidated_Statements_Of_Cash_Flow" ref="A121:C149" totalsRowShown="0">
+  <autoFilter ref="A121:C149" xr:uid="{3AAC487E-DBF0-4C56-AF4F-056F3601ED72}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2F45C01F-02D6-4CB5-9364-F722A27B3859}" name="Consolidated Statements of Cash Flow" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{2F45C01F-02D6-4CB5-9364-F722A27B3859}" name="Consolidated Statements of Cash Flow" dataDxfId="57"/>
     <tableColumn id="3" xr3:uid="{712741C7-204F-4298-8050-873B208D5060}" name="2025"/>
     <tableColumn id="5" xr3:uid="{2534FEF1-3F52-460C-AB74-977F2325376E}" name="2024"/>
   </tableColumns>
@@ -1448,11 +1689,11 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{80062148-2C94-44FA-AA84-D3AF2950CAE1}" name="Table005__Page_8" displayName="Table005__Page_8" ref="A2:C21" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{80062148-2C94-44FA-AA84-D3AF2950CAE1}" name="CL2024_Financial_Highlights" displayName="CL2024_Financial_Highlights" ref="A2:C21" totalsRowShown="0">
   <autoFilter ref="A2:C21" xr:uid="{80062148-2C94-44FA-AA84-D3AF2950CAE1}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A504AF7D-4077-4F75-AD8E-F00D66A4E1EB}" name="Financial Highlights (in Canadian $ millions)" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{6DE21333-8B6D-493E-A3FB-12219341B858}" name="2024" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{A504AF7D-4077-4F75-AD8E-F00D66A4E1EB}" name="Financial Highlights (in Canadian $ millions)" dataDxfId="56"/>
+    <tableColumn id="5" xr3:uid="{6DE21333-8B6D-493E-A3FB-12219341B858}" name="2024" dataDxfId="55"/>
     <tableColumn id="7" xr3:uid="{1D1F864D-619C-4D8B-BDCB-F9F994AD3F85}" name="2023"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1460,22 +1701,22 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F2E5B2C2-C7D4-4C68-B8DF-B451C6AD2FA5}" name="Table010__Page_10" displayName="Table010__Page_10" ref="A24:C54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F2E5B2C2-C7D4-4C68-B8DF-B451C6AD2FA5}" name="CL2024_Consolidated_Statement_Of_Earnings" displayName="CL2024_Consolidated_Statement_Of_Earnings" ref="A24:C54" totalsRowShown="0">
   <autoFilter ref="A24:C54" xr:uid="{F2E5B2C2-C7D4-4C68-B8DF-B451C6AD2FA5}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B00DF7C4-46F0-426A-99DA-8CD1485C8167}" name="Consolidated Satatements of Earnings (in Canadian $ millions)" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{6DBC8D88-3782-41F5-8C7F-4912F53C3845}" name="2024" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{0DA8B320-B9A4-43AB-B84E-C184D12EEBCE}" name="2023" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{B00DF7C4-46F0-426A-99DA-8CD1485C8167}" name="Consolidated Statements of Earnings (in Canadian $ millions)" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{6DBC8D88-3782-41F5-8C7F-4912F53C3845}" name="2024" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{0DA8B320-B9A4-43AB-B84E-C184D12EEBCE}" name="2023" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{09288B11-3956-44BF-B015-CDD67BF6122B}" name="Table013__Page_12" displayName="Table013__Page_12" ref="A57:C104" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{09288B11-3956-44BF-B015-CDD67BF6122B}" name="CL2024_Consolidated_Balance_Sheet" displayName="CL2024_Consolidated_Balance_Sheet" ref="A57:C104" totalsRowShown="0">
   <autoFilter ref="A57:C104" xr:uid="{09288B11-3956-44BF-B015-CDD67BF6122B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{9A2A315A-17C4-44C5-839B-27077EDAFBE8}" name="Consolidated Balance Sheet  (in Canadian $ millions)" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{9A2A315A-17C4-44C5-839B-27077EDAFBE8}" name="Consolidated Balance Sheet  (in Canadian $ millions)" dataDxfId="51"/>
     <tableColumn id="3" xr3:uid="{AC35110F-0BC5-4C19-B333-64D500DD652D}" name="2024"/>
     <tableColumn id="5" xr3:uid="{FC18CAD8-EF52-4B84-B287-4440BF8988D1}" name="2023"/>
   </tableColumns>
@@ -1484,18 +1725,18 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{95B36E1D-5C8B-415A-8BB2-72AC852DFE1F}" name="Table015__Page_13" displayName="Table015__Page_13" ref="A107:I115" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{95B36E1D-5C8B-415A-8BB2-72AC852DFE1F}" name="CL2024_Consolidated_Statements_Of_Changes_In_Equity" displayName="CL2024_Consolidated_Statements_Of_Changes_In_Equity" ref="A107:I115" totalsRowShown="0">
   <autoFilter ref="A107:I115" xr:uid="{95B36E1D-5C8B-415A-8BB2-72AC852DFE1F}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{346EBBBA-D3E8-43C4-B112-84CFBA884811}" name="Consolidated Statements of Changes in Equity  (in Canadian $ millions)" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{A3F2222E-550B-4C91-822F-4D93B86D0518}" name="Share capital" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{5DE7CF1E-A17D-4E32-B7FB-FD3FCA7A27C6}" name="Contributed surplus" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{7CD3F9B9-2C9F-423A-9B10-5566ED617B23}" name="Accumulated surplus" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{81A55F20-6E2D-49CB-A777-7EA2FA186E54}" name="Accumulated other comprehensive income (loss)" dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{436743AE-2B63-4A1B-B86F-48A200522D06}" name="Total shareholder's equity" dataDxfId="25"/>
-    <tableColumn id="12" xr3:uid="{185E9850-C6B0-4386-B196-713B0971812A}" name="Non-controlling interests" dataDxfId="24"/>
-    <tableColumn id="14" xr3:uid="{F07A79B8-D988-4A89-BC52-58700AEF495C}" name="Participating account surplus" dataDxfId="23"/>
-    <tableColumn id="16" xr3:uid="{DAC2842E-0699-4DFF-A5A2-CA0460B0936F}" name="Total equity" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{346EBBBA-D3E8-43C4-B112-84CFBA884811}" name="Consolidated Statements of Changes in Equity  (in Canadian $ millions)" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{A3F2222E-550B-4C91-822F-4D93B86D0518}" name="Share capital" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{5DE7CF1E-A17D-4E32-B7FB-FD3FCA7A27C6}" name="Contributed surplus" dataDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{7CD3F9B9-2C9F-423A-9B10-5566ED617B23}" name="Accumulated surplus" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{81A55F20-6E2D-49CB-A777-7EA2FA186E54}" name="Accumulated other comprehensive income (loss)" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{436743AE-2B63-4A1B-B86F-48A200522D06}" name="Total shareholder's equity" dataDxfId="45"/>
+    <tableColumn id="12" xr3:uid="{185E9850-C6B0-4386-B196-713B0971812A}" name="Non-controlling interests" dataDxfId="44"/>
+    <tableColumn id="14" xr3:uid="{F07A79B8-D988-4A89-BC52-58700AEF495C}" name="Participating account surplus" dataDxfId="43"/>
+    <tableColumn id="16" xr3:uid="{DAC2842E-0699-4DFF-A5A2-CA0460B0936F}" name="Total equity" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1818,7 +2059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BEB5D32-C32B-46D8-AAE3-E026189F450B}">
-  <dimension ref="A2:I146"/>
+  <dimension ref="A2:I149"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="72.6328125" bestFit="1" customWidth="1"/>
@@ -1835,17 +2076,17 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1"/>
@@ -1866,1068 +2107,1010 @@
       <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="10">
         <v>2724</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="10">
         <v>3140</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="10">
         <v>2766</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="10">
         <v>3247</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" s="23"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B8" s="1">
         <v>3450</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C8" s="1">
         <v>3258</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B9" s="1">
         <v>603</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C9" s="1">
         <v>1015</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="10">
         <v>3016</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C10" s="10">
         <v>2853</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="23"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B12" s="1">
         <v>505652</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C12" s="1">
         <v>461204</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="1">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B13" s="1">
         <v>529301</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C13" s="1">
         <v>469722</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>207</v>
-      </c>
-      <c r="B12" s="1">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="1">
         <v>723435</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C14" s="1">
         <v>654853</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B15" s="1">
         <v>13494</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C15" s="1">
         <v>13243</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="1">
-        <v>3082</v>
-      </c>
-      <c r="C14" s="1">
-        <v>3043</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="1">
-        <v>10</v>
-      </c>
-    </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="1">
-        <v>20938</v>
-      </c>
-      <c r="C16" s="1">
-        <v>20909</v>
-      </c>
+      <c r="A16" s="21"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="1">
+        <v>3082</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3043</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="1">
+        <v>20938</v>
+      </c>
+      <c r="C19" s="1">
+        <v>20909</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B20" s="1">
         <v>24020</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C20" s="1">
         <v>23962</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>189</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>246</v>
-      </c>
-      <c r="B23" s="1">
-        <v>22131</v>
-      </c>
-      <c r="C23" s="1">
-        <v>21007</v>
+      <c r="A21" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="B21" s="13">
+        <v>1.28</v>
+      </c>
+      <c r="C21" s="13">
+        <v>1.3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="1">
+        <v>185</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>240</v>
+      </c>
+      <c r="B26" s="1">
+        <v>22131</v>
+      </c>
+      <c r="C26" s="1">
+        <v>21007</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>242</v>
+      </c>
+      <c r="B27" s="1">
         <v>-17002</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C27" s="1">
         <v>-16165</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="10">
-        <v>-1679</v>
-      </c>
-      <c r="C25" s="10">
-        <v>-1584</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="11">
-        <v>3450</v>
-      </c>
-      <c r="C26" s="11">
-        <v>3258</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="1">
-        <v>5837</v>
-      </c>
-      <c r="C28" s="1">
-        <v>5719</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>18</v>
-      </c>
-      <c r="B29" s="10">
-        <v>1328</v>
-      </c>
-      <c r="C29" s="10">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B30" s="1">
-        <v>7165</v>
-      </c>
-      <c r="C30" s="1">
-        <v>6999</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B28" s="10">
+        <v>-1679</v>
+      </c>
+      <c r="C28" s="10">
+        <v>-1584</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="11">
+        <v>3450</v>
+      </c>
+      <c r="C29" s="11">
+        <v>3258</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B31" s="1">
-        <v>-6116</v>
+        <v>5837</v>
       </c>
       <c r="C31" s="1">
-        <v>-5851</v>
+        <v>5719</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="1">
-        <v>-303</v>
-      </c>
-      <c r="C32" s="1">
-        <v>26</v>
+        <v>17</v>
+      </c>
+      <c r="B32" s="10">
+        <v>1328</v>
+      </c>
+      <c r="C32" s="10">
+        <v>1280</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B33" s="10">
-        <v>-143</v>
-      </c>
-      <c r="C33" s="10">
-        <v>-159</v>
+      <c r="B33" s="1">
+        <v>7165</v>
+      </c>
+      <c r="C33" s="1">
+        <v>6999</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
       <c r="B34" s="1">
-        <v>603</v>
+        <v>-6116</v>
       </c>
       <c r="C34" s="1">
-        <v>1015</v>
+        <v>-5851</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="B35" s="1">
+        <v>-303</v>
+      </c>
+      <c r="C35" s="1">
+        <v>26</v>
+      </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="1">
-        <v>5044</v>
-      </c>
-      <c r="C36" s="1">
-        <v>6828</v>
+        <v>20</v>
+      </c>
+      <c r="B36" s="10">
+        <v>-143</v>
+      </c>
+      <c r="C36" s="10">
+        <v>-159</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>19</v>
-      </c>
       <c r="B37" s="1">
-        <v>-5044</v>
+        <v>603</v>
       </c>
       <c r="C37" s="1">
-        <v>-6828</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>24</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="B39" s="1">
+        <v>5044</v>
+      </c>
+      <c r="C39" s="1">
+        <v>6828</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B40" s="1">
-        <v>3016</v>
+        <v>-5044</v>
       </c>
       <c r="C40" s="1">
-        <v>2853</v>
+        <v>-6828</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>25</v>
-      </c>
-      <c r="B41" s="1">
-        <v>-3408</v>
-      </c>
-      <c r="C41" s="1">
-        <v>-3088</v>
+      <c r="B41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>26</v>
-      </c>
-      <c r="B42" s="1">
-        <v>-194</v>
-      </c>
-      <c r="C42" s="1">
-        <v>-185</v>
-      </c>
+      <c r="A42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B43" s="1">
-        <v>-107</v>
+        <v>3016</v>
       </c>
       <c r="C43" s="1">
-        <v>-105</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>28</v>
+        <v>243</v>
       </c>
       <c r="B44" s="1">
-        <v>-346</v>
+        <v>-3408</v>
       </c>
       <c r="C44" s="1">
-        <v>-49</v>
+        <v>-3088</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B45" s="1">
-        <v>3014</v>
+        <v>-194</v>
       </c>
       <c r="C45" s="1">
-        <v>3699</v>
+        <v>-185</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B46" s="1">
-        <v>248</v>
+        <v>-107</v>
       </c>
       <c r="C46" s="1">
-        <v>455</v>
+        <v>-105</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B47" s="1">
-        <v>2766</v>
+        <v>-346</v>
       </c>
       <c r="C47" s="1">
-        <v>3244</v>
+        <v>-49</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>32</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>23</v>
+      <c r="A48" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" s="1">
+        <v>3014</v>
       </c>
       <c r="C48" s="1">
-        <v>-3</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B49" s="1">
+        <v>248</v>
+      </c>
+      <c r="C49" s="1">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50" s="1">
         <v>2766</v>
       </c>
-      <c r="C49" s="1">
-        <v>3247</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>33</v>
-      </c>
-      <c r="B50" s="1">
-        <v>42</v>
-      </c>
       <c r="C50" s="1">
-        <v>107</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>34</v>
-      </c>
-      <c r="B51" s="1">
+        <v>30</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="1">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="1">
+        <v>2766</v>
+      </c>
+      <c r="C52" s="1">
+        <v>3247</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" s="1">
+        <v>42</v>
+      </c>
+      <c r="C53" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B54" s="1">
         <v>2724</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C54" s="1">
         <v>3140</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>190</v>
-      </c>
-      <c r="B55" t="s">
-        <v>186</v>
-      </c>
-      <c r="C55" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>35</v>
-      </c>
-      <c r="B57" s="1">
-        <v>4679</v>
-      </c>
-      <c r="C57" s="1">
-        <v>4522</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>36</v>
-      </c>
-      <c r="B58" s="1">
-        <v>104567</v>
-      </c>
-      <c r="C58" s="1">
-        <v>100863</v>
+        <v>186</v>
+      </c>
+      <c r="B58" t="s">
+        <v>182</v>
+      </c>
+      <c r="C58" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="1">
-        <v>26009</v>
-      </c>
-      <c r="C59" s="1">
-        <v>25477</v>
+      <c r="A59" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>38</v>
+        <v>244</v>
       </c>
       <c r="B60" s="1">
-        <v>16990</v>
+        <v>4679</v>
       </c>
       <c r="C60" s="1">
-        <v>14794</v>
+        <v>4522</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="10">
-        <v>8277</v>
-      </c>
-      <c r="C61" s="10">
-        <v>8235</v>
+        <v>34</v>
+      </c>
+      <c r="B61" s="1">
+        <v>104567</v>
+      </c>
+      <c r="C61" s="1">
+        <v>100863</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>35</v>
+      </c>
       <c r="B62" s="1">
-        <v>160522</v>
+        <v>26009</v>
       </c>
       <c r="C62" s="1">
-        <v>153891</v>
+        <v>25477</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C63" s="1"/>
+      <c r="A63" t="s">
+        <v>36</v>
+      </c>
+      <c r="B63" s="1">
+        <v>16990</v>
+      </c>
+      <c r="C63" s="1">
+        <v>14794</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1256</v>
-      </c>
-      <c r="C64" s="1">
-        <v>858</v>
+        <v>37</v>
+      </c>
+      <c r="B64" s="10">
+        <v>8277</v>
+      </c>
+      <c r="C64" s="10">
+        <v>8235</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>41</v>
-      </c>
       <c r="B65" s="1">
-        <v>6399</v>
+        <v>160522</v>
       </c>
       <c r="C65" s="1">
-        <v>6544</v>
+        <v>153891</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="1">
-        <v>6905</v>
-      </c>
-      <c r="C66" s="1">
-        <v>6827</v>
-      </c>
+      <c r="C66" s="1"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B67" s="1">
-        <v>2983</v>
+        <v>1256</v>
       </c>
       <c r="C67" s="1">
-        <v>2866</v>
+        <v>858</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B68" s="1">
-        <v>1290</v>
+        <v>6399</v>
       </c>
       <c r="C68" s="1">
-        <v>1458</v>
+        <v>6544</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B69" s="1">
-        <v>641</v>
+        <v>6905</v>
       </c>
       <c r="C69" s="1">
-        <v>589</v>
+        <v>6827</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B70" s="1">
-        <v>321</v>
+        <v>2983</v>
       </c>
       <c r="C70" s="1">
-        <v>277</v>
+        <v>2866</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B71" s="1">
-        <v>3926</v>
+        <v>1290</v>
       </c>
       <c r="C71" s="1">
-        <v>3704</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B72" s="1">
-        <v>2981</v>
+        <v>641</v>
       </c>
       <c r="C72" s="1">
-        <v>2647</v>
+        <v>589</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B73" s="1">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C73" s="1">
-        <v>185</v>
+        <v>277</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B74" s="1">
-        <v>1156</v>
+        <v>3926</v>
       </c>
       <c r="C74" s="1">
-        <v>958</v>
+        <v>3704</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>51</v>
-      </c>
-      <c r="B75" s="10">
+        <v>46</v>
+      </c>
+      <c r="B75" s="1">
+        <v>2981</v>
+      </c>
+      <c r="C75" s="1">
+        <v>2647</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>47</v>
+      </c>
+      <c r="B76" s="1">
+        <v>315</v>
+      </c>
+      <c r="C76" s="1">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>48</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1156</v>
+      </c>
+      <c r="C77" s="1">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>49</v>
+      </c>
+      <c r="B78" s="10">
         <v>316957</v>
       </c>
-      <c r="C75" s="10">
+      <c r="C78" s="10">
         <v>280400</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="2" t="s">
+    <row r="79" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B76" s="11">
+      <c r="B79" s="11">
         <v>505652</v>
       </c>
-      <c r="C76" s="11">
+      <c r="C79" s="11">
         <v>461204</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="2"/>
-      <c r="C77" s="1"/>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>53</v>
-      </c>
-      <c r="B79" s="1">
-        <v>147329</v>
-      </c>
-      <c r="C79" s="1">
-        <v>140310</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>54</v>
-      </c>
-      <c r="B80" s="1">
-        <v>4422</v>
-      </c>
-      <c r="C80" s="1">
-        <v>4687</v>
-      </c>
+    <row r="80" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="2"/>
+      <c r="C80" s="1"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>55</v>
-      </c>
-      <c r="B81" s="1">
-        <v>787</v>
-      </c>
-      <c r="C81" s="1">
-        <v>628</v>
-      </c>
+      <c r="A81" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B82" s="1">
-        <v>827</v>
+        <v>147329</v>
       </c>
       <c r="C82" s="1">
-        <v>807</v>
+        <v>140310</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B83" s="1">
-        <v>1000</v>
+        <v>4422</v>
       </c>
       <c r="C83" s="1">
-        <v>1000</v>
+        <v>4687</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B84" s="1">
-        <v>2130</v>
+        <v>787</v>
       </c>
       <c r="C84" s="1">
-        <v>2074</v>
+        <v>628</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>58</v>
+        <v>245</v>
       </c>
       <c r="B85" s="1">
-        <v>2236</v>
+        <v>827</v>
       </c>
       <c r="C85" s="1">
-        <v>2028</v>
+        <v>807</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B86" s="1">
-        <v>5006</v>
+        <v>1000</v>
       </c>
       <c r="C86" s="1">
-        <v>4534</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B87" s="1">
-        <v>400</v>
+        <v>2130</v>
       </c>
       <c r="C87" s="1">
-        <v>227</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B88" s="1">
-        <v>538</v>
+        <v>2236</v>
       </c>
       <c r="C88" s="1">
-        <v>547</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B89" s="1">
-        <v>56153</v>
+        <v>5006</v>
       </c>
       <c r="C89" s="1">
-        <v>51934</v>
+        <v>4534</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>62</v>
-      </c>
-      <c r="B90" s="10">
+        <v>47</v>
+      </c>
+      <c r="B90" s="1">
+        <v>400</v>
+      </c>
+      <c r="C90" s="1">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>57</v>
+      </c>
+      <c r="B91" s="1">
+        <v>538</v>
+      </c>
+      <c r="C91" s="1">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>58</v>
+      </c>
+      <c r="B92" s="1">
+        <v>56153</v>
+      </c>
+      <c r="C92" s="1">
+        <v>51934</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>59</v>
+      </c>
+      <c r="B93" s="10">
         <v>260804</v>
       </c>
-      <c r="C90" s="10">
+      <c r="C93" s="10">
         <v>228466</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A91" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B91" s="1">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B94" s="1">
         <v>481632</v>
       </c>
-      <c r="C91" s="1">
+      <c r="C94" s="1">
         <v>437242</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A92" s="2"/>
-      <c r="C92" s="1"/>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A93" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>65</v>
-      </c>
-      <c r="B94" s="1">
-        <v>3082</v>
-      </c>
-      <c r="C94" s="1">
-        <v>3043</v>
-      </c>
-    </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>66</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C95" s="1">
-        <v>10</v>
-      </c>
+      <c r="A95" s="2"/>
+      <c r="C95" s="1"/>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>67</v>
+      <c r="A96" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>68</v>
-      </c>
-      <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
+        <v>62</v>
+      </c>
+      <c r="B97" s="1">
+        <v>3082</v>
+      </c>
+      <c r="C97" s="1">
+        <v>3043</v>
+      </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>69</v>
-      </c>
-      <c r="B98" s="1">
-        <v>7995</v>
+        <v>63</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C98" s="1">
-        <v>7995</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>70</v>
-      </c>
-      <c r="B99" s="1">
-        <v>11332</v>
-      </c>
-      <c r="C99" s="1">
-        <v>11758</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>71</v>
-      </c>
-      <c r="B100" s="1">
-        <v>1154</v>
-      </c>
-      <c r="C100" s="1">
-        <v>711</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>72</v>
-      </c>
-      <c r="B101" s="10">
+        <v>66</v>
+      </c>
+      <c r="B101" s="1">
+        <v>7995</v>
+      </c>
+      <c r="C101" s="1">
+        <v>7995</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>67</v>
+      </c>
+      <c r="B102" s="1">
+        <v>11332</v>
+      </c>
+      <c r="C102" s="1">
+        <v>11758</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>68</v>
+      </c>
+      <c r="B103" s="1">
+        <v>1154</v>
+      </c>
+      <c r="C103" s="1">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>69</v>
+      </c>
+      <c r="B104" s="10">
         <v>457</v>
       </c>
-      <c r="C101" s="10">
+      <c r="C104" s="10">
         <v>445</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A102" s="2" t="s">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A105" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B102" s="12">
+      <c r="B105" s="12">
         <v>24020</v>
       </c>
-      <c r="C102" s="12">
+      <c r="C105" s="12">
         <v>23962</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B103" s="11">
+    <row r="106" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A106" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B106" s="11">
         <v>505652</v>
       </c>
-      <c r="C103" s="11">
+      <c r="C106" s="11">
         <v>461204</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>191</v>
-      </c>
-      <c r="B106" t="s">
-        <v>197</v>
-      </c>
-      <c r="C106" t="s">
-        <v>198</v>
-      </c>
-      <c r="D106" t="s">
-        <v>199</v>
-      </c>
-      <c r="E106" t="s">
-        <v>200</v>
-      </c>
-      <c r="F106" t="s">
-        <v>201</v>
-      </c>
-      <c r="G106" t="s">
-        <v>202</v>
-      </c>
-      <c r="H106" t="s">
-        <v>203</v>
-      </c>
-      <c r="I106" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A107" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B107" s="3">
-        <v>7995</v>
-      </c>
-      <c r="C107" s="4">
-        <v>445</v>
-      </c>
-      <c r="D107" s="3">
-        <v>11758</v>
-      </c>
-      <c r="E107" s="4">
-        <v>711</v>
-      </c>
-      <c r="F107" s="3">
-        <v>20909</v>
-      </c>
-      <c r="G107" s="4">
-        <v>10</v>
-      </c>
-      <c r="H107" s="3">
-        <v>3043</v>
-      </c>
-      <c r="I107" s="4">
-        <v>23962</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>192</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D108" s="3">
-        <v>2724</v>
-      </c>
-      <c r="E108" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F108" s="3">
-        <v>2724</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H108" s="4">
-        <v>42</v>
-      </c>
-      <c r="I108" s="4">
-        <v>2766</v>
-      </c>
-    </row>
+    <row r="107" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
+        <v>187</v>
+      </c>
+      <c r="B109" t="s">
         <v>193</v>
       </c>
-      <c r="B109" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D109" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E109" s="7">
-        <v>443</v>
-      </c>
-      <c r="F109" s="7">
-        <v>443</v>
-      </c>
-      <c r="G109" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H109" s="7">
-        <v>-3</v>
-      </c>
-      <c r="I109" s="7">
-        <v>440</v>
+      <c r="C109" t="s">
+        <v>194</v>
+      </c>
+      <c r="D109" t="s">
+        <v>195</v>
+      </c>
+      <c r="E109" t="s">
+        <v>196</v>
+      </c>
+      <c r="F109" t="s">
+        <v>197</v>
+      </c>
+      <c r="G109" t="s">
+        <v>198</v>
+      </c>
+      <c r="H109" t="s">
+        <v>199</v>
+      </c>
+      <c r="I109" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A110" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="B110" s="3">
         <v>7995</v>
       </c>
@@ -2935,402 +3118,486 @@
         <v>445</v>
       </c>
       <c r="D110" s="3">
-        <v>14482</v>
-      </c>
-      <c r="E110" s="3">
-        <v>1154</v>
+        <v>11758</v>
+      </c>
+      <c r="E110" s="4">
+        <v>711</v>
       </c>
       <c r="F110" s="3">
-        <v>24076</v>
+        <v>20909</v>
       </c>
       <c r="G110" s="4">
         <v>10</v>
       </c>
       <c r="H110" s="3">
-        <v>3082</v>
+        <v>3043</v>
       </c>
       <c r="I110" s="4">
-        <v>27168</v>
+        <v>23962</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D111" s="3">
-        <v>-3150</v>
+        <v>2724</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F111" s="3">
-        <v>-3150</v>
+        <v>2724</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="H111" s="4">
+        <v>42</v>
       </c>
       <c r="I111" s="4">
-        <v>-3150</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>195</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C112" s="4">
+        <v>189</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E112" s="7">
+        <v>443</v>
+      </c>
+      <c r="F112" s="7">
+        <v>443</v>
+      </c>
+      <c r="G112" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H112" s="7">
+        <v>-3</v>
+      </c>
+      <c r="I112" s="7">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B113" s="3">
+        <v>7995</v>
+      </c>
+      <c r="C113" s="4">
+        <v>445</v>
+      </c>
+      <c r="D113" s="3">
+        <v>14482</v>
+      </c>
+      <c r="E113" s="3">
+        <v>1154</v>
+      </c>
+      <c r="F113" s="3">
+        <v>24076</v>
+      </c>
+      <c r="G113" s="4">
+        <v>10</v>
+      </c>
+      <c r="H113" s="3">
+        <v>3082</v>
+      </c>
+      <c r="I113" s="4">
+        <v>27168</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>190</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D114" s="3">
+        <v>-3150</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F114" s="3">
+        <v>-3150</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I114" s="4">
+        <v>-3150</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>191</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C115" s="4">
         <v>12</v>
       </c>
-      <c r="D112" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E112" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F112" s="4">
+      <c r="D115" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F115" s="4">
         <v>12</v>
       </c>
-      <c r="G112" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I112" s="4">
+      <c r="G115" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I115" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
-        <v>196</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E113" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F113" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G113" s="7">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>192</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G116" s="7">
         <v>-10</v>
       </c>
-      <c r="H113" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I113" s="7">
+      <c r="H116" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I116" s="7">
         <v>-10</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B114" s="8">
+    <row r="117" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A117" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B117" s="8">
         <v>7995</v>
       </c>
-      <c r="C114" s="9">
+      <c r="C117" s="9">
         <v>457</v>
       </c>
-      <c r="D114" s="8">
+      <c r="D117" s="8">
         <v>11332</v>
       </c>
-      <c r="E114" s="8">
+      <c r="E117" s="8">
         <v>1154</v>
       </c>
-      <c r="F114" s="8">
+      <c r="F117" s="8">
         <v>20938</v>
       </c>
-      <c r="G114" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H114" s="8">
+      <c r="G117" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H117" s="8">
         <v>3082</v>
       </c>
-      <c r="I114" s="9">
+      <c r="I117" s="9">
         <v>24020</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>205</v>
-      </c>
-      <c r="B118" t="s">
-        <v>186</v>
-      </c>
-      <c r="C118" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A119" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>29</v>
-      </c>
-      <c r="B120">
-        <v>3014</v>
-      </c>
-      <c r="C120">
-        <v>3699</v>
-      </c>
-    </row>
+    <row r="118" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>74</v>
-      </c>
-      <c r="B121">
-        <v>-554</v>
-      </c>
-      <c r="C121">
-        <v>-602</v>
+        <v>201</v>
+      </c>
+      <c r="B121" t="s">
+        <v>182</v>
+      </c>
+      <c r="C121" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>75</v>
+      <c r="A122" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="B123">
-        <v>5118</v>
+        <v>3014</v>
       </c>
       <c r="C123">
-        <v>6256</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B124">
-        <v>-261</v>
+        <v>-554</v>
       </c>
       <c r="C124">
-        <v>-326</v>
+        <v>-602</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>78</v>
-      </c>
-      <c r="B125">
-        <v>147</v>
-      </c>
-      <c r="C125">
-        <v>133</v>
+        <v>72</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B126">
-        <v>351</v>
+        <v>5118</v>
       </c>
       <c r="C126">
-        <v>206</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B127">
-        <v>-376</v>
+        <v>-261</v>
       </c>
       <c r="C127">
-        <v>58</v>
+        <v>-326</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B128">
-        <v>-1328</v>
+        <v>147</v>
       </c>
       <c r="C128">
-        <v>-1280</v>
+        <v>133</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B129">
-        <v>37806</v>
+        <v>351</v>
       </c>
       <c r="C129">
-        <v>31916</v>
+        <v>206</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B130">
-        <v>-40045</v>
+        <v>-376</v>
       </c>
       <c r="C130">
-        <v>-35642</v>
+        <v>58</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>84</v>
-      </c>
-      <c r="B131" s="5">
-        <v>-621</v>
-      </c>
-      <c r="C131" s="5">
-        <v>-1071</v>
+        <v>78</v>
+      </c>
+      <c r="B131">
+        <v>-1328</v>
+      </c>
+      <c r="C131">
+        <v>-1280</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>79</v>
+      </c>
       <c r="B132">
-        <v>3251</v>
+        <v>37806</v>
       </c>
       <c r="C132">
-        <v>3347</v>
+        <v>31916</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A133" s="2" t="s">
-        <v>85</v>
+      <c r="A133" t="s">
+        <v>80</v>
+      </c>
+      <c r="B133">
+        <v>-40045</v>
+      </c>
+      <c r="C133">
+        <v>-35642</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>86</v>
-      </c>
-      <c r="B134">
-        <v>-3150</v>
-      </c>
-      <c r="C134">
-        <v>-2838</v>
+        <v>81</v>
+      </c>
+      <c r="B134" s="5">
+        <v>-621</v>
+      </c>
+      <c r="C134" s="5">
+        <v>-1071</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B135">
+        <v>3251</v>
+      </c>
+      <c r="C135">
+        <v>3347</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
+        <v>83</v>
+      </c>
+      <c r="B137">
+        <v>-3150</v>
+      </c>
+      <c r="C137">
+        <v>-2838</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>85</v>
+      </c>
+      <c r="B140">
+        <v>-22</v>
+      </c>
+      <c r="C140">
+        <v>-103</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>86</v>
+      </c>
+      <c r="B142">
+        <v>78</v>
+      </c>
+      <c r="C142">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B143">
+        <v>157</v>
+      </c>
+      <c r="C143">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B137">
-        <v>-22</v>
-      </c>
-      <c r="C137">
-        <v>-103</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
+      <c r="B144" s="5">
+        <v>4522</v>
+      </c>
+      <c r="C144" s="5">
+        <v>3944</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B139">
-        <v>78</v>
-      </c>
-      <c r="C139">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A140" s="2" t="s">
+      <c r="B145" s="6">
+        <v>4679</v>
+      </c>
+      <c r="C145" s="6">
+        <v>4522</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B140">
-        <v>157</v>
-      </c>
-      <c r="C140">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A141" s="2" t="s">
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
         <v>91</v>
       </c>
-      <c r="B141" s="5">
-        <v>4522</v>
-      </c>
-      <c r="C141" s="5">
-        <v>3944</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="2" t="s">
+      <c r="B147">
+        <v>5172</v>
+      </c>
+      <c r="C147">
+        <v>4675</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
         <v>92</v>
       </c>
-      <c r="B142" s="6">
-        <v>4679</v>
-      </c>
-      <c r="C142" s="6">
-        <v>4522</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="2" t="s">
+      <c r="B148">
+        <v>114</v>
+      </c>
+      <c r="C148">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>94</v>
-      </c>
-      <c r="B144">
-        <v>5172</v>
-      </c>
-      <c r="C144">
-        <v>4675</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>95</v>
-      </c>
-      <c r="B145">
-        <v>114</v>
-      </c>
-      <c r="C145">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>96</v>
-      </c>
-      <c r="B146">
+      <c r="B149">
         <v>447</v>
       </c>
-      <c r="C146">
+      <c r="C149">
         <v>417</v>
       </c>
     </row>
@@ -3365,13 +3632,13 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -3466,7 +3733,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B13" s="1">
         <v>576201</v>
@@ -3477,7 +3744,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B14" s="1">
         <v>654853</v>
@@ -3547,24 +3814,24 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B21" s="13">
         <v>1.3</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="13">
         <v>1.28</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B24" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -3576,7 +3843,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B26" s="1">
         <v>21007</v>
@@ -3587,7 +3854,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>242</v>
       </c>
       <c r="B27" s="1">
         <v>-16165</v>
@@ -3598,7 +3865,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B28" s="10">
         <v>-1584</v>
@@ -3617,14 +3884,14 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31" s="1">
         <v>5719</v>
@@ -3635,7 +3902,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" s="10">
         <v>1280</v>
@@ -3654,7 +3921,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B34" s="1">
         <v>-5851</v>
@@ -3665,7 +3932,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B35" s="1">
         <v>26</v>
@@ -3676,7 +3943,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B36" s="10">
         <v>-159</v>
@@ -3695,14 +3962,14 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B39" s="1">
         <v>6828</v>
@@ -3713,7 +3980,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B40" s="10">
         <v>-6828</v>
@@ -3724,15 +3991,15 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -3750,7 +4017,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>243</v>
       </c>
       <c r="B44" s="1">
         <v>-3088</v>
@@ -3761,7 +4028,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B45" s="1">
         <v>-185</v>
@@ -3772,7 +4039,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B46" s="1">
         <v>-105</v>
@@ -3783,7 +4050,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B47" s="10">
         <v>-49</v>
@@ -3794,7 +4061,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B48" s="1">
         <v>3699</v>
@@ -3805,7 +4072,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B49" s="10">
         <v>455</v>
@@ -3816,7 +4083,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B50" s="1">
         <v>3244</v>
@@ -3827,7 +4094,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B51" s="10">
         <v>-3</v>
@@ -3849,7 +4116,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B53" s="10">
         <v>107</v>
@@ -3860,7 +4127,7 @@
     </row>
     <row r="54" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B54" s="11">
         <v>3140</v>
@@ -3872,23 +4139,23 @@
     <row r="55" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B57" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C57" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>100</v>
+        <v>244</v>
       </c>
       <c r="B59" s="1">
         <v>4522</v>
@@ -3899,7 +4166,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B60" s="1">
         <v>100863</v>
@@ -3910,7 +4177,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B61" s="1">
         <v>25477</v>
@@ -3921,7 +4188,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B62" s="1">
         <v>14794</v>
@@ -3932,7 +4199,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B63" s="10">
         <v>8235</v>
@@ -3951,7 +4218,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B65" s="1">
         <v>858</v>
@@ -3962,7 +4229,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B66" s="1">
         <v>6544</v>
@@ -3973,7 +4240,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B67" s="1">
         <v>6827</v>
@@ -3984,7 +4251,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B68" s="1">
         <v>2866</v>
@@ -3995,7 +4262,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B69" s="1">
         <v>1458</v>
@@ -4006,7 +4273,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B70" s="1">
         <v>589</v>
@@ -4017,7 +4284,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B71" s="1">
         <v>277</v>
@@ -4028,7 +4295,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B72" s="1">
         <v>3704</v>
@@ -4039,7 +4306,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B73" s="1">
         <v>2647</v>
@@ -4050,7 +4317,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B74" s="1">
         <v>185</v>
@@ -4061,7 +4328,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B75" s="1">
         <v>958</v>
@@ -4072,7 +4339,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B76" s="10">
         <v>280400</v>
@@ -4099,14 +4366,14 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B80" s="1">
         <v>140310</v>
@@ -4117,7 +4384,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B81" s="1">
         <v>4687</v>
@@ -4128,7 +4395,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B82" s="1">
         <v>628</v>
@@ -4139,7 +4406,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>56</v>
+        <v>245</v>
       </c>
       <c r="B83" s="1">
         <v>807</v>
@@ -4150,7 +4417,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B84" s="1">
         <v>1000</v>
@@ -4161,7 +4428,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B85" s="1">
         <v>2074</v>
@@ -4172,7 +4439,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B86" s="1">
         <v>2028</v>
@@ -4183,7 +4450,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B87" s="1">
         <v>4534</v>
@@ -4194,7 +4461,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B88" s="1">
         <v>227</v>
@@ -4205,7 +4472,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B89" s="1">
         <v>547</v>
@@ -4216,7 +4483,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B90" s="1">
         <v>51934</v>
@@ -4227,7 +4494,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B91" s="10">
         <v>228466</v>
@@ -4238,7 +4505,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B92" s="1">
         <v>437242</v>
@@ -4254,14 +4521,14 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B95" s="1">
         <v>3043</v>
@@ -4272,7 +4539,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B96" s="1">
         <v>10</v>
@@ -4283,21 +4550,21 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B99" s="1">
         <v>7995</v>
@@ -4308,7 +4575,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B100" s="1">
         <v>11758</v>
@@ -4319,7 +4586,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B101" s="1">
         <v>711</v>
@@ -4330,7 +4597,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B102" s="1">
         <v>445</v>
@@ -4352,7 +4619,7 @@
     </row>
     <row r="104" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B104" s="11">
         <v>461204</v>
@@ -4364,22 +4631,22 @@
     <row r="105" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B107" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C107" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D107" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E107" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F107" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G107" t="s">
         <v>10</v>
@@ -4393,7 +4660,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B108" s="15">
         <v>7995</v>
@@ -4405,7 +4672,7 @@
         <v>11456</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F108" s="15">
         <v>19813</v>
@@ -4422,19 +4689,19 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D109" s="15">
         <v>3140</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F109" s="15">
         <v>3140</v>
@@ -4451,16 +4718,16 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E110" s="16">
         <v>782</v>
@@ -4469,7 +4736,7 @@
         <v>782</v>
       </c>
       <c r="G110" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H110" s="16">
         <v>92</v>
@@ -4506,28 +4773,28 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D112" s="15">
         <v>-2838</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F112" s="15">
         <v>-2838</v>
       </c>
       <c r="G112" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H112" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I112" s="15">
         <v>-2838</v>
@@ -4535,28 +4802,28 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C113" s="15">
         <v>12</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F113" s="15">
         <v>12</v>
       </c>
       <c r="G113" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H113" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I113" s="15">
         <v>12</v>
@@ -4564,28 +4831,28 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E114" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F114" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G114" s="16">
         <v>-3</v>
       </c>
       <c r="H114" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I114" s="16">
         <v>-3</v>
@@ -4593,7 +4860,7 @@
     </row>
     <row r="115" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B115" s="17">
         <v>7995</v>
@@ -4623,23 +4890,23 @@
     <row r="116" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B118" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C118" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B120" s="1">
         <v>3699</v>
@@ -4650,7 +4917,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B121" s="1">
         <v>-602</v>
@@ -4661,14 +4928,14 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B123" s="1">
         <v>6256</v>
@@ -4679,7 +4946,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B124" s="1">
         <v>-326</v>
@@ -4690,7 +4957,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B125" s="1">
         <v>133</v>
@@ -4701,7 +4968,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B126" s="1">
         <v>206</v>
@@ -4712,7 +4979,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B127" s="1">
         <v>58</v>
@@ -4723,7 +4990,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B128" s="1">
         <v>-1280</v>
@@ -4734,7 +5001,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B129" s="1">
         <v>31916</v>
@@ -4745,7 +5012,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B130" s="1">
         <v>-35642</v>
@@ -4756,7 +5023,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B131" s="10">
         <v>-1071</v>
@@ -4775,14 +5042,14 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B134" s="1">
         <v>-2838</v>
@@ -4797,14 +5064,14 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B137" s="1">
         <v>-103</v>
@@ -4815,10 +5082,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C138" s="10">
         <v>-560</v>
@@ -4834,7 +5101,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B140" s="1">
         <v>172</v>
@@ -4845,7 +5112,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B141" s="1">
         <v>578</v>
@@ -4856,7 +5123,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B142" s="10">
         <v>3944</v>
@@ -4867,7 +5134,7 @@
     </row>
     <row r="143" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B143" s="11">
         <v>4522</v>
@@ -4878,14 +5145,14 @@
     </row>
     <row r="144" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B145" s="1">
         <v>4675</v>
@@ -4896,7 +5163,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B146" s="1">
         <v>112</v>
@@ -4907,7 +5174,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B147" s="1">
         <v>417</v>
@@ -4947,13 +5214,13 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -5052,7 +5319,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B13" s="1">
         <v>499941</v>
@@ -5063,7 +5330,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B14" s="1">
         <v>567652</v>
@@ -5132,20 +5399,32 @@
         <v>22788</v>
       </c>
     </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="B21" s="20">
+        <v>1.28</v>
+      </c>
+      <c r="C21" s="20">
+        <f>'CL 2022 (Original)'!B26</f>
+        <v>1.2</v>
+      </c>
+    </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C24" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -5155,7 +5434,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B26" s="1">
         <v>20188</v>
@@ -5166,7 +5445,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>242</v>
       </c>
       <c r="B27" s="1">
         <v>-15622</v>
@@ -5177,7 +5456,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B28" s="10">
         <v>-1564</v>
@@ -5196,14 +5475,14 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31" s="1">
         <v>4877</v>
@@ -5214,7 +5493,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B32" s="10">
         <v>4267</v>
@@ -5233,7 +5512,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B34" s="1">
         <v>-9032</v>
@@ -5244,7 +5523,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B35" s="1">
         <v>266</v>
@@ -5255,7 +5534,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B36" s="1">
         <v>-178</v>
@@ -5274,14 +5553,14 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B39" s="1">
         <v>4808</v>
@@ -5292,7 +5571,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B40" s="10">
         <v>-4808</v>
@@ -5303,15 +5582,15 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B41" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -5329,7 +5608,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>25</v>
+        <v>243</v>
       </c>
       <c r="B44" s="1">
         <v>-2635</v>
@@ -5340,7 +5619,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B45" s="1">
         <v>-160</v>
@@ -5351,7 +5630,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B46" s="1">
         <v>-105</v>
@@ -5362,18 +5641,18 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B47" s="10">
         <v>-126</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B48" s="1">
         <v>2339</v>
@@ -5384,7 +5663,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B49" s="1">
         <v>-80</v>
@@ -5395,7 +5674,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B50" s="1">
         <v>2419</v>
@@ -5406,7 +5685,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B51" s="10">
         <v>1</v>
@@ -5428,7 +5707,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B53" s="10">
         <v>24</v>
@@ -5439,7 +5718,7 @@
     </row>
     <row r="54" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B54" s="11">
         <v>2394</v>
@@ -5451,34 +5730,34 @@
     <row r="55" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C57" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D57" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C58" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D58" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>35</v>
+        <v>244</v>
       </c>
       <c r="B60" s="1">
         <v>3944</v>
@@ -5492,7 +5771,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B61" s="1">
         <v>91904</v>
@@ -5506,7 +5785,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B62" s="1">
         <v>24449</v>
@@ -5520,7 +5799,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B63" s="1">
         <v>13589</v>
@@ -5534,7 +5813,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B64" s="10">
         <v>7849</v>
@@ -5559,7 +5838,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B67" s="1">
         <v>902</v>
@@ -5573,7 +5852,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B68" s="1">
         <v>6546</v>
@@ -5587,7 +5866,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B69" s="1">
         <v>7072</v>
@@ -5601,7 +5880,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B70" s="1">
         <v>2484</v>
@@ -5615,7 +5894,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B71" s="1">
         <v>1486</v>
@@ -5629,7 +5908,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B72" s="1">
         <v>544</v>
@@ -5643,7 +5922,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B73" s="1">
         <v>252</v>
@@ -5657,7 +5936,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B74" s="1">
         <v>3117</v>
@@ -5671,7 +5950,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B75" s="1">
         <v>2344</v>
@@ -5685,7 +5964,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B76" s="1">
         <v>144</v>
@@ -5699,7 +5978,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B77" s="1">
         <v>804</v>
@@ -5713,7 +5992,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B78" s="10">
         <v>243186</v>
@@ -5744,7 +6023,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -5752,7 +6031,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B82" s="1">
         <v>129689</v>
@@ -5766,7 +6045,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B83" s="1">
         <v>4953</v>
@@ -5780,7 +6059,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B84" s="1">
         <v>475</v>
@@ -5794,7 +6073,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>56</v>
+        <v>245</v>
       </c>
       <c r="B85" s="1">
         <v>748</v>
@@ -5808,7 +6087,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B86" s="1">
         <v>1000</v>
@@ -5822,7 +6101,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B87" s="1">
         <v>1208</v>
@@ -5836,7 +6115,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B88" s="1">
         <v>1672</v>
@@ -5850,7 +6129,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B89" s="1">
         <v>4401</v>
@@ -5864,7 +6143,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B90" s="1">
         <v>97</v>
@@ -5878,7 +6157,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B91" s="1">
         <v>514</v>
@@ -5892,7 +6171,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B92" s="1">
         <v>47410</v>
@@ -5906,7 +6185,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B93" s="10">
         <v>195776</v>
@@ -5920,7 +6199,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B94" s="1">
         <v>387943</v>
@@ -5934,7 +6213,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -5942,7 +6221,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B96" s="1">
         <v>2844</v>
@@ -5956,7 +6235,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B97" s="1">
         <v>16</v>
@@ -5970,7 +6249,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -5978,7 +6257,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -5986,7 +6265,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B100" s="1">
         <v>7995</v>
@@ -6000,7 +6279,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B101" s="1">
         <v>11456</v>
@@ -6014,7 +6293,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B102" s="1">
         <v>-71</v>
@@ -6028,7 +6307,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B103" s="10">
         <v>433</v>
@@ -6056,7 +6335,7 @@
     </row>
     <row r="105" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B105" s="11">
         <v>410616</v>
@@ -6071,22 +6350,22 @@
     <row r="106" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B108" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C108" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D108" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E108" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F108" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G108" t="s">
         <v>10</v>
@@ -6100,7 +6379,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B109" s="15">
         <v>7884</v>
@@ -6112,7 +6391,7 @@
         <v>12054</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F109" s="15">
         <v>20004</v>
@@ -6129,28 +6408,28 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D110" s="16">
         <v>-31</v>
       </c>
       <c r="E110" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F110" s="16">
         <v>-31</v>
       </c>
       <c r="G110" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H110" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I110" s="16">
         <v>-31</v>
@@ -6158,7 +6437,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B111" s="15">
         <v>7884</v>
@@ -6190,16 +6469,16 @@
         <v>3</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D112" s="15">
         <v>2394</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F112" s="15">
         <v>2394</v>
@@ -6216,16 +6495,16 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E113" s="16">
         <v>288</v>
@@ -6234,7 +6513,7 @@
         <v>288</v>
       </c>
       <c r="G113" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H113" s="16">
         <v>87</v>
@@ -6271,28 +6550,28 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D115" s="15">
         <v>-2934</v>
       </c>
       <c r="E115" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F115" s="15">
         <v>-2934</v>
       </c>
       <c r="G115" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H115" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I115" s="15">
         <v>-2934</v>
@@ -6300,28 +6579,28 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C116" s="15">
         <v>8</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F116" s="15">
         <v>8</v>
       </c>
       <c r="G116" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H116" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I116" s="15">
         <v>8</v>
@@ -6329,28 +6608,28 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B117" s="15">
         <v>111</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E117" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F117" s="15">
         <v>111</v>
       </c>
       <c r="G117" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H117" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I117" s="15">
         <v>111</v>
@@ -6358,19 +6637,19 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D118" s="16">
         <v>-27</v>
       </c>
       <c r="E118" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F118" s="16">
         <v>-27</v>
@@ -6379,7 +6658,7 @@
         <v>-36</v>
       </c>
       <c r="H118" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I118" s="16">
         <v>-63</v>
@@ -6387,7 +6666,7 @@
     </row>
     <row r="119" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B119" s="17">
         <v>7995</v>
@@ -6399,7 +6678,7 @@
         <v>11456</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F119" s="17">
         <v>19813</v>
@@ -6417,28 +6696,28 @@
     <row r="120" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
     <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B122" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C122" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C123" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>113</v>
+      <c r="A124" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B125">
         <v>2339</v>
@@ -6449,7 +6728,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B126">
         <v>-360</v>
@@ -6460,12 +6739,12 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B128">
         <v>9242</v>
@@ -6476,7 +6755,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B129">
         <v>289</v>
@@ -6487,7 +6766,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B130">
         <v>206</v>
@@ -6498,7 +6777,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B131">
         <v>100</v>
@@ -6509,7 +6788,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B132">
         <v>-439</v>
@@ -6520,7 +6799,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B133">
         <v>-4267</v>
@@ -6531,7 +6810,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B134">
         <v>24224</v>
@@ -6542,7 +6821,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B135">
         <v>-27299</v>
@@ -6553,7 +6832,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B136" s="5">
         <v>-199</v>
@@ -6571,13 +6850,13 @@
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>85</v>
+      <c r="A138" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B139">
         <v>-2934</v>
@@ -6587,13 +6866,13 @@
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>87</v>
+      <c r="A141" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B142">
         <v>-185</v>
@@ -6604,7 +6883,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B143">
         <v>-560</v>
@@ -6623,7 +6902,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B145">
         <v>26</v>
@@ -6634,7 +6913,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B146">
         <v>183</v>
@@ -6645,7 +6924,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B147" s="5">
         <v>3761</v>
@@ -6656,7 +6935,7 @@
     </row>
     <row r="148" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B148" s="18">
         <v>3944</v>
@@ -6667,12 +6946,12 @@
     </row>
     <row r="149" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B150">
         <v>4210</v>
@@ -6683,7 +6962,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B151">
         <v>112</v>
@@ -6694,7 +6973,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B152">
         <v>400</v>
@@ -6741,18 +7020,18 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -6764,7 +7043,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B5" s="1">
         <v>1809</v>
@@ -6775,7 +7054,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B6" s="1">
         <v>1625</v>
@@ -6786,7 +7065,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B7" s="10">
         <v>184</v>
@@ -6824,7 +7103,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B11" s="1">
         <v>54322</v>
@@ -6835,7 +7114,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B12" s="1">
         <v>98025</v>
@@ -6857,7 +7136,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B14" s="10">
         <v>48246</v>
@@ -6879,7 +7158,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B16" s="10">
         <v>65410</v>
@@ -6890,7 +7169,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B17" s="1">
         <v>459392</v>
@@ -6901,7 +7180,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B18" s="1">
         <v>37689</v>
@@ -6912,7 +7191,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B19" s="10">
         <v>497081</v>
@@ -6972,7 +7251,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B25" s="1">
         <v>9268</v>
@@ -6983,7 +7262,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B26" s="13">
         <v>1.2</v>
@@ -6994,28 +7273,28 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B32" s="1">
         <v>58060</v>
@@ -7026,7 +7305,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B33" s="10">
         <v>-3738</v>
@@ -7037,7 +7316,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B34" s="12">
         <v>54322</v>
@@ -7048,14 +7327,14 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B36" s="1">
         <v>-4898</v>
@@ -7066,7 +7345,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B37" s="10">
         <v>-16011</v>
@@ -7077,7 +7356,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B38" s="1">
         <v>-11113</v>
@@ -7107,21 +7386,21 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B43" s="1">
         <v>48611</v>
@@ -7132,7 +7411,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B44" s="10">
         <v>-2537</v>
@@ -7143,7 +7422,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B45" s="1">
         <v>46074</v>
@@ -7154,14 +7433,14 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B47" s="1">
         <v>-12410</v>
@@ -7172,7 +7451,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B48" s="10">
         <v>1169</v>
@@ -7183,7 +7462,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B49" s="1">
         <v>-11241</v>
@@ -7194,7 +7473,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B50" s="10">
         <v>2172</v>
@@ -7205,7 +7484,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B51" s="1">
         <v>37005</v>
@@ -7216,7 +7495,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B52" s="1">
         <v>2148</v>
@@ -7227,7 +7506,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B53" s="1">
         <v>3249</v>
@@ -7238,7 +7517,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B54" s="1">
         <v>474</v>
@@ -7249,7 +7528,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B55" s="1">
         <v>109</v>
@@ -7260,7 +7539,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B56" s="10">
         <v>168</v>
@@ -7271,7 +7550,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B57" s="1">
         <v>3381</v>
@@ -7282,7 +7561,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B58" s="10">
         <v>199</v>
@@ -7293,7 +7572,7 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B59" s="1">
         <v>3182</v>
@@ -7304,7 +7583,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B60" s="10">
         <v>3</v>
@@ -7326,7 +7605,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B62" s="10">
         <v>184</v>
@@ -7337,7 +7616,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B63" s="12">
         <v>2995</v>
@@ -7348,23 +7627,23 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B66" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C66" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B68" s="1">
         <v>3761</v>
@@ -7375,7 +7654,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B69" s="1">
         <v>87814</v>
@@ -7386,7 +7665,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B70" s="1">
         <v>24012</v>
@@ -7397,7 +7676,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B71" s="1">
         <v>12663</v>
@@ -7408,7 +7687,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B72" s="1">
         <v>8315</v>
@@ -7419,7 +7698,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B73" s="10">
         <v>3660</v>
@@ -7438,7 +7717,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B75" s="1">
         <v>7041</v>
@@ -7449,7 +7728,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B76" s="1">
         <v>6877</v>
@@ -7460,7 +7739,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B77" s="1">
         <v>6372</v>
@@ -7471,7 +7750,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B78" s="1">
         <v>2450</v>
@@ -7482,7 +7761,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B79" s="1">
         <v>1120</v>
@@ -7493,7 +7772,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B80" s="1">
         <v>532</v>
@@ -7504,7 +7783,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B81" s="1">
         <v>257</v>
@@ -7515,7 +7794,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B82" s="1">
         <v>2091</v>
@@ -7526,7 +7805,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B83" s="1">
         <v>4825</v>
@@ -7537,7 +7816,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B84" s="1">
         <v>254</v>
@@ -7548,7 +7827,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B85" s="1">
         <v>315</v>
@@ -7559,7 +7838,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B86" s="1">
         <v>221623</v>
@@ -7586,14 +7865,14 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B90" s="1">
         <v>134389</v>
@@ -7604,7 +7883,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B91" s="1">
         <v>1568</v>
@@ -7615,7 +7894,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B92" s="1">
         <v>747</v>
@@ -7626,7 +7905,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B93" s="1">
         <v>1000</v>
@@ -7637,7 +7916,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B94" s="1">
         <v>1646</v>
@@ -7648,7 +7927,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B95" s="1">
         <v>1575</v>
@@ -7659,7 +7938,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B96" s="1">
         <v>2047</v>
@@ -7670,7 +7949,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B97" s="1">
         <v>2935</v>
@@ -7681,7 +7960,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B98" s="1">
         <v>50</v>
@@ -7692,7 +7971,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B99" s="1">
         <v>892</v>
@@ -7703,7 +7982,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B100" s="10">
         <v>221623</v>
@@ -7714,7 +7993,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B101" s="12">
         <v>368472</v>
@@ -7725,14 +8004,14 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B103" s="1">
         <v>3147</v>
@@ -7743,7 +8022,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B104" s="1">
         <v>51</v>
@@ -7761,14 +8040,14 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B107" s="1">
         <v>7884</v>
@@ -7779,7 +8058,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B108" s="1">
         <v>14258</v>
@@ -7790,7 +8069,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B109" s="1">
         <v>-255</v>
@@ -7801,7 +8080,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B110" s="10">
         <v>425</v>
@@ -7823,7 +8102,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B112" s="12">
         <v>393982</v>
@@ -7834,22 +8113,22 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
+        <v>234</v>
+      </c>
+      <c r="B115" t="s">
+        <v>65</v>
+      </c>
+      <c r="C115" t="s">
+        <v>69</v>
+      </c>
+      <c r="D115" t="s">
+        <v>67</v>
+      </c>
+      <c r="E115" t="s">
+        <v>238</v>
+      </c>
+      <c r="F115" t="s">
         <v>239</v>
-      </c>
-      <c r="B115" t="s">
-        <v>68</v>
-      </c>
-      <c r="C115" t="s">
-        <v>72</v>
-      </c>
-      <c r="D115" t="s">
-        <v>70</v>
-      </c>
-      <c r="E115" t="s">
-        <v>243</v>
-      </c>
-      <c r="F115" t="s">
-        <v>244</v>
       </c>
       <c r="G115" t="s">
         <v>10</v>
@@ -7863,7 +8142,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B116" s="15">
         <v>7884</v>
@@ -7921,7 +8200,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B118" s="16" t="s">
         <v>11</v>
@@ -7976,7 +8255,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B120" s="15" t="s">
         <v>11</v>
@@ -8005,7 +8284,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B121" s="15" t="s">
         <v>11</v>
@@ -8034,7 +8313,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B122" s="15" t="s">
         <v>11</v>
@@ -8063,7 +8342,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B123" s="15" t="s">
         <v>11</v>
@@ -8092,7 +8371,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B124" s="15">
         <v>7884</v>
@@ -8121,25 +8400,25 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B127" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C127" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B129" s="1">
         <v>3381</v>
@@ -8150,7 +8429,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B130" s="1">
         <v>-326</v>
@@ -8161,14 +8440,14 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B132" s="1">
         <v>-12992</v>
@@ -8179,7 +8458,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B133" s="1">
         <v>-491</v>
@@ -8190,7 +8469,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B134" s="1">
         <v>-354</v>
@@ -8201,7 +8480,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B135" s="1">
         <v>1972</v>
@@ -8212,7 +8491,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B136" s="1">
         <v>16011</v>
@@ -8223,7 +8502,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B137" s="10">
         <v>-860</v>
@@ -8242,14 +8521,14 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B140" s="1">
         <v>-1770</v>
@@ -8264,14 +8543,14 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B143" s="1">
         <v>15714</v>
@@ -8282,7 +8561,7 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B144" s="1">
         <v>2398</v>
@@ -8293,7 +8572,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B145" s="1">
         <v>4129</v>
@@ -8304,7 +8583,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B146" s="1">
         <v>55</v>
@@ -8315,7 +8594,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B147" s="1">
         <v>-156</v>
@@ -8326,7 +8605,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B148" s="1">
         <v>-6</v>
@@ -8337,7 +8616,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B149" s="1">
         <v>-17493</v>
@@ -8348,7 +8627,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B150" s="1">
         <v>-4018</v>
@@ -8359,7 +8638,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B151" s="1">
         <v>-3980</v>
@@ -8370,7 +8649,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B152" s="10">
         <v>-710</v>
@@ -8389,7 +8668,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B154" s="1">
         <v>-14</v>
@@ -8400,7 +8679,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B155" s="1">
         <v>490</v>
@@ -8411,7 +8690,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B156" s="10">
         <v>3271</v>
@@ -8422,7 +8701,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B157" s="12">
         <v>3761</v>
@@ -8433,14 +8712,14 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B159" s="1">
         <v>3661</v>
@@ -8451,7 +8730,7 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B160" s="1">
         <v>116</v>
@@ -8462,7 +8741,7 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B161" s="1">
         <v>352</v>
@@ -8485,68 +8764,375 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB2D2CB0-3C74-48F6-A0FC-1C79BE7E1C5C}">
-  <dimension ref="A2:F5"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" customWidth="1"/>
+    <col min="5" max="5" width="16.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="1" cm="1">
+        <f t="array" ref="B2">_xlfn.XLOOKUP(A2,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2022]],"Not Found",0)</f>
+        <v>19424</v>
+      </c>
+      <c r="C2" s="1" cm="1">
+        <f t="array" ref="C2">_xlfn.XLOOKUP(A2,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2023]],"Not Found", 0)</f>
+        <v>20188</v>
+      </c>
+      <c r="D2" s="1" cm="1">
+        <f t="array" ref="D2">_xlfn.XLOOKUP(A2,CL2024_Consolidated_Statement_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2024_Consolidated_Statement_Of_Earnings[[#All],[2024]],"Not Found", 0)</f>
+        <v>21007</v>
+      </c>
+      <c r="E2" s="1">
+        <f>_xlfn.XLOOKUP(A2,CL2025_Consolidated_Statements_Of_Earnings[Consolidated Statements Of Earnings (in Canadian $ Million)],CL2025_Consolidated_Statements_Of_Earnings[2025],"Not Found",0)</f>
+        <v>22131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B3" s="1" cm="1">
+        <f t="array" ref="B3">_xlfn.XLOOKUP(A3,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2022]],"Not Found",0)</f>
+        <v>-15110</v>
+      </c>
+      <c r="C3" s="1" cm="1">
+        <f t="array" ref="C3">_xlfn.XLOOKUP(A3,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2023]],"Not Found",0)</f>
+        <v>-15622</v>
+      </c>
+      <c r="D3" s="1">
+        <f>_xlfn.XLOOKUP(A3,CL2024_Consolidated_Statement_Of_Earnings[Consolidated Statements of Earnings (in Canadian $ millions)],CL2024_Consolidated_Statement_Of_Earnings[2024],"Not Found",0)</f>
+        <v>-16165</v>
+      </c>
+      <c r="E3" s="1">
+        <f>_xlfn.XLOOKUP(A3,CL2025_Consolidated_Statements_Of_Earnings[Consolidated Statements Of Earnings (in Canadian $ Million)],CL2025_Consolidated_Statements_Of_Earnings[2025],"Not Found",0)</f>
+        <v>-17002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1">
+        <f>SUM('CL 2023 (Original)'!C26:C28)</f>
+        <v>2766</v>
+      </c>
+      <c r="C4" s="1">
+        <f>SUM('CL 2023 (Original)'!B26:B28)</f>
+        <v>3002</v>
+      </c>
+      <c r="D4" s="1">
+        <f>SUM('CL 2024 (Original)'!B26:B28)</f>
+        <v>3258</v>
+      </c>
+      <c r="E4" s="1">
+        <f>SUM('CL 2025 (Original)'!B26:B28)</f>
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" s="1" cm="1">
+        <f t="array" ref="B5">_xlfn.XLOOKUP(A5,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2022]],"Not Found",0)</f>
+        <v>-2221</v>
+      </c>
+      <c r="C5" s="1" cm="1">
+        <f t="array" ref="C5">_xlfn.XLOOKUP(A5,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2023]],"Not Found",0)</f>
+        <v>-2635</v>
+      </c>
+      <c r="D5" s="1" cm="1">
+        <f t="array" ref="D5">_xlfn.XLOOKUP(A5,CL2024_Consolidated_Statement_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2024_Consolidated_Statement_Of_Earnings[[#All],[2024]],"Not Found",0)</f>
+        <v>-3088</v>
+      </c>
+      <c r="E5" s="1" cm="1">
+        <f t="array" ref="E5">_xlfn.XLOOKUP(A5,CL2025_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements Of Earnings (in Canadian $ Million)]],CL2025_Consolidated_Statements_Of_Earnings[[#All],[2025]],"Not Found",0)</f>
+        <v>-3408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" cm="1">
+        <f t="array" ref="B6">_xlfn.XLOOKUP(A6,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2022]],"Not Found",0)</f>
+        <v>3286</v>
+      </c>
+      <c r="C6" s="1" cm="1">
+        <f t="array" ref="C6">_xlfn.XLOOKUP(A6,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2023]],"Not Found",0)</f>
+        <v>2418</v>
+      </c>
+      <c r="D6" s="1" cm="1">
+        <f t="array" ref="D6">_xlfn.XLOOKUP(A6,CL2024_Consolidated_Statement_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2024_Consolidated_Statement_Of_Earnings[[#All],[2024]],"Not Found",0)</f>
+        <v>3247</v>
+      </c>
+      <c r="E6" s="1" cm="1">
+        <f t="array" ref="E6">_xlfn.XLOOKUP(A6,CL2025_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements Of Earnings (in Canadian $ Million)]],CL2025_Consolidated_Statements_Of_Earnings[[#All],[2025]],"Not Found",0)</f>
+        <v>2766</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" cm="1">
+        <f t="array" ref="B7">_xlfn.XLOOKUP(A7,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2022]],"Not Found", 0)</f>
+        <v>378654</v>
+      </c>
+      <c r="C7" s="1" cm="1">
+        <f t="array" ref="C7">_xlfn.XLOOKUP(A7,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2023]],"Not Found",0)</f>
+        <v>410616</v>
+      </c>
+      <c r="D7" s="1" cm="1">
+        <f t="array" ref="D7">_xlfn.XLOOKUP(A7,CL2024_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ millions)]],CL2024_Consolidated_Balance_Sheet[[#All],[2024]],"Not Found",0)</f>
+        <v>461204</v>
+      </c>
+      <c r="E7" s="1" cm="1">
+        <f t="array" ref="E7">_xlfn.XLOOKUP(A7,CL2025_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ Million)]],CL2025_Consolidated_Balance_Sheet[[#All],[2025]],"Not Found",0)</f>
+        <v>505652</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="1" cm="1">
+        <f t="array" ref="B8">_xlfn.XLOOKUP(A8,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2022]],"Not Found",0)</f>
+        <v>355866</v>
+      </c>
+      <c r="C8" s="1" cm="1">
+        <f t="array" ref="C8">_xlfn.XLOOKUP(A8,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2023]],"Not Found",0)</f>
+        <v>387943</v>
+      </c>
+      <c r="D8" s="1" cm="1">
+        <f t="array" ref="D8">_xlfn.XLOOKUP(A8,CL2024_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ millions)]],CL2024_Consolidated_Balance_Sheet[[#All],[2024]],"Not Found",0)</f>
+        <v>437242</v>
+      </c>
+      <c r="E8" s="1" cm="1">
+        <f t="array" ref="E8">_xlfn.XLOOKUP(A8,CL2025_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ Million)]],CL2025_Consolidated_Balance_Sheet[[#All],[2025]],"Not Found",0)</f>
+        <v>481632</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1" cm="1">
+        <f t="array" ref="B9">_xlfn.XLOOKUP(A9,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</f>
+        <v>20004</v>
+      </c>
+      <c r="C9" s="1" cm="1">
+        <f t="array" ref="C9">_xlfn.XLOOKUP(A9,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</f>
+        <v>19813</v>
+      </c>
+      <c r="D9" s="1" cm="1">
+        <f t="array" ref="D9">_xlfn.XLOOKUP(A9,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</f>
+        <v>20909</v>
+      </c>
+      <c r="E9" s="1" cm="1">
+        <f t="array" ref="E9">_xlfn.XLOOKUP(A9,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</f>
+        <v>20938</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>244</v>
+      </c>
+      <c r="B10" s="1" cm="1">
+        <f t="array" ref="B10">_xlfn.XLOOKUP(A10,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2022]],"Not Found",0)</f>
+        <v>3761</v>
+      </c>
+      <c r="C10" s="1" cm="1">
+        <f t="array" ref="C10">_xlfn.XLOOKUP(A10,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2023]],"Not Found",0)</f>
+        <v>3944</v>
+      </c>
+      <c r="D10" s="1" cm="1">
+        <f t="array" ref="D10">_xlfn.XLOOKUP(A10,CL2024_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ millions)]],CL2024_Consolidated_Balance_Sheet[[#All],[2024]],"Not Found",0)</f>
+        <v>4522</v>
+      </c>
+      <c r="E10" s="1" cm="1">
+        <f t="array" ref="E10">_xlfn.XLOOKUP(A10,CL2025_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ Million)]],CL2025_Consolidated_Balance_Sheet[[#All],[2025]],"Not Found",0)</f>
+        <v>4679</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>245</v>
       </c>
-      <c r="B2">
-        <v>2021</v>
-      </c>
-      <c r="C2">
-        <v>2022</v>
-      </c>
-      <c r="D2">
-        <v>2023</v>
-      </c>
-      <c r="E2">
-        <v>2024</v>
-      </c>
-      <c r="F2">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B11" s="1" cm="1">
+        <f t="array" ref="B11">_xlfn.XLOOKUP(A11,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2022]],"Not Found",0)</f>
+        <v>747</v>
+      </c>
+      <c r="C11" s="1" cm="1">
+        <f t="array" ref="C11">_xlfn.XLOOKUP(A11,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2023]],"Not Found",0)</f>
+        <v>748</v>
+      </c>
+      <c r="D11" s="1" cm="1">
+        <f t="array" ref="D11">_xlfn.XLOOKUP(A11,CL2024_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ millions)]],CL2024_Consolidated_Balance_Sheet[[#All],[2024]],"Not Found",0)</f>
+        <v>807</v>
+      </c>
+      <c r="E11" s="1" cm="1">
+        <f t="array" ref="E11">_xlfn.XLOOKUP(A11,CL2025_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ Million)]],CL2025_Consolidated_Balance_Sheet[[#All],[2025]],"Not Found",0)</f>
+        <v>827</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>246</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" cm="1">
-        <f t="array" ref="C3">_xlfn.XLOOKUP(A3,Table010__Page_10_1[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],Table010__Page_10_1[[#All],[2022]],"Not Found",0)</f>
-        <v>19424</v>
-      </c>
-      <c r="D3" s="1" cm="1">
-        <f t="array" ref="D3">_xlfn.XLOOKUP(A3,Table010__Page_10_1[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],Table010__Page_10_1[[#All],[2023]],"Not Found", 0)</f>
-        <v>20188</v>
-      </c>
-      <c r="E3" s="1" cm="1">
-        <f t="array" ref="E3">_xlfn.XLOOKUP(A3,Table010__Page_10[[#All],[Consolidated Satatements of Earnings (in Canadian $ millions)]],Table010__Page_10[[#All],[2024]],"Not Found", 0)</f>
-        <v>21007</v>
-      </c>
-      <c r="F3" s="1">
-        <f>_xlfn.XLOOKUP(A3,Table010__Page_9[Consolidated Statements Of Earnings (in Canadian $ Million)],Table010__Page_9[2025],"Not Found",0)</f>
-        <v>22131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>248</v>
+      <c r="B12" s="1">
+        <f>'CL 2023 (Original)'!C137</f>
+        <v>2343</v>
+      </c>
+      <c r="C12" s="1">
+        <f>'CL 2023 (Original)'!B137</f>
+        <v>3836</v>
+      </c>
+      <c r="D12" s="1">
+        <f>'CL 2024 (Original)'!B132</f>
+        <v>3347</v>
+      </c>
+      <c r="E12" s="1">
+        <f>'CL 2025 (Original)'!B135</f>
+        <v>3251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" cm="1">
+        <f t="array" ref="B13">_xlfn.XLOOKUP(A13,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</f>
+        <v>12496</v>
+      </c>
+      <c r="C13" s="1" cm="1">
+        <f t="array" ref="C13">_xlfn.XLOOKUP(A13,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</f>
+        <v>12458</v>
+      </c>
+      <c r="D13" s="1" cm="1">
+        <f t="array" ref="D13">_xlfn.XLOOKUP(A13,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</f>
+        <v>13243</v>
+      </c>
+      <c r="E13" s="1" cm="1">
+        <f t="array" ref="E13">_xlfn.XLOOKUP(A13,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</f>
+        <v>13494</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" cm="1">
+        <f t="array" ref="B14">_xlfn.XLOOKUP(A14,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</f>
+        <v>20004</v>
+      </c>
+      <c r="C14" s="1" cm="1">
+        <f t="array" ref="C14">_xlfn.XLOOKUP(A14,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</f>
+        <v>19813</v>
+      </c>
+      <c r="D14" s="1" cm="1">
+        <f t="array" ref="D14">_xlfn.XLOOKUP(A14,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</f>
+        <v>20909</v>
+      </c>
+      <c r="E14" s="1" cm="1">
+        <f t="array" ref="E14">_xlfn.XLOOKUP(A14,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</f>
+        <v>20938</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" cm="1">
+        <f t="array" ref="B15">_xlfn.XLOOKUP(A15,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</f>
+        <v>22788</v>
+      </c>
+      <c r="C15" s="1" cm="1">
+        <f t="array" ref="C15">_xlfn.XLOOKUP(A15,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</f>
+        <v>22673</v>
+      </c>
+      <c r="D15" s="1" cm="1">
+        <f t="array" ref="D15">_xlfn.XLOOKUP(A15,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</f>
+        <v>23962</v>
+      </c>
+      <c r="E15" s="1" cm="1">
+        <f t="array" ref="E15">_xlfn.XLOOKUP(A15,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</f>
+        <v>24020</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="1" cm="1">
+        <f t="array" ref="B16">_xlfn.XLOOKUP(A16,CL2023_Consolidated_Statements_Of_Cash_Flows[[#All],[Consolidated Statements of Cash Flows (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Cash_Flows[[#All],[2022]],"Not Found",0)</f>
+        <v>-1770</v>
+      </c>
+      <c r="C16" s="1" cm="1">
+        <f t="array" ref="C16">_xlfn.XLOOKUP(A16,CL2023_Consolidated_Statements_Of_Cash_Flows[[#All],[Consolidated Statements of Cash Flows (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Cash_Flows[[#All],[2023]],"Not Found",0)</f>
+        <v>-2934</v>
+      </c>
+      <c r="D16" s="1" cm="1">
+        <f t="array" ref="D16">_xlfn.XLOOKUP(A16,CL2024_Consolidated_Statements_Of_Cash_Flow[[#All],[Consolidated Statements of Cash Flow  (in Canadian $ millions)]],CL2024_Consolidated_Statements_Of_Cash_Flow[[#All],[2024]],"Not Found",0)</f>
+        <v>-2838</v>
+      </c>
+      <c r="E16" s="1" cm="1">
+        <f t="array" ref="E16">_xlfn.XLOOKUP(A16,CL2025_Consolidated_Statements_Of_Cash_Flow[[#All],[Consolidated Statements of Cash Flow]],CL2025_Consolidated_Statements_Of_Cash_Flow[[#All],[2025]],"Not Found",0)</f>
+        <v>-3150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" s="24" cm="1">
+        <f t="array" ref="B17">_xlfn.XLOOKUP(A17,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</f>
+        <v>1.2</v>
+      </c>
+      <c r="C17" s="24" cm="1">
+        <f t="array" ref="C17">_xlfn.XLOOKUP(A17,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</f>
+        <v>1.28</v>
+      </c>
+      <c r="D17" s="24" cm="1">
+        <f t="array" ref="D17">_xlfn.XLOOKUP(A17,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</f>
+        <v>1.3</v>
+      </c>
+      <c r="E17" s="24" cm="1">
+        <f t="array" ref="E17">_xlfn.XLOOKUP(A17,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</f>
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/Canada Life Annual Report Project.xlsx
+++ b/Canada Life Annual Report Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GMU058\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00970483-80E7-419D-9B3C-93B76A3434B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB2540C-51E6-44C3-8B2B-0BDB7D047591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{3CB541B1-AEC2-4997-AFCF-80587D906177}"/>
   </bookViews>
@@ -54,7 +54,7 @@
     <author>Han, Eugene</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{2F1AC64B-51DF-41DB-A3BA-D2F7A4C31212}">
+    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{2F1AC64B-51DF-41DB-A3BA-D2F7A4C31212}">
       <text>
         <r>
           <rPr>
@@ -68,7 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{87F8FDE5-D62D-4E7F-A4BA-16BB35468722}">
+    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{87F8FDE5-D62D-4E7F-A4BA-16BB35468722}">
       <text>
         <r>
           <rPr>
@@ -82,7 +82,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{30CFD3FD-CCDC-4029-927A-6AAD5D42226B}">
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{30CFD3FD-CCDC-4029-927A-6AAD5D42226B}">
       <text>
         <r>
           <rPr>
@@ -99,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{52185BAC-91F8-4007-BE14-C8BC8372536E}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{52185BAC-91F8-4007-BE14-C8BC8372536E}">
       <text>
         <r>
           <rPr>
@@ -133,7 +133,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{1659F652-C2DB-4293-8464-90B77BE23056}">
+    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{1659F652-C2DB-4293-8464-90B77BE23056}">
       <text>
         <r>
           <rPr>
@@ -146,7 +146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0" shapeId="0" xr:uid="{BC8F9592-D229-4214-BF29-23C47D38A133}">
+    <comment ref="A13" authorId="0" shapeId="0" xr:uid="{BC8F9592-D229-4214-BF29-23C47D38A133}">
       <text>
         <r>
           <rPr>
@@ -161,7 +161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{49202555-5642-4FDD-9E1A-C531441A6D5B}">
+    <comment ref="A14" authorId="0" shapeId="0" xr:uid="{49202555-5642-4FDD-9E1A-C531441A6D5B}">
       <text>
         <r>
           <rPr>
@@ -195,7 +195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A13" authorId="0" shapeId="0" xr:uid="{6E6F5986-C5FF-4C2E-90CF-37E0CC3DF7DD}">
+    <comment ref="A15" authorId="0" shapeId="0" xr:uid="{6E6F5986-C5FF-4C2E-90CF-37E0CC3DF7DD}">
       <text>
         <r>
           <rPr>
@@ -226,7 +226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A17" authorId="0" shapeId="0" xr:uid="{07E7F086-D1ED-4C08-B9ED-98813F81BF49}">
+    <comment ref="A18" authorId="0" shapeId="0" xr:uid="{07E7F086-D1ED-4C08-B9ED-98813F81BF49}">
       <text>
         <r>
           <rPr>
@@ -247,6 +247,988 @@
           <t xml:space="preserve">
 A higher ratio means the insurer has a larger cushion against adverse events such as: Market crashes, Interest rate shocks, Higher-than-expected death claims, Disability claims, Longevity risk, Credit losses, Operational failures.
 Why investors care - A high LICAT ratio means: Greater ability to withstand recessions, Better claim-paying ability, Lower insolvency risk, More flexibility to pay dividends, More room for growth and acquisitions, For insurers, a LICAT of around 120%-130%+ is generally considered strong.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A22" authorId="0" shapeId="0" xr:uid="{43EF8877-12E6-4E7B-8394-96CDDB4FEB04}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Profitability ratio
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Net profit margin = Net earnings/Insurance revenue</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Net earnings generated from each dollar of insurance revenue.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A23" authorId="0" shapeId="0" xr:uid="{E1455F4C-C318-46D6-A7A9-6F48D9A79412}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Profitability ratio
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ROA = Net earnings/Average total assets
+Average total assets = (Beginning assets + Ending assets)/2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+How efficiently assets generate earnings</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0" shapeId="0" xr:uid="{41886427-F51F-427E-99B7-CE9A641D56BD}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>For the average total assets calculation, the number is found by online since the IFRS 17 started in 2023, which doesn't apply for previous annual reports.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A24" authorId="0" shapeId="0" xr:uid="{EE852A70-6329-4DDD-A72F-A6921A566855}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Profitability ratio
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ROE = Net earnings/Average shareholders’ equity
+Average shareholders’ equity=(Beginning shareholders’ equity+Ending shareholders’ equity​)/2</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Return earned on shareholder capital</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0" shapeId="0" xr:uid="{6C35B411-9729-4A75-9213-F0257E95F3F3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>For the average calculation, the number is found by online since the IFRS 17 started in 2023, which doesn't apply for previous annual reports.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C24" authorId="0" shapeId="0" xr:uid="{68B85B61-38F4-49F6-B803-35686864675F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">For the average calculation, the number is found by online since the IFRS 17 started in 2023, which doesn't apply for previous annual reports.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A25" authorId="0" shapeId="0" xr:uid="{59EF187E-C4A7-40BA-8340-A600C25EF35E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Profitability ratio
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Return on total equity = Net earnings/Average total equity
+Average total equity=(Beginning Total Equity+Ending Total Equity)/2​</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Return generated on all reported equity</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0" shapeId="0" xr:uid="{98CD0ECD-2671-49BF-97E7-E871C370AAF9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>For the average calculation, the number is found by online since the IFRS 17 started in 2023, which doesn't apply for previous annual reports.</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C25" authorId="0" shapeId="0" xr:uid="{354AABDA-71A0-40AF-9187-925B76AFAE5D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>For the average calculation, the number is found by online since the IFRS 17 started in 2023, which doesn't apply for previous annual reports.</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A26" authorId="0" shapeId="0" xr:uid="{C9EC406D-5054-4117-913B-0F9F04B2C2EE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Insurance performance ratio
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insurance service margin = Insurance service result ÷ Insurance revenue</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Profitability of insurance services before other income and expenses
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A27" authorId="0" shapeId="0" xr:uid="{B09D3D18-15E9-48A7-996B-D31027F65B1F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Insurance performance
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Insurance service expense ratio = Insurance service expenses/Insurance revenue</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Insurance service costs as a percentage of insurance revenue</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A28" authorId="0" shapeId="0" xr:uid="{0C6F8177-8310-4EF9-87AC-C31FEF7CE6E1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Insurance performance
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Implied reinsurance expense ratio = Implied net reinsurance expense/Insurance revenue
+Implied net reinsurance expense=Insurance Revenue−∣Insurance Service Expenses∣−Insurance Service Result
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Impact of reinsurance on insurance service profitability</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A29" authorId="0" shapeId="0" xr:uid="{831CF2C4-12E4-4DF5-B800-2141E47B5909}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Expense efficiency
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Operating expense ratio = Operating and administrative expenses/Insurance revenue</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Administrative cost relative to insurance revenue</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A30" authorId="0" shapeId="0" xr:uid="{D60A130F-886B-42E7-9140-B9ECEF664754}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Expense efficiency
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Combined operating burden = (Insurance service expenses + operating expenses)/Insurance revenue</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Broader cost burden relative to insurance revenue</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A31" authorId="0" shapeId="0" xr:uid="{1F648360-AA5B-4022-B6C8-CF146731F016}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Solvency
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Liabilities-to-assets ratio = Total liabilities/Total assets</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Percentage of assets financed by liabilities</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A32" authorId="0" shapeId="0" xr:uid="{70FD3DEC-DF5D-4EA3-9FC3-F9E13BD05EB2}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Solvency
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Equity-to-assets ratio = Total equity/Total assets</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Capital cushion relative to assets
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A33" authorId="0" shapeId="0" xr:uid="{5D2F9C80-D27B-42F8-A659-09BDD6D655E9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Solvency
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Debt-to-shareholders’ equity = Debentures and other debt instruments/Shareholders’ equity</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Financial debt compared with shareholder capital</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A34" authorId="0" shapeId="0" xr:uid="{3E4A40E6-1782-438C-8DC9-F02E761C67B9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Solvency
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Debt-to-total-equity=Debentures and other debt instruments/Total equity</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Debt burden compared with all equity
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A35" authorId="0" shapeId="0" xr:uid="{5D3F9509-4EFB-4815-9A0A-E544B9F9880B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Solvency
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Financial leverage ratio=Average total assets/Average shareholders’ equity</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Assets supported by each dollar of shareholder equity</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A36" authorId="0" shapeId="0" xr:uid="{78A0EA3A-0EA3-4F0C-8B97-D273619C6B2A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Liquidity
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Cash-to-assets ratio=Cash and cash equivalents/Total assets</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Immediate liquidity as a percentage of assets</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A37" authorId="0" shapeId="0" xr:uid="{818E8D7C-1E59-47E6-9894-C4596500B96B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Liquidity
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Cash-to-debt ratio=Cash and cash equivalents/Debentures and other debt instruments
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Ability of cash to cover reported debentures and debt</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A38" authorId="0" shapeId="0" xr:uid="{65A866B5-7AFE-42AB-A2F9-3D7377921322}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Cash flow
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Operating cash-flow margin=Operating cash flow/Insurance revenue</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Operating cash generated per dollar of insurance revenue</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A39" authorId="0" shapeId="0" xr:uid="{629534E1-DB65-4909-B2F1-6C0C15200DB8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Cash flow
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Operating cash flow to net earnings=Operating cash flow/Net earnings</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Cash conversion of accounting earnings</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A40" authorId="0" shapeId="0" xr:uid="{E42FF970-40FC-4452-964C-7E65024B0C3F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Cash flow
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Operating cash flow return on assets=Operating cash flow/Average total assets</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Cash-generating productivity of assets</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A41" authorId="0" shapeId="0" xr:uid="{86D58471-CB9D-4EF0-A244-66B9DB1545D4}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Dividends
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Dividend payout ratio=Dividends paid/Net earnings</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Percentage of earnings distributed as dividends</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A42" authorId="0" shapeId="0" xr:uid="{EDCED61D-B27E-48AC-AA05-171679C21D2B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Dividends
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Cash dividend coverage=Operating cash flow/Dividends paid</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Ability of operating cash flow to cover dividends</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A43" authorId="0" shapeId="0" xr:uid="{ACA0D7E7-5E65-409D-958F-C708762B912F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Dividends
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Dividends-to-equity ratio=Dividends paid/Average shareholders’ equity</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Dividend distributions relative to shareholder capital</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A44" authorId="0" shapeId="0" xr:uid="{08A04C87-71B6-47FC-876B-5E4EEC1D55A6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">IFRS 17
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>CSM-to-insurance-revenue ratio=Total CSM/Insurance revenue</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Future unearned insurance profit relative to annual revenue</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A45" authorId="0" shapeId="0" xr:uid="{C988D486-401B-4C5B-B061-28A26349F99C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">IFRS 17
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>CSM-to-equity ratio=Total CSM/Total equity</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Future insurance profit balance relative to existing equity</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A46" authorId="0" shapeId="0" xr:uid="{A54D03D1-D2F0-449C-B052-FDF96F3A474F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>IFRS 17
+CSM growth rate=Current CSM/Prior-year CSM − 1
+Growth or contraction in future unearned profit</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A47" authorId="0" shapeId="0" xr:uid="{E004DCCA-492B-45D1-9BA3-5B72A68E0BE8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Capital adequacy</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+LICAT year-over-year change=Current LICAT ratio − Prior-year LICAT ratio
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Change in regulatory capital strength, in percentage points</t>
         </r>
       </text>
     </comment>
@@ -277,7 +1259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="275">
   <si>
     <t>Summary of net earnings attributable to:</t>
   </si>
@@ -1018,6 +2000,90 @@
   </si>
   <si>
     <t>Operating cash flow</t>
+  </si>
+  <si>
+    <t>Canada Life</t>
+  </si>
+  <si>
+    <t>Financial ratio analysis</t>
+  </si>
+  <si>
+    <t>Net profit margin</t>
+  </si>
+  <si>
+    <t>Return on assets, ROA</t>
+  </si>
+  <si>
+    <t>Return on shareholders’ equity, ROE</t>
+  </si>
+  <si>
+    <t>Return on total equity</t>
+  </si>
+  <si>
+    <t>Insurance service margin</t>
+  </si>
+  <si>
+    <t>Insurance service expense ratio</t>
+  </si>
+  <si>
+    <t>Implied reinsurance expense ratio</t>
+  </si>
+  <si>
+    <t>Operating expense ratio</t>
+  </si>
+  <si>
+    <t>Combined operating burden</t>
+  </si>
+  <si>
+    <t>Liabilities-to-assets ratio</t>
+  </si>
+  <si>
+    <t>Equity-to-assets ratio</t>
+  </si>
+  <si>
+    <t>Debt-to-shareholders’ equity</t>
+  </si>
+  <si>
+    <t>Debt-to-total-equity</t>
+  </si>
+  <si>
+    <t>Financial leverage ratio</t>
+  </si>
+  <si>
+    <t>Cash-to-assets ratio</t>
+  </si>
+  <si>
+    <t>Cash-to-debt ratio</t>
+  </si>
+  <si>
+    <t>Operating cash-flow margin</t>
+  </si>
+  <si>
+    <t>Operating cash flow to net earnings</t>
+  </si>
+  <si>
+    <t>Operating cash flow return on assets</t>
+  </si>
+  <si>
+    <t>Dividend payout ratio</t>
+  </si>
+  <si>
+    <t>Cash dividend coverage</t>
+  </si>
+  <si>
+    <t>Dividends-to-equity ratio</t>
+  </si>
+  <si>
+    <t>CSM-to-insurance-revenue ratio</t>
+  </si>
+  <si>
+    <t>CSM-to-equity ratio</t>
+  </si>
+  <si>
+    <t>CSM growth rate</t>
+  </si>
+  <si>
+    <t>LICAT year-over-year change</t>
   </si>
 </sst>
 </file>
@@ -1027,7 +2093,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1076,6 +2142,12 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1085,7 +2157,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1133,12 +2205,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE6E6E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1174,30 +2261,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="75">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     </dxf>
@@ -1442,6 +2517,18 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1459,9 +2546,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32C6B56A-ED7A-4BC5-86FB-BC86DC51FC56}" name="CL2025_Financial_Highlights" displayName="CL2025_Financial_Highlights" ref="A2:C21" totalsRowShown="0">
   <autoFilter ref="A2:C21" xr:uid="{32C6B56A-ED7A-4BC5-86FB-BC86DC51FC56}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{5C2C5EAF-8FD7-4548-B79E-158A94C36CEC}" name="Financial Highlights (Unaudited) (in Canadian $ Million)" dataDxfId="74"/>
-    <tableColumn id="4" xr3:uid="{F845F529-FD47-4771-A575-3ECAFBD90817}" name="2025" dataDxfId="73"/>
-    <tableColumn id="6" xr3:uid="{2D1DF53C-C68C-4325-9449-0D2B4F3F7A6D}" name="2024" dataDxfId="72"/>
+    <tableColumn id="1" xr3:uid="{5C2C5EAF-8FD7-4548-B79E-158A94C36CEC}" name="Financial Highlights (Unaudited) (in Canadian $ Million)" dataDxfId="70"/>
+    <tableColumn id="4" xr3:uid="{F845F529-FD47-4771-A575-3ECAFBD90817}" name="2025" dataDxfId="69"/>
+    <tableColumn id="6" xr3:uid="{2D1DF53C-C68C-4325-9449-0D2B4F3F7A6D}" name="2024" dataDxfId="68"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1471,8 +2558,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{872B3C60-F251-4571-AC34-BA109A0E39B4}" name="CL2024_Consolidated_Statements_Of_Cash_Flow" displayName="CL2024_Consolidated_Statements_Of_Cash_Flow" ref="A118:C147" totalsRowShown="0">
   <autoFilter ref="A118:C147" xr:uid="{872B3C60-F251-4571-AC34-BA109A0E39B4}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{03DD1A9C-855C-4E1B-BC85-F1DA52E562A1}" name="Consolidated Statements of Cash Flow  (in Canadian $ millions)" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{9F529541-D5F9-4E8A-9852-77076A9252D7}" name="2024" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{03DD1A9C-855C-4E1B-BC85-F1DA52E562A1}" name="Consolidated Statements of Cash Flow  (in Canadian $ millions)" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{9F529541-D5F9-4E8A-9852-77076A9252D7}" name="2024" dataDxfId="36"/>
     <tableColumn id="5" xr3:uid="{D60C0FDC-FC22-4E62-9467-CDCB0E581960}" name="2023"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1483,9 +2570,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{AECA25C1-C846-4A7B-A2BF-C9448B60FB0D}" name="CL2023_Financial_Highlights" displayName="CL2023_Financial_Highlights" ref="A2:C21" totalsRowShown="0">
   <autoFilter ref="A2:C21" xr:uid="{AECA25C1-C846-4A7B-A2BF-C9448B60FB0D}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2FBD130F-2F76-40A4-8A35-F73D197CF679}" name="Financial Highlights (unaudited) (in Canadian $ millions)" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{EB1CCD9F-222B-42FF-A665-B40808CDFA23}" name="2023" dataDxfId="38"/>
-    <tableColumn id="6" xr3:uid="{606BD4DE-1AB4-4377-AD4C-304EEE364AE0}" name="2022" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{2FBD130F-2F76-40A4-8A35-F73D197CF679}" name="Financial Highlights (unaudited) (in Canadian $ millions)" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{EB1CCD9F-222B-42FF-A665-B40808CDFA23}" name="2023" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{606BD4DE-1AB4-4377-AD4C-304EEE364AE0}" name="2022" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1495,9 +2582,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{403F03B7-0B2F-429E-9099-05D4B79628EE}" name="CL2023_Consolidated_Statements_Of_Earnings" displayName="CL2023_Consolidated_Statements_Of_Earnings" ref="A23:C54" totalsRowShown="0">
   <autoFilter ref="A23:C54" xr:uid="{403F03B7-0B2F-429E-9099-05D4B79628EE}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{348E9B7F-8015-4CEA-9CB7-F5A11E794924}" name="Consolidated Statements of Earnings (in Canadian $ millions)" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{9CB5D784-9668-43E2-912F-CCC0C5A46AFC}" name="2023" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{7DFA6E59-95B4-4F39-8D95-F85AC0C103B7}" name="2022" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{348E9B7F-8015-4CEA-9CB7-F5A11E794924}" name="Consolidated Statements of Earnings (in Canadian $ millions)" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{9CB5D784-9668-43E2-912F-CCC0C5A46AFC}" name="2023" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{7DFA6E59-95B4-4F39-8D95-F85AC0C103B7}" name="2022" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1507,10 +2594,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{C8294548-29F4-4247-8D91-46256870F255}" name="CL2023_Consolidated_Balance_Sheets" displayName="CL2023_Consolidated_Balance_Sheets" ref="A57:D105" totalsRowShown="0">
   <autoFilter ref="A57:D105" xr:uid="{C8294548-29F4-4247-8D91-46256870F255}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A77F868F-A01A-4E28-831C-123758FFEE1B}" name="Consolidated Balance Sheets (in Canadian $ millions)" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{BF1169F7-EA41-4E34-B1BE-468D058EC001}" name="2023" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{0DED70B6-5DBC-4722-9AEA-0F35DB477359}" name="2022" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{391AF299-CDE1-44A4-94F3-25223ECFCF43}" name="2021" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{A77F868F-A01A-4E28-831C-123758FFEE1B}" name="Consolidated Balance Sheets (in Canadian $ millions)" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{BF1169F7-EA41-4E34-B1BE-468D058EC001}" name="2023" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{0DED70B6-5DBC-4722-9AEA-0F35DB477359}" name="2022" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{391AF299-CDE1-44A4-94F3-25223ECFCF43}" name="2021" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1520,15 +2607,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{010BDDA1-0210-42C8-BA1E-98C8F4E39148}" name="CL2023_Consolidated_Statements_Of_Changes_In_Equity" displayName="CL2023_Consolidated_Statements_Of_Changes_In_Equity" ref="A108:I119" totalsRowShown="0">
   <autoFilter ref="A108:I119" xr:uid="{010BDDA1-0210-42C8-BA1E-98C8F4E39148}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{12AD67BC-57B1-41C3-A7A2-ECD190ADFB8A}" name="Consolidated Statements of Changes in Equity (in Canadian $ millions)" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{D69CD2BD-7405-43A8-B2F6-D33B29AE7319}" name="Share capital" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{D7419A9F-70E7-4602-A940-77D76211462A}" name="Contributed surplus" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{6F1EC460-0E36-4BAA-BD61-804EA1A7B604}" name="Accumulated surplus" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{ECC52595-0035-4144-8E9B-C830D055A87F}" name="Accumulated other comprehensive income (loss)" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{DD90BFCF-0719-4732-B663-A0F6DDCBB014}" name="Total shareholders' equity" dataDxfId="24"/>
-    <tableColumn id="11" xr3:uid="{45A80F18-CA21-485E-9774-7188CBDBD23A}" name="Non-controlling interests" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{5EFFD87C-8A6F-4E32-BC35-2981FB121A78}" name="Participating account surplus" dataDxfId="22"/>
-    <tableColumn id="15" xr3:uid="{E2F54086-E050-49D8-8244-5234819E6F63}" name="Total equity" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{12AD67BC-57B1-41C3-A7A2-ECD190ADFB8A}" name="Consolidated Statements of Changes in Equity (in Canadian $ millions)" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{D69CD2BD-7405-43A8-B2F6-D33B29AE7319}" name="Share capital" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{D7419A9F-70E7-4602-A940-77D76211462A}" name="Contributed surplus" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{6F1EC460-0E36-4BAA-BD61-804EA1A7B604}" name="Accumulated surplus" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{ECC52595-0035-4144-8E9B-C830D055A87F}" name="Accumulated other comprehensive income (loss)" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{DD90BFCF-0719-4732-B663-A0F6DDCBB014}" name="Total shareholders' equity" dataDxfId="20"/>
+    <tableColumn id="11" xr3:uid="{45A80F18-CA21-485E-9774-7188CBDBD23A}" name="Non-controlling interests" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{5EFFD87C-8A6F-4E32-BC35-2981FB121A78}" name="Participating account surplus" dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{E2F54086-E050-49D8-8244-5234819E6F63}" name="Total equity" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1538,7 +2625,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{070ABDE2-BBC3-4908-AB0F-44D6EF66AED5}" name="CL2023_Consolidated_Statements_Of_Cash_Flows" displayName="CL2023_Consolidated_Statements_Of_Cash_Flows" ref="A122:C152" totalsRowShown="0">
   <autoFilter ref="A122:C152" xr:uid="{070ABDE2-BBC3-4908-AB0F-44D6EF66AED5}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7B75C2BC-A013-41C7-861B-9EDA9E0AE1BA}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{7B75C2BC-A013-41C7-861B-9EDA9E0AE1BA}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="16"/>
     <tableColumn id="5" xr3:uid="{D08EF108-C608-416D-A0FA-78700D08B198}" name="2023"/>
     <tableColumn id="7" xr3:uid="{0A748248-90C6-42D4-A30D-90D2E6522606}" name="2022"/>
   </tableColumns>
@@ -1550,7 +2637,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{DA35DAB2-1EB1-4099-B43A-7BBB210BD1B2}" name="CL2022_Financial_Highlight" displayName="CL2022_Financial_Highlight" ref="A2:C26" totalsRowShown="0">
   <autoFilter ref="A2:C26" xr:uid="{DA35DAB2-1EB1-4099-B43A-7BBB210BD1B2}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{742648AB-0CC3-4711-89DE-BEA31617073E}" name="Financial Highlight (unaudited)  (in Canadian $ millions)" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{742648AB-0CC3-4711-89DE-BEA31617073E}" name="Financial Highlight (unaudited)  (in Canadian $ millions)" dataDxfId="15"/>
     <tableColumn id="4" xr3:uid="{8EFD586F-8504-433C-ACA7-A80E443245D8}" name="2022"/>
     <tableColumn id="6" xr3:uid="{F3762B59-FF64-4412-994B-4F79CC8C4273}" name="2021"/>
   </tableColumns>
@@ -1562,8 +2649,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{D352CFDF-76E1-4D3C-8C7B-7F57348B216F}" name="CL2022_Consolidated_Statements_Of_Earnings" displayName="CL2022_Consolidated_Statements_Of_Earnings" ref="A29:C63" totalsRowShown="0">
   <autoFilter ref="A29:C63" xr:uid="{D352CFDF-76E1-4D3C-8C7B-7F57348B216F}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E02CB553-D5D4-402A-8C54-8DE755972EFF}" name="Consolidated Statements of Earnings  (in Canadian $ millions)" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{63FC9382-AFA6-415E-82F8-8CF40DE991D2}" name="2022" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{E02CB553-D5D4-402A-8C54-8DE755972EFF}" name="Consolidated Statements of Earnings  (in Canadian $ millions)" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{63FC9382-AFA6-415E-82F8-8CF40DE991D2}" name="2022" dataDxfId="13"/>
     <tableColumn id="6" xr3:uid="{75F17EC1-69D4-4F5D-8315-089CA34D666C}" name="2021"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1574,7 +2661,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{BB04493A-D9FF-4D74-A5D0-111BD2A4656C}" name="CL2022_Consolidated_Balance_Sheets" displayName="CL2022_Consolidated_Balance_Sheets" ref="A66:C112" totalsRowShown="0">
   <autoFilter ref="A66:C112" xr:uid="{BB04493A-D9FF-4D74-A5D0-111BD2A4656C}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{893DB4C7-64EE-4ADA-8217-9192AD5B689E}" name="Consolidated Balance Sheets" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{893DB4C7-64EE-4ADA-8217-9192AD5B689E}" name="Consolidated Balance Sheets" dataDxfId="12"/>
     <tableColumn id="4" xr3:uid="{DFF048A5-755F-448B-87C0-4E919F682AF0}" name="2022"/>
     <tableColumn id="6" xr3:uid="{5DD01DB6-24AF-4D26-80A0-169FFD04A979}" name="2021"/>
   </tableColumns>
@@ -1586,15 +2673,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{215DB435-83EB-4E91-B08B-67EC402A3AFF}" name="CL2022_Consolidated_Statements_Of_Changes_In_Equity" displayName="CL2022_Consolidated_Statements_Of_Changes_In_Equity" ref="A115:I124" totalsRowShown="0">
   <autoFilter ref="A115:I124" xr:uid="{215DB435-83EB-4E91-B08B-67EC402A3AFF}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{09504AB0-770E-4D43-ACD1-DE5F040CED87}" name="Consolidated Statements of Changes in Equity" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{BFA1FFA7-6E3B-4F23-85D7-277A408FB401}" name="Share capital" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{701F6E9A-D8E6-4794-950B-B6C0DCDFFB6C}" name="Contributed surplus" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{C6BCA9CA-AA5E-4ECD-A8ED-3425059521DC}" name="Accumulated surplus" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{C387DAE6-44DC-4C88-B247-97FF4BBC177F}" name="Accumulated other comprehensive loss comprehensive loss" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{3D9F6865-2163-45E5-9E9F-FE1EFA6E0A4E}" name="Total shareholders’ equity" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{A62F3586-FEAD-4757-955C-167BA489C2DA}" name="Non-controlling interests" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{5EC6C0BE-4B74-4A04-B001-36C6B2FE1058}" name="Participating account surplus" dataDxfId="8"/>
-    <tableColumn id="17" xr3:uid="{63AE17E1-9D3F-402A-8E50-6A25D991559F}" name="Total equity" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{09504AB0-770E-4D43-ACD1-DE5F040CED87}" name="Consolidated Statements of Changes in Equity" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{BFA1FFA7-6E3B-4F23-85D7-277A408FB401}" name="Share capital" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{701F6E9A-D8E6-4794-950B-B6C0DCDFFB6C}" name="Contributed surplus" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{C6BCA9CA-AA5E-4ECD-A8ED-3425059521DC}" name="Accumulated surplus" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{C387DAE6-44DC-4C88-B247-97FF4BBC177F}" name="Accumulated other comprehensive loss comprehensive loss" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{3D9F6865-2163-45E5-9E9F-FE1EFA6E0A4E}" name="Total shareholders’ equity" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{A62F3586-FEAD-4757-955C-167BA489C2DA}" name="Non-controlling interests" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{5EC6C0BE-4B74-4A04-B001-36C6B2FE1058}" name="Participating account surplus" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{63AE17E1-9D3F-402A-8E50-6A25D991559F}" name="Total equity" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1604,9 +2691,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{34C03A14-B5FE-4A4C-A2DD-6F7C99CBB8B6}" name="CL2025_Consolidated_Statements_Of_Earnings" displayName="CL2025_Consolidated_Statements_Of_Earnings" ref="A24:C54" totalsRowShown="0">
   <autoFilter ref="A24:C54" xr:uid="{34C03A14-B5FE-4A4C-A2DD-6F7C99CBB8B6}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{AF140A9C-2544-462A-8D05-83FCA92FCC29}" name="Consolidated Statements Of Earnings (in Canadian $ Million)" dataDxfId="71"/>
-    <tableColumn id="3" xr3:uid="{16B7134F-532D-42E5-B2C1-83A349FA9ED6}" name="2025" dataDxfId="70"/>
-    <tableColumn id="5" xr3:uid="{A04CC424-6000-4365-8CE5-358C2FA21877}" name="2024" dataDxfId="69"/>
+    <tableColumn id="1" xr3:uid="{AF140A9C-2544-462A-8D05-83FCA92FCC29}" name="Consolidated Statements Of Earnings (in Canadian $ Million)" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{16B7134F-532D-42E5-B2C1-83A349FA9ED6}" name="2025" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{A04CC424-6000-4365-8CE5-358C2FA21877}" name="2024" dataDxfId="65"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1616,30 +2703,30 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{395EA000-7795-40F0-80C9-309E26D34DB3}" name="CL2022_Consolidated_Statements_Of_Cash_Flows" displayName="CL2022_Consolidated_Statements_Of_Cash_Flows" ref="A127:C161" totalsRowShown="0">
   <autoFilter ref="A127:C161" xr:uid="{395EA000-7795-40F0-80C9-309E26D34DB3}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D9D5A221-D279-446F-84E7-045892C71C4C}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{0B41E5F3-DDED-491F-B3FE-F07FAA1FC2F1}" name="2022" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{597E5080-187F-4732-87DD-297275C991F1}" name="2021" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{D9D5A221-D279-446F-84E7-045892C71C4C}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{0B41E5F3-DDED-491F-B3FE-F07FAA1FC2F1}" name="2022" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{597E5080-187F-4732-87DD-297275C991F1}" name="2021" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{62B2A73A-1EEC-46AC-91EE-7CD6FB19EA63}" name="CL_Annual_Financial_Item" displayName="CL_Annual_Financial_Item" ref="A1:E17" totalsRowShown="0">
-  <autoFilter ref="A1:E17" xr:uid="{62B2A73A-1EEC-46AC-91EE-7CD6FB19EA63}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{62B2A73A-1EEC-46AC-91EE-7CD6FB19EA63}" name="CL_Annual_Financial_Item" displayName="CL_Annual_Financial_Item" ref="A3:E18" totalsRowShown="0">
+  <autoFilter ref="A3:E18" xr:uid="{62B2A73A-1EEC-46AC-91EE-7CD6FB19EA63}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C65EBD19-CB55-4FE0-9E64-CCC55F3C53D5}" name="Financial item (CAD $ millions)"/>
-    <tableColumn id="2" xr3:uid="{64F0E65D-5B27-41C2-9D64-A1370C90CAE6}" name="2022" dataDxfId="3">
-      <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A2,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{64F0E65D-5B27-41C2-9D64-A1370C90CAE6}" name="2022" dataDxfId="74">
+      <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A4,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5DB1D296-8814-4B6A-9833-E4A1CCA5D2FA}" name="2023" dataDxfId="2">
-      <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A2,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{5DB1D296-8814-4B6A-9833-E4A1CCA5D2FA}" name="2023" dataDxfId="73">
+      <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A4,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{59F5E5CB-387A-45BC-B330-F894B4F6DE82}" name="2024" dataDxfId="1">
-      <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A2,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</calculatedColumnFormula>
+    <tableColumn id="4" xr3:uid="{59F5E5CB-387A-45BC-B330-F894B4F6DE82}" name="2024" dataDxfId="72">
+      <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A4,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{553985D8-0F6B-4CAB-A4A1-B67873C194FD}" name="2025" dataDxfId="0">
-      <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A2,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{553985D8-0F6B-4CAB-A4A1-B67873C194FD}" name="2025" dataDxfId="71">
+      <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A4,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1650,8 +2737,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FABD7B52-E650-435A-863F-F68E89A607E8}" name="CL2025_Consolidated_Balance_Sheet" displayName="CL2025_Consolidated_Balance_Sheet" ref="A58:C106" totalsRowShown="0">
   <autoFilter ref="A58:C106" xr:uid="{FABD7B52-E650-435A-863F-F68E89A607E8}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D6729C5B-6996-4AD6-921A-4FCB66DC5B45}" name="Consolidated Balance Sheet  (in Canadian $ Million)" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{1B220B5B-DEB0-4054-AD07-3C5B3F8AACD1}" name="2025" dataDxfId="67"/>
+    <tableColumn id="1" xr3:uid="{D6729C5B-6996-4AD6-921A-4FCB66DC5B45}" name="Consolidated Balance Sheet  (in Canadian $ Million)" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{1B220B5B-DEB0-4054-AD07-3C5B3F8AACD1}" name="2025" dataDxfId="63"/>
     <tableColumn id="5" xr3:uid="{E50E6906-CAA9-42F6-9EB9-A1F697BB2F20}" name="2024"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1662,15 +2749,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CF654234-2B8F-4830-BE0E-554991835BD9}" name="CL2025_Consolidated_Statements_Of_Change_In_Equity" displayName="CL2025_Consolidated_Statements_Of_Change_In_Equity" ref="A109:I117" totalsRowShown="0">
   <autoFilter ref="A109:I117" xr:uid="{CF654234-2B8F-4830-BE0E-554991835BD9}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C372BC7B-EDAA-425F-B029-CC348E8759F1}" name="Consolidated Statements of Change in Equity" dataDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{87A431C1-44DD-4CAE-8CF0-67ED9C3536FA}" name="Share Capital" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{1ACAEC2D-550E-4F1E-899C-D23FDA3C7A2F}" name="Contributed Surplus" dataDxfId="64"/>
-    <tableColumn id="6" xr3:uid="{DA9BD253-8ABA-4C4C-90D8-B886FCF7BB0C}" name="Accumulated Surplus" dataDxfId="63"/>
-    <tableColumn id="8" xr3:uid="{35415082-274B-4DFF-B6E0-53920A2A9F6D}" name="Accumulated Other Comprehensive Income" dataDxfId="62"/>
-    <tableColumn id="10" xr3:uid="{2F102C70-C964-49EB-A16F-A1842CC2B96F}" name="Total Shareholder's Equity" dataDxfId="61"/>
-    <tableColumn id="12" xr3:uid="{ECFC45BF-2FD7-4257-A71D-CD62160491EA}" name="Non-controlling Interest" dataDxfId="60"/>
-    <tableColumn id="14" xr3:uid="{E959836E-9965-4D14-BCC3-3BCC273F49C9}" name="Participating Account Surplus" dataDxfId="59"/>
-    <tableColumn id="16" xr3:uid="{C57C220A-153E-480B-8F20-BD9766EBCC5D}" name="Total Equity" dataDxfId="58"/>
+    <tableColumn id="1" xr3:uid="{C372BC7B-EDAA-425F-B029-CC348E8759F1}" name="Consolidated Statements of Change in Equity" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{87A431C1-44DD-4CAE-8CF0-67ED9C3536FA}" name="Share Capital" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{1ACAEC2D-550E-4F1E-899C-D23FDA3C7A2F}" name="Contributed Surplus" dataDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{DA9BD253-8ABA-4C4C-90D8-B886FCF7BB0C}" name="Accumulated Surplus" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{35415082-274B-4DFF-B6E0-53920A2A9F6D}" name="Accumulated Other Comprehensive Income" dataDxfId="58"/>
+    <tableColumn id="10" xr3:uid="{2F102C70-C964-49EB-A16F-A1842CC2B96F}" name="Total Shareholder's Equity" dataDxfId="57"/>
+    <tableColumn id="12" xr3:uid="{ECFC45BF-2FD7-4257-A71D-CD62160491EA}" name="Non-controlling Interest" dataDxfId="56"/>
+    <tableColumn id="14" xr3:uid="{E959836E-9965-4D14-BCC3-3BCC273F49C9}" name="Participating Account Surplus" dataDxfId="55"/>
+    <tableColumn id="16" xr3:uid="{C57C220A-153E-480B-8F20-BD9766EBCC5D}" name="Total Equity" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1680,7 +2767,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3AAC487E-DBF0-4C56-AF4F-056F3601ED72}" name="CL2025_Consolidated_Statements_Of_Cash_Flow" displayName="CL2025_Consolidated_Statements_Of_Cash_Flow" ref="A121:C149" totalsRowShown="0">
   <autoFilter ref="A121:C149" xr:uid="{3AAC487E-DBF0-4C56-AF4F-056F3601ED72}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2F45C01F-02D6-4CB5-9364-F722A27B3859}" name="Consolidated Statements of Cash Flow" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{2F45C01F-02D6-4CB5-9364-F722A27B3859}" name="Consolidated Statements of Cash Flow" dataDxfId="53"/>
     <tableColumn id="3" xr3:uid="{712741C7-204F-4298-8050-873B208D5060}" name="2025"/>
     <tableColumn id="5" xr3:uid="{2534FEF1-3F52-460C-AB74-977F2325376E}" name="2024"/>
   </tableColumns>
@@ -1692,8 +2779,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{80062148-2C94-44FA-AA84-D3AF2950CAE1}" name="CL2024_Financial_Highlights" displayName="CL2024_Financial_Highlights" ref="A2:C21" totalsRowShown="0">
   <autoFilter ref="A2:C21" xr:uid="{80062148-2C94-44FA-AA84-D3AF2950CAE1}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A504AF7D-4077-4F75-AD8E-F00D66A4E1EB}" name="Financial Highlights (in Canadian $ millions)" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{6DE21333-8B6D-493E-A3FB-12219341B858}" name="2024" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{A504AF7D-4077-4F75-AD8E-F00D66A4E1EB}" name="Financial Highlights (in Canadian $ millions)" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{6DE21333-8B6D-493E-A3FB-12219341B858}" name="2024" dataDxfId="51"/>
     <tableColumn id="7" xr3:uid="{1D1F864D-619C-4D8B-BDCB-F9F994AD3F85}" name="2023"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1704,9 +2791,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F2E5B2C2-C7D4-4C68-B8DF-B451C6AD2FA5}" name="CL2024_Consolidated_Statement_Of_Earnings" displayName="CL2024_Consolidated_Statement_Of_Earnings" ref="A24:C54" totalsRowShown="0">
   <autoFilter ref="A24:C54" xr:uid="{F2E5B2C2-C7D4-4C68-B8DF-B451C6AD2FA5}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B00DF7C4-46F0-426A-99DA-8CD1485C8167}" name="Consolidated Statements of Earnings (in Canadian $ millions)" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{6DBC8D88-3782-41F5-8C7F-4912F53C3845}" name="2024" dataDxfId="53"/>
-    <tableColumn id="5" xr3:uid="{0DA8B320-B9A4-43AB-B84E-C184D12EEBCE}" name="2023" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{B00DF7C4-46F0-426A-99DA-8CD1485C8167}" name="Consolidated Statements of Earnings (in Canadian $ millions)" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{6DBC8D88-3782-41F5-8C7F-4912F53C3845}" name="2024" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{0DA8B320-B9A4-43AB-B84E-C184D12EEBCE}" name="2023" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1716,7 +2803,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{09288B11-3956-44BF-B015-CDD67BF6122B}" name="CL2024_Consolidated_Balance_Sheet" displayName="CL2024_Consolidated_Balance_Sheet" ref="A57:C104" totalsRowShown="0">
   <autoFilter ref="A57:C104" xr:uid="{09288B11-3956-44BF-B015-CDD67BF6122B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{9A2A315A-17C4-44C5-839B-27077EDAFBE8}" name="Consolidated Balance Sheet  (in Canadian $ millions)" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{9A2A315A-17C4-44C5-839B-27077EDAFBE8}" name="Consolidated Balance Sheet  (in Canadian $ millions)" dataDxfId="47"/>
     <tableColumn id="3" xr3:uid="{AC35110F-0BC5-4C19-B333-64D500DD652D}" name="2024"/>
     <tableColumn id="5" xr3:uid="{FC18CAD8-EF52-4B84-B287-4440BF8988D1}" name="2023"/>
   </tableColumns>
@@ -1728,15 +2815,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{95B36E1D-5C8B-415A-8BB2-72AC852DFE1F}" name="CL2024_Consolidated_Statements_Of_Changes_In_Equity" displayName="CL2024_Consolidated_Statements_Of_Changes_In_Equity" ref="A107:I115" totalsRowShown="0">
   <autoFilter ref="A107:I115" xr:uid="{95B36E1D-5C8B-415A-8BB2-72AC852DFE1F}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{346EBBBA-D3E8-43C4-B112-84CFBA884811}" name="Consolidated Statements of Changes in Equity  (in Canadian $ millions)" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{A3F2222E-550B-4C91-822F-4D93B86D0518}" name="Share capital" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{5DE7CF1E-A17D-4E32-B7FB-FD3FCA7A27C6}" name="Contributed surplus" dataDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{7CD3F9B9-2C9F-423A-9B10-5566ED617B23}" name="Accumulated surplus" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{81A55F20-6E2D-49CB-A777-7EA2FA186E54}" name="Accumulated other comprehensive income (loss)" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{436743AE-2B63-4A1B-B86F-48A200522D06}" name="Total shareholder's equity" dataDxfId="45"/>
-    <tableColumn id="12" xr3:uid="{185E9850-C6B0-4386-B196-713B0971812A}" name="Non-controlling interests" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{F07A79B8-D988-4A89-BC52-58700AEF495C}" name="Participating account surplus" dataDxfId="43"/>
-    <tableColumn id="16" xr3:uid="{DAC2842E-0699-4DFF-A5A2-CA0460B0936F}" name="Total equity" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{346EBBBA-D3E8-43C4-B112-84CFBA884811}" name="Consolidated Statements of Changes in Equity  (in Canadian $ millions)" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{A3F2222E-550B-4C91-822F-4D93B86D0518}" name="Share capital" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{5DE7CF1E-A17D-4E32-B7FB-FD3FCA7A27C6}" name="Contributed surplus" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{7CD3F9B9-2C9F-423A-9B10-5566ED617B23}" name="Accumulated surplus" dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{81A55F20-6E2D-49CB-A777-7EA2FA186E54}" name="Accumulated other comprehensive income (loss)" dataDxfId="42"/>
+    <tableColumn id="10" xr3:uid="{436743AE-2B63-4A1B-B86F-48A200522D06}" name="Total shareholder's equity" dataDxfId="41"/>
+    <tableColumn id="12" xr3:uid="{185E9850-C6B0-4386-B196-713B0971812A}" name="Non-controlling interests" dataDxfId="40"/>
+    <tableColumn id="14" xr3:uid="{F07A79B8-D988-4A89-BC52-58700AEF495C}" name="Participating account surplus" dataDxfId="39"/>
+    <tableColumn id="16" xr3:uid="{DAC2842E-0699-4DFF-A5A2-CA0460B0936F}" name="Total equity" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2126,9 +3213,9 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="23"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
@@ -2164,9 +3251,9 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="23"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
@@ -2213,7 +3300,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="21"/>
+      <c r="A16" s="2"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
     </row>
@@ -2262,7 +3349,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="2" t="s">
         <v>204</v>
       </c>
       <c r="B21" s="13">
@@ -5400,13 +6487,13 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="19" t="s">
+      <c r="A21" t="s">
         <v>204</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="19">
         <v>1.28</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="19">
         <f>'CL 2022 (Original)'!B26</f>
         <v>1.2</v>
       </c>
@@ -8764,7 +9851,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB2D2CB0-3C74-48F6-A0FC-1C79BE7E1C5C}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="47.453125" bestFit="1" customWidth="1"/>
@@ -8776,359 +9863,606 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B2" s="1" cm="1">
-        <f t="array" ref="B2">_xlfn.XLOOKUP(A2,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2022]],"Not Found",0)</f>
-        <v>19424</v>
-      </c>
-      <c r="C2" s="1" cm="1">
-        <f t="array" ref="C2">_xlfn.XLOOKUP(A2,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2023]],"Not Found", 0)</f>
-        <v>20188</v>
-      </c>
-      <c r="D2" s="1" cm="1">
-        <f t="array" ref="D2">_xlfn.XLOOKUP(A2,CL2024_Consolidated_Statement_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2024_Consolidated_Statement_Of_Earnings[[#All],[2024]],"Not Found", 0)</f>
-        <v>21007</v>
-      </c>
-      <c r="E2" s="1">
-        <f>_xlfn.XLOOKUP(A2,CL2025_Consolidated_Statements_Of_Earnings[Consolidated Statements Of Earnings (in Canadian $ Million)],CL2025_Consolidated_Statements_Of_Earnings[2025],"Not Found",0)</f>
-        <v>22131</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B3" s="1" cm="1">
-        <f t="array" ref="B3">_xlfn.XLOOKUP(A3,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2022]],"Not Found",0)</f>
-        <v>-15110</v>
-      </c>
-      <c r="C3" s="1" cm="1">
-        <f t="array" ref="C3">_xlfn.XLOOKUP(A3,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2023]],"Not Found",0)</f>
-        <v>-15622</v>
-      </c>
-      <c r="D3" s="1">
-        <f>_xlfn.XLOOKUP(A3,CL2024_Consolidated_Statement_Of_Earnings[Consolidated Statements of Earnings (in Canadian $ millions)],CL2024_Consolidated_Statement_Of_Earnings[2024],"Not Found",0)</f>
-        <v>-16165</v>
-      </c>
-      <c r="E3" s="1">
-        <f>_xlfn.XLOOKUP(A3,CL2025_Consolidated_Statements_Of_Earnings[Consolidated Statements Of Earnings (in Canadian $ Million)],CL2025_Consolidated_Statements_Of_Earnings[2025],"Not Found",0)</f>
-        <v>-17002</v>
+        <v>241</v>
+      </c>
+      <c r="B3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="1" cm="1">
+        <f t="array" ref="B4">_xlfn.XLOOKUP(A4,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2022]],"Not Found",0)</f>
+        <v>19424</v>
+      </c>
+      <c r="C4" s="1" cm="1">
+        <f t="array" ref="C4">_xlfn.XLOOKUP(A4,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2023]],"Not Found", 0)</f>
+        <v>20188</v>
+      </c>
+      <c r="D4" s="1" cm="1">
+        <f t="array" ref="D4">_xlfn.XLOOKUP(A4,CL2024_Consolidated_Statement_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2024_Consolidated_Statement_Of_Earnings[[#All],[2024]],"Not Found", 0)</f>
+        <v>21007</v>
+      </c>
+      <c r="E4" s="1">
+        <f>_xlfn.XLOOKUP(A4,CL2025_Consolidated_Statements_Of_Earnings[Consolidated Statements Of Earnings (in Canadian $ Million)],CL2025_Consolidated_Statements_Of_Earnings[2025],"Not Found",0)</f>
+        <v>22131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B5" s="1" cm="1">
+        <f t="array" ref="B5">_xlfn.XLOOKUP(A5,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2022]],"Not Found",0)</f>
+        <v>-15110</v>
+      </c>
+      <c r="C5" s="1" cm="1">
+        <f t="array" ref="C5">_xlfn.XLOOKUP(A5,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2023]],"Not Found",0)</f>
+        <v>-15622</v>
+      </c>
+      <c r="D5" s="1">
+        <f>_xlfn.XLOOKUP(A5,CL2024_Consolidated_Statement_Of_Earnings[Consolidated Statements of Earnings (in Canadian $ millions)],CL2024_Consolidated_Statement_Of_Earnings[2024],"Not Found",0)</f>
+        <v>-16165</v>
+      </c>
+      <c r="E5" s="1">
+        <f>_xlfn.XLOOKUP(A5,CL2025_Consolidated_Statements_Of_Earnings[Consolidated Statements Of Earnings (in Canadian $ Million)],CL2025_Consolidated_Statements_Of_Earnings[2025],"Not Found",0)</f>
+        <v>-17002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B6" s="1">
         <f>SUM('CL 2023 (Original)'!C26:C28)</f>
         <v>2766</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C6" s="1">
         <f>SUM('CL 2023 (Original)'!B26:B28)</f>
         <v>3002</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D6" s="1">
         <f>SUM('CL 2024 (Original)'!B26:B28)</f>
         <v>3258</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E6" s="1">
         <f>SUM('CL 2025 (Original)'!B26:B28)</f>
         <v>3450</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>243</v>
-      </c>
-      <c r="B5" s="1" cm="1">
-        <f t="array" ref="B5">_xlfn.XLOOKUP(A5,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2022]],"Not Found",0)</f>
-        <v>-2221</v>
-      </c>
-      <c r="C5" s="1" cm="1">
-        <f t="array" ref="C5">_xlfn.XLOOKUP(A5,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2023]],"Not Found",0)</f>
-        <v>-2635</v>
-      </c>
-      <c r="D5" s="1" cm="1">
-        <f t="array" ref="D5">_xlfn.XLOOKUP(A5,CL2024_Consolidated_Statement_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2024_Consolidated_Statement_Of_Earnings[[#All],[2024]],"Not Found",0)</f>
-        <v>-3088</v>
-      </c>
-      <c r="E5" s="1" cm="1">
-        <f t="array" ref="E5">_xlfn.XLOOKUP(A5,CL2025_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements Of Earnings (in Canadian $ Million)]],CL2025_Consolidated_Statements_Of_Earnings[[#All],[2025]],"Not Found",0)</f>
-        <v>-3408</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" cm="1">
-        <f t="array" ref="B6">_xlfn.XLOOKUP(A6,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2022]],"Not Found",0)</f>
-        <v>3286</v>
-      </c>
-      <c r="C6" s="1" cm="1">
-        <f t="array" ref="C6">_xlfn.XLOOKUP(A6,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2023]],"Not Found",0)</f>
-        <v>2418</v>
-      </c>
-      <c r="D6" s="1" cm="1">
-        <f t="array" ref="D6">_xlfn.XLOOKUP(A6,CL2024_Consolidated_Statement_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2024_Consolidated_Statement_Of_Earnings[[#All],[2024]],"Not Found",0)</f>
-        <v>3247</v>
-      </c>
-      <c r="E6" s="1" cm="1">
-        <f t="array" ref="E6">_xlfn.XLOOKUP(A6,CL2025_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements Of Earnings (in Canadian $ Million)]],CL2025_Consolidated_Statements_Of_Earnings[[#All],[2025]],"Not Found",0)</f>
-        <v>2766</v>
-      </c>
-    </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>243</v>
       </c>
       <c r="B7" s="1" cm="1">
-        <f t="array" ref="B7">_xlfn.XLOOKUP(A7,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2022]],"Not Found", 0)</f>
-        <v>378654</v>
+        <f t="array" ref="B7">_xlfn.XLOOKUP(A7,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2022]],"Not Found",0)</f>
+        <v>-2221</v>
       </c>
       <c r="C7" s="1" cm="1">
-        <f t="array" ref="C7">_xlfn.XLOOKUP(A7,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2023]],"Not Found",0)</f>
-        <v>410616</v>
+        <f t="array" ref="C7">_xlfn.XLOOKUP(A7,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2023]],"Not Found",0)</f>
+        <v>-2635</v>
       </c>
       <c r="D7" s="1" cm="1">
-        <f t="array" ref="D7">_xlfn.XLOOKUP(A7,CL2024_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ millions)]],CL2024_Consolidated_Balance_Sheet[[#All],[2024]],"Not Found",0)</f>
-        <v>461204</v>
+        <f t="array" ref="D7">_xlfn.XLOOKUP(A7,CL2024_Consolidated_Statement_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2024_Consolidated_Statement_Of_Earnings[[#All],[2024]],"Not Found",0)</f>
+        <v>-3088</v>
       </c>
       <c r="E7" s="1" cm="1">
-        <f t="array" ref="E7">_xlfn.XLOOKUP(A7,CL2025_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ Million)]],CL2025_Consolidated_Balance_Sheet[[#All],[2025]],"Not Found",0)</f>
-        <v>505652</v>
+        <f t="array" ref="E7">_xlfn.XLOOKUP(A7,CL2025_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements Of Earnings (in Canadian $ Million)]],CL2025_Consolidated_Statements_Of_Earnings[[#All],[2025]],"Not Found",0)</f>
+        <v>-3408</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="B8" s="1" cm="1">
-        <f t="array" ref="B8">_xlfn.XLOOKUP(A8,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2022]],"Not Found",0)</f>
-        <v>355866</v>
+        <f t="array" ref="B8">_xlfn.XLOOKUP(A8,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2022]],"Not Found",0)</f>
+        <v>3286</v>
       </c>
       <c r="C8" s="1" cm="1">
-        <f t="array" ref="C8">_xlfn.XLOOKUP(A8,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2023]],"Not Found",0)</f>
-        <v>387943</v>
+        <f t="array" ref="C8">_xlfn.XLOOKUP(A8,CL2023_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Earnings[[#All],[2023]],"Not Found",0)</f>
+        <v>2418</v>
       </c>
       <c r="D8" s="1" cm="1">
-        <f t="array" ref="D8">_xlfn.XLOOKUP(A8,CL2024_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ millions)]],CL2024_Consolidated_Balance_Sheet[[#All],[2024]],"Not Found",0)</f>
-        <v>437242</v>
+        <f t="array" ref="D8">_xlfn.XLOOKUP(A8,CL2024_Consolidated_Statement_Of_Earnings[[#All],[Consolidated Statements of Earnings (in Canadian $ millions)]],CL2024_Consolidated_Statement_Of_Earnings[[#All],[2024]],"Not Found",0)</f>
+        <v>3247</v>
       </c>
       <c r="E8" s="1" cm="1">
-        <f t="array" ref="E8">_xlfn.XLOOKUP(A8,CL2025_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ Million)]],CL2025_Consolidated_Balance_Sheet[[#All],[2025]],"Not Found",0)</f>
-        <v>481632</v>
+        <f t="array" ref="E8">_xlfn.XLOOKUP(A8,CL2025_Consolidated_Statements_Of_Earnings[[#All],[Consolidated Statements Of Earnings (in Canadian $ Million)]],CL2025_Consolidated_Statements_Of_Earnings[[#All],[2025]],"Not Found",0)</f>
+        <v>2766</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" cm="1">
-        <f t="array" ref="B9">_xlfn.XLOOKUP(A9,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</f>
-        <v>20004</v>
+        <f t="array" ref="B9">_xlfn.XLOOKUP(A9,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2022]],"Not Found", 0)</f>
+        <v>378654</v>
       </c>
       <c r="C9" s="1" cm="1">
-        <f t="array" ref="C9">_xlfn.XLOOKUP(A9,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</f>
-        <v>19813</v>
+        <f t="array" ref="C9">_xlfn.XLOOKUP(A9,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2023]],"Not Found",0)</f>
+        <v>410616</v>
       </c>
       <c r="D9" s="1" cm="1">
-        <f t="array" ref="D9">_xlfn.XLOOKUP(A9,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</f>
-        <v>20909</v>
+        <f t="array" ref="D9">_xlfn.XLOOKUP(A9,CL2024_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ millions)]],CL2024_Consolidated_Balance_Sheet[[#All],[2024]],"Not Found",0)</f>
+        <v>461204</v>
       </c>
       <c r="E9" s="1" cm="1">
-        <f t="array" ref="E9">_xlfn.XLOOKUP(A9,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</f>
-        <v>20938</v>
+        <f t="array" ref="E9">_xlfn.XLOOKUP(A9,CL2025_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ Million)]],CL2025_Consolidated_Balance_Sheet[[#All],[2025]],"Not Found",0)</f>
+        <v>505652</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>244</v>
+        <v>60</v>
       </c>
       <c r="B10" s="1" cm="1">
         <f t="array" ref="B10">_xlfn.XLOOKUP(A10,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2022]],"Not Found",0)</f>
-        <v>3761</v>
+        <v>355866</v>
       </c>
       <c r="C10" s="1" cm="1">
         <f t="array" ref="C10">_xlfn.XLOOKUP(A10,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2023]],"Not Found",0)</f>
-        <v>3944</v>
+        <v>387943</v>
       </c>
       <c r="D10" s="1" cm="1">
         <f t="array" ref="D10">_xlfn.XLOOKUP(A10,CL2024_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ millions)]],CL2024_Consolidated_Balance_Sheet[[#All],[2024]],"Not Found",0)</f>
-        <v>4522</v>
+        <v>437242</v>
       </c>
       <c r="E10" s="1" cm="1">
         <f t="array" ref="E10">_xlfn.XLOOKUP(A10,CL2025_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ Million)]],CL2025_Consolidated_Balance_Sheet[[#All],[2025]],"Not Found",0)</f>
-        <v>4679</v>
+        <v>481632</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>245</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1" cm="1">
-        <f t="array" ref="B11">_xlfn.XLOOKUP(A11,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2022]],"Not Found",0)</f>
-        <v>747</v>
+        <f t="array" ref="B11">_xlfn.XLOOKUP(A11,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</f>
+        <v>20004</v>
       </c>
       <c r="C11" s="1" cm="1">
-        <f t="array" ref="C11">_xlfn.XLOOKUP(A11,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2023]],"Not Found",0)</f>
-        <v>748</v>
+        <f t="array" ref="C11">_xlfn.XLOOKUP(A11,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</f>
+        <v>19813</v>
       </c>
       <c r="D11" s="1" cm="1">
-        <f t="array" ref="D11">_xlfn.XLOOKUP(A11,CL2024_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ millions)]],CL2024_Consolidated_Balance_Sheet[[#All],[2024]],"Not Found",0)</f>
-        <v>807</v>
+        <f t="array" ref="D11">_xlfn.XLOOKUP(A11,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</f>
+        <v>20909</v>
       </c>
       <c r="E11" s="1" cm="1">
-        <f t="array" ref="E11">_xlfn.XLOOKUP(A11,CL2025_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ Million)]],CL2025_Consolidated_Balance_Sheet[[#All],[2025]],"Not Found",0)</f>
-        <v>827</v>
+        <f t="array" ref="E11">_xlfn.XLOOKUP(A11,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</f>
+        <v>20938</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B12" s="1" cm="1">
+        <f t="array" ref="B12">_xlfn.XLOOKUP(A12,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2022]],"Not Found",0)</f>
+        <v>3761</v>
+      </c>
+      <c r="C12" s="1" cm="1">
+        <f t="array" ref="C12">_xlfn.XLOOKUP(A12,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2023]],"Not Found",0)</f>
+        <v>3944</v>
+      </c>
+      <c r="D12" s="1" cm="1">
+        <f t="array" ref="D12">_xlfn.XLOOKUP(A12,CL2024_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ millions)]],CL2024_Consolidated_Balance_Sheet[[#All],[2024]],"Not Found",0)</f>
+        <v>4522</v>
+      </c>
+      <c r="E12" s="1" cm="1">
+        <f t="array" ref="E12">_xlfn.XLOOKUP(A12,CL2025_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ Million)]],CL2025_Consolidated_Balance_Sheet[[#All],[2025]],"Not Found",0)</f>
+        <v>4679</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>245</v>
+      </c>
+      <c r="B13" s="1" cm="1">
+        <f t="array" ref="B13">_xlfn.XLOOKUP(A13,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2022]],"Not Found",0)</f>
+        <v>747</v>
+      </c>
+      <c r="C13" s="1" cm="1">
+        <f t="array" ref="C13">_xlfn.XLOOKUP(A13,CL2023_Consolidated_Balance_Sheets[[#All],[Consolidated Balance Sheets (in Canadian $ millions)]],CL2023_Consolidated_Balance_Sheets[[#All],[2023]],"Not Found",0)</f>
+        <v>748</v>
+      </c>
+      <c r="D13" s="1" cm="1">
+        <f t="array" ref="D13">_xlfn.XLOOKUP(A13,CL2024_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ millions)]],CL2024_Consolidated_Balance_Sheet[[#All],[2024]],"Not Found",0)</f>
+        <v>807</v>
+      </c>
+      <c r="E13" s="1" cm="1">
+        <f t="array" ref="E13">_xlfn.XLOOKUP(A13,CL2025_Consolidated_Balance_Sheet[[#All],[Consolidated Balance Sheet  (in Canadian $ Million)]],CL2025_Consolidated_Balance_Sheet[[#All],[2025]],"Not Found",0)</f>
+        <v>827</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>246</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B14" s="1">
         <f>'CL 2023 (Original)'!C137</f>
         <v>2343</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C14" s="1">
         <f>'CL 2023 (Original)'!B137</f>
         <v>3836</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D14" s="1">
         <f>'CL 2024 (Original)'!B132</f>
         <v>3347</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E14" s="1">
         <f>'CL 2025 (Original)'!B135</f>
         <v>3251</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="1" cm="1">
-        <f t="array" ref="B13">_xlfn.XLOOKUP(A13,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</f>
-        <v>12496</v>
-      </c>
-      <c r="C13" s="1" cm="1">
-        <f t="array" ref="C13">_xlfn.XLOOKUP(A13,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</f>
-        <v>12458</v>
-      </c>
-      <c r="D13" s="1" cm="1">
-        <f t="array" ref="D13">_xlfn.XLOOKUP(A13,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</f>
-        <v>13243</v>
-      </c>
-      <c r="E13" s="1" cm="1">
-        <f t="array" ref="E13">_xlfn.XLOOKUP(A13,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</f>
-        <v>13494</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1" cm="1">
-        <f t="array" ref="B14">_xlfn.XLOOKUP(A14,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</f>
-        <v>20004</v>
-      </c>
-      <c r="C14" s="1" cm="1">
-        <f t="array" ref="C14">_xlfn.XLOOKUP(A14,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</f>
-        <v>19813</v>
-      </c>
-      <c r="D14" s="1" cm="1">
-        <f t="array" ref="D14">_xlfn.XLOOKUP(A14,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</f>
-        <v>20909</v>
-      </c>
-      <c r="E14" s="1" cm="1">
-        <f t="array" ref="E14">_xlfn.XLOOKUP(A14,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</f>
-        <v>20938</v>
-      </c>
-    </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B15" s="1" cm="1">
         <f t="array" ref="B15">_xlfn.XLOOKUP(A15,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</f>
-        <v>22788</v>
+        <v>12496</v>
       </c>
       <c r="C15" s="1" cm="1">
         <f t="array" ref="C15">_xlfn.XLOOKUP(A15,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</f>
-        <v>22673</v>
+        <v>12458</v>
       </c>
       <c r="D15" s="1" cm="1">
         <f t="array" ref="D15">_xlfn.XLOOKUP(A15,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</f>
-        <v>23962</v>
+        <v>13243</v>
       </c>
       <c r="E15" s="1" cm="1">
         <f t="array" ref="E15">_xlfn.XLOOKUP(A15,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</f>
-        <v>24020</v>
+        <v>13494</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" cm="1">
-        <f t="array" ref="B16">_xlfn.XLOOKUP(A16,CL2023_Consolidated_Statements_Of_Cash_Flows[[#All],[Consolidated Statements of Cash Flows (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Cash_Flows[[#All],[2022]],"Not Found",0)</f>
-        <v>-1770</v>
+        <f t="array" ref="B16">_xlfn.XLOOKUP(A16,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</f>
+        <v>22788</v>
       </c>
       <c r="C16" s="1" cm="1">
-        <f t="array" ref="C16">_xlfn.XLOOKUP(A16,CL2023_Consolidated_Statements_Of_Cash_Flows[[#All],[Consolidated Statements of Cash Flows (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Cash_Flows[[#All],[2023]],"Not Found",0)</f>
-        <v>-2934</v>
+        <f t="array" ref="C16">_xlfn.XLOOKUP(A16,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</f>
+        <v>22673</v>
       </c>
       <c r="D16" s="1" cm="1">
-        <f t="array" ref="D16">_xlfn.XLOOKUP(A16,CL2024_Consolidated_Statements_Of_Cash_Flow[[#All],[Consolidated Statements of Cash Flow  (in Canadian $ millions)]],CL2024_Consolidated_Statements_Of_Cash_Flow[[#All],[2024]],"Not Found",0)</f>
-        <v>-2838</v>
+        <f t="array" ref="D16">_xlfn.XLOOKUP(A16,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</f>
+        <v>23962</v>
       </c>
       <c r="E16" s="1" cm="1">
-        <f t="array" ref="E16">_xlfn.XLOOKUP(A16,CL2025_Consolidated_Statements_Of_Cash_Flow[[#All],[Consolidated Statements of Cash Flow]],CL2025_Consolidated_Statements_Of_Cash_Flow[[#All],[2025]],"Not Found",0)</f>
-        <v>-3150</v>
+        <f t="array" ref="E16">_xlfn.XLOOKUP(A16,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</f>
+        <v>24020</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="1" cm="1">
+        <f t="array" ref="B17">_xlfn.XLOOKUP(A17,CL2023_Consolidated_Statements_Of_Cash_Flows[[#All],[Consolidated Statements of Cash Flows (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Cash_Flows[[#All],[2022]],"Not Found",0)</f>
+        <v>-1770</v>
+      </c>
+      <c r="C17" s="1" cm="1">
+        <f t="array" ref="C17">_xlfn.XLOOKUP(A17,CL2023_Consolidated_Statements_Of_Cash_Flows[[#All],[Consolidated Statements of Cash Flows (in Canadian $ millions)]],CL2023_Consolidated_Statements_Of_Cash_Flows[[#All],[2023]],"Not Found",0)</f>
+        <v>-2934</v>
+      </c>
+      <c r="D17" s="1" cm="1">
+        <f t="array" ref="D17">_xlfn.XLOOKUP(A17,CL2024_Consolidated_Statements_Of_Cash_Flow[[#All],[Consolidated Statements of Cash Flow  (in Canadian $ millions)]],CL2024_Consolidated_Statements_Of_Cash_Flow[[#All],[2024]],"Not Found",0)</f>
+        <v>-2838</v>
+      </c>
+      <c r="E17" s="1" cm="1">
+        <f t="array" ref="E17">_xlfn.XLOOKUP(A17,CL2025_Consolidated_Statements_Of_Cash_Flow[[#All],[Consolidated Statements of Cash Flow]],CL2025_Consolidated_Statements_Of_Cash_Flow[[#All],[2025]],"Not Found",0)</f>
+        <v>-3150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>204</v>
       </c>
-      <c r="B17" s="24" cm="1">
-        <f t="array" ref="B17">_xlfn.XLOOKUP(A17,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</f>
+      <c r="B18" s="20" cm="1">
+        <f t="array" ref="B18">_xlfn.XLOOKUP(A18,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</f>
         <v>1.2</v>
       </c>
-      <c r="C17" s="24" cm="1">
-        <f t="array" ref="C17">_xlfn.XLOOKUP(A17,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</f>
+      <c r="C18" s="20" cm="1">
+        <f t="array" ref="C18">_xlfn.XLOOKUP(A18,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</f>
         <v>1.28</v>
       </c>
-      <c r="D17" s="24" cm="1">
-        <f t="array" ref="D17">_xlfn.XLOOKUP(A17,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</f>
+      <c r="D18" s="20" cm="1">
+        <f t="array" ref="D18">_xlfn.XLOOKUP(A18,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</f>
         <v>1.3</v>
       </c>
-      <c r="E17" s="24" cm="1">
-        <f t="array" ref="E17">_xlfn.XLOOKUP(A17,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</f>
+      <c r="E18" s="20" cm="1">
+        <f t="array" ref="E18">_xlfn.XLOOKUP(A18,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</f>
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>248</v>
+      </c>
+      <c r="B21">
+        <v>2022</v>
+      </c>
+      <c r="C21">
+        <v>2023</v>
+      </c>
+      <c r="D21">
+        <v>2024</v>
+      </c>
+      <c r="E21">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>249</v>
+      </c>
+      <c r="B22" s="22">
+        <f>B8/B4</f>
+        <v>0.16917215815485998</v>
+      </c>
+      <c r="C22" s="22">
+        <f t="shared" ref="C22:E22" si="0">C8/C4</f>
+        <v>0.11977412324152963</v>
+      </c>
+      <c r="D22" s="22">
+        <f t="shared" si="0"/>
+        <v>0.1545675251106774</v>
+      </c>
+      <c r="E22" s="22">
+        <f t="shared" si="0"/>
+        <v>0.12498305544259183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>250</v>
+      </c>
+      <c r="B23" s="22">
+        <f>B8/((B9+416689)/2)</f>
+        <v>8.2631015800730002E-3</v>
+      </c>
+      <c r="C23" s="22">
+        <f>C8/AVERAGE(B9:C9)</f>
+        <v>6.127180812649664E-3</v>
+      </c>
+      <c r="D23" s="22">
+        <f t="shared" ref="D23:E23" si="1">D8/AVERAGE(C9:D9)</f>
+        <v>7.4487852997178316E-3</v>
+      </c>
+      <c r="E23" s="22">
+        <f t="shared" si="1"/>
+        <v>5.7216379688392067E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>251</v>
+      </c>
+      <c r="B24" s="22">
+        <f>B8/((B11+18719)/2)</f>
+        <v>0.16971825530046741</v>
+      </c>
+      <c r="C24" s="22">
+        <f>C8/((C11+19973)/2)</f>
+        <v>0.12155029407329211</v>
+      </c>
+      <c r="D24" s="22">
+        <f>D8/AVERAGE(C11:D11)</f>
+        <v>0.15947153872599579</v>
+      </c>
+      <c r="E24" s="22">
+        <f>E8/AVERAGE(D11:E11)</f>
+        <v>0.13219585633378736</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>252</v>
+      </c>
+      <c r="B25" s="22">
+        <f>B8/((B16+21730)/2)</f>
+        <v>0.14762567950042679</v>
+      </c>
+      <c r="C25" s="22">
+        <f>C8/((C16+22757)/2)</f>
+        <v>0.10644948272066916</v>
+      </c>
+      <c r="D25" s="22">
+        <f>D8/AVERAGE(C16:D16)</f>
+        <v>0.13925163503806154</v>
+      </c>
+      <c r="E25" s="22">
+        <f>E8/AVERAGE(D16:E16)</f>
+        <v>0.11529323496311117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>253</v>
+      </c>
+      <c r="B26" s="22">
+        <f>B6/B4</f>
+        <v>0.14240115321252059</v>
+      </c>
+      <c r="C26" s="22">
+        <f t="shared" ref="C26:E26" si="2">C6/C4</f>
+        <v>0.14870219932633247</v>
+      </c>
+      <c r="D26" s="22">
+        <f t="shared" si="2"/>
+        <v>0.15509116008949397</v>
+      </c>
+      <c r="E26" s="22">
+        <f t="shared" si="2"/>
+        <v>0.1558899281550766</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>254</v>
+      </c>
+      <c r="B27" s="22">
+        <f>ABS(B5)/B4</f>
+        <v>0.77790362438220761</v>
+      </c>
+      <c r="C27" s="22">
+        <f t="shared" ref="C27:E27" si="3">ABS(C5)/C4</f>
+        <v>0.77382603526847638</v>
+      </c>
+      <c r="D27" s="22">
+        <f t="shared" si="3"/>
+        <v>0.76950540296091774</v>
+      </c>
+      <c r="E27" s="22">
+        <f t="shared" si="3"/>
+        <v>0.76824364014278612</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>255</v>
+      </c>
+      <c r="B28" s="22">
+        <f>(B4-ABS(B5)-B6)/B4</f>
+        <v>7.9695222405271826E-2</v>
+      </c>
+      <c r="C28" s="22">
+        <f t="shared" ref="C28:E28" si="4">(C4-ABS(C5)-C6)/C4</f>
+        <v>7.7471765405191198E-2</v>
+      </c>
+      <c r="D28" s="22">
+        <f t="shared" si="4"/>
+        <v>7.5403436949588232E-2</v>
+      </c>
+      <c r="E28" s="22">
+        <f t="shared" si="4"/>
+        <v>7.5866431702137277E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>258</v>
+      </c>
+      <c r="B31" s="21"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="C8" calculatedColumn="1"/>
+  </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>

--- a/Canada Life Annual Report Project.xlsx
+++ b/Canada Life Annual Report Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GMU058\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB2540C-51E6-44C3-8B2B-0BDB7D047591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999C781F-FB6D-4E2D-B900-8B6419DA0901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="4" xr2:uid="{3CB541B1-AEC2-4997-AFCF-80587D906177}"/>
   </bookViews>
@@ -1198,6 +1198,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="B46" authorId="0" shapeId="0" xr:uid="{054EE631-1840-489F-875A-41F792B16BCE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Not reported. CSM was introduced under IFRS 17, adopted effective January 1, 2023.
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="A47" authorId="0" shapeId="0" xr:uid="{E004DCCA-492B-45D1-9BA3-5B72A68E0BE8}">
       <text>
         <r>
@@ -1232,6 +1246,33 @@
         </r>
       </text>
     </comment>
+    <comment ref="B47" authorId="0" shapeId="0" xr:uid="{44E15BE6-2331-4155-A08F-99F2DE8CCF28}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">The previous year LICAT is received from the CL 2022 (Original) raw data.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B75" authorId="0" shapeId="0" xr:uid="{CC4FFB47-73DE-486D-A77D-0E59D474863E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Not reported. CSM was introduced under IFRS 17, adopted effective January 1, 2023.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1259,7 +1300,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="307">
   <si>
     <t>Summary of net earnings attributable to:</t>
   </si>
@@ -2084,6 +2125,102 @@
   </si>
   <si>
     <t>LICAT year-over-year change</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>2023 vs 2022</t>
+  </si>
+  <si>
+    <t>2024 vs 2023</t>
+  </si>
+  <si>
+    <t>2025 vs 2024</t>
+  </si>
+  <si>
+    <t>Year-over-Year Financial Ratio Analysis, 2022–2025</t>
+  </si>
+  <si>
+    <t>Overall analysis</t>
+  </si>
+  <si>
+    <t>Volatile; profitability weakened in 2025</t>
+  </si>
+  <si>
+    <t>Lower asset profitability overall</t>
+  </si>
+  <si>
+    <t>Recovered in 2024, then weakened</t>
+  </si>
+  <si>
+    <t>Similar pattern to ROE</t>
+  </si>
+  <si>
+    <t>Improving, but growth nearly levelled off</t>
+  </si>
+  <si>
+    <t>Gradual improvement in insurance cost efficiency</t>
+  </si>
+  <si>
+    <t>Improved through 2024; slight deterioration in 2025</t>
+  </si>
+  <si>
+    <t>Consistently rising operating-cost burden</t>
+  </si>
+  <si>
+    <t>Rising burden, although increase slowed in 2025</t>
+  </si>
+  <si>
+    <t>Increasing reliance on liabilities</t>
+  </si>
+  <si>
+    <t>Declining equity cushion</t>
+  </si>
+  <si>
+    <t>Debt increased gradually relative to shareholders’ equity</t>
+  </si>
+  <si>
+    <t>Small but consistent increase</t>
+  </si>
+  <si>
+    <t>Leverage increased each year and accelerated in 2025</t>
+  </si>
+  <si>
+    <t>Stable near 1%, but lower in 2025</t>
+  </si>
+  <si>
+    <t>Cash coverage of debt improved, but improvement slowed</t>
+  </si>
+  <si>
+    <t>Strong 2023 increase followed by two years of decline</t>
+  </si>
+  <si>
+    <t>Volatile; improved in 2025 but below 2023</t>
+  </si>
+  <si>
+    <t>Cash generation relative to assets declined after 2023</t>
+  </si>
+  <si>
+    <t>Highly volatile; payout exceeded earnings in 2023 and 2025</t>
+  </si>
+  <si>
+    <t>Consistently weakening dividend cash coverage</t>
+  </si>
+  <si>
+    <t>Dividend distribution relative to equity rose overall</t>
+  </si>
+  <si>
+    <t>Volatile; lower overall by 2025</t>
+  </si>
+  <si>
+    <t>Steadily rising future-profit balance relative to equity</t>
+  </si>
+  <si>
+    <t>Positive growth continued, but slowed sharply in 2025</t>
+  </si>
+  <si>
+    <t>Capital ratio improvement reversed in 2025</t>
   </si>
 </sst>
 </file>
@@ -2143,10 +2280,12 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="24"/>
       <color theme="1"/>
-      <name val="Segoe UI"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2206,17 +2345,15 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFE6E6E6"/>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
       </left>
-      <right style="medium">
-        <color rgb="FFE6E6E6"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFE6E6E6"/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFE6E6E6"/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2225,7 +2362,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2263,16 +2400,123 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="75">
+  <dxfs count="83">
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     </dxf>
@@ -2546,9 +2790,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32C6B56A-ED7A-4BC5-86FB-BC86DC51FC56}" name="CL2025_Financial_Highlights" displayName="CL2025_Financial_Highlights" ref="A2:C21" totalsRowShown="0">
   <autoFilter ref="A2:C21" xr:uid="{32C6B56A-ED7A-4BC5-86FB-BC86DC51FC56}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{5C2C5EAF-8FD7-4548-B79E-158A94C36CEC}" name="Financial Highlights (Unaudited) (in Canadian $ Million)" dataDxfId="70"/>
-    <tableColumn id="4" xr3:uid="{F845F529-FD47-4771-A575-3ECAFBD90817}" name="2025" dataDxfId="69"/>
-    <tableColumn id="6" xr3:uid="{2D1DF53C-C68C-4325-9449-0D2B4F3F7A6D}" name="2024" dataDxfId="68"/>
+    <tableColumn id="1" xr3:uid="{5C2C5EAF-8FD7-4548-B79E-158A94C36CEC}" name="Financial Highlights (Unaudited) (in Canadian $ Million)" dataDxfId="78"/>
+    <tableColumn id="4" xr3:uid="{F845F529-FD47-4771-A575-3ECAFBD90817}" name="2025" dataDxfId="77"/>
+    <tableColumn id="6" xr3:uid="{2D1DF53C-C68C-4325-9449-0D2B4F3F7A6D}" name="2024" dataDxfId="76"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2558,8 +2802,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{872B3C60-F251-4571-AC34-BA109A0E39B4}" name="CL2024_Consolidated_Statements_Of_Cash_Flow" displayName="CL2024_Consolidated_Statements_Of_Cash_Flow" ref="A118:C147" totalsRowShown="0">
   <autoFilter ref="A118:C147" xr:uid="{872B3C60-F251-4571-AC34-BA109A0E39B4}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{03DD1A9C-855C-4E1B-BC85-F1DA52E562A1}" name="Consolidated Statements of Cash Flow  (in Canadian $ millions)" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{9F529541-D5F9-4E8A-9852-77076A9252D7}" name="2024" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{03DD1A9C-855C-4E1B-BC85-F1DA52E562A1}" name="Consolidated Statements of Cash Flow  (in Canadian $ millions)" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{9F529541-D5F9-4E8A-9852-77076A9252D7}" name="2024" dataDxfId="44"/>
     <tableColumn id="5" xr3:uid="{D60C0FDC-FC22-4E62-9467-CDCB0E581960}" name="2023"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2570,9 +2814,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{AECA25C1-C846-4A7B-A2BF-C9448B60FB0D}" name="CL2023_Financial_Highlights" displayName="CL2023_Financial_Highlights" ref="A2:C21" totalsRowShown="0">
   <autoFilter ref="A2:C21" xr:uid="{AECA25C1-C846-4A7B-A2BF-C9448B60FB0D}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2FBD130F-2F76-40A4-8A35-F73D197CF679}" name="Financial Highlights (unaudited) (in Canadian $ millions)" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{EB1CCD9F-222B-42FF-A665-B40808CDFA23}" name="2023" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{606BD4DE-1AB4-4377-AD4C-304EEE364AE0}" name="2022" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{2FBD130F-2F76-40A4-8A35-F73D197CF679}" name="Financial Highlights (unaudited) (in Canadian $ millions)" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{EB1CCD9F-222B-42FF-A665-B40808CDFA23}" name="2023" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{606BD4DE-1AB4-4377-AD4C-304EEE364AE0}" name="2022" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2582,9 +2826,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{403F03B7-0B2F-429E-9099-05D4B79628EE}" name="CL2023_Consolidated_Statements_Of_Earnings" displayName="CL2023_Consolidated_Statements_Of_Earnings" ref="A23:C54" totalsRowShown="0">
   <autoFilter ref="A23:C54" xr:uid="{403F03B7-0B2F-429E-9099-05D4B79628EE}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{348E9B7F-8015-4CEA-9CB7-F5A11E794924}" name="Consolidated Statements of Earnings (in Canadian $ millions)" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{9CB5D784-9668-43E2-912F-CCC0C5A46AFC}" name="2023" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{7DFA6E59-95B4-4F39-8D95-F85AC0C103B7}" name="2022" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{348E9B7F-8015-4CEA-9CB7-F5A11E794924}" name="Consolidated Statements of Earnings (in Canadian $ millions)" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{9CB5D784-9668-43E2-912F-CCC0C5A46AFC}" name="2023" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{7DFA6E59-95B4-4F39-8D95-F85AC0C103B7}" name="2022" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2594,10 +2838,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{C8294548-29F4-4247-8D91-46256870F255}" name="CL2023_Consolidated_Balance_Sheets" displayName="CL2023_Consolidated_Balance_Sheets" ref="A57:D105" totalsRowShown="0">
   <autoFilter ref="A57:D105" xr:uid="{C8294548-29F4-4247-8D91-46256870F255}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{A77F868F-A01A-4E28-831C-123758FFEE1B}" name="Consolidated Balance Sheets (in Canadian $ millions)" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{BF1169F7-EA41-4E34-B1BE-468D058EC001}" name="2023" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{0DED70B6-5DBC-4722-9AEA-0F35DB477359}" name="2022" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{391AF299-CDE1-44A4-94F3-25223ECFCF43}" name="2021" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{A77F868F-A01A-4E28-831C-123758FFEE1B}" name="Consolidated Balance Sheets (in Canadian $ millions)" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{BF1169F7-EA41-4E34-B1BE-468D058EC001}" name="2023" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{0DED70B6-5DBC-4722-9AEA-0F35DB477359}" name="2022" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{391AF299-CDE1-44A4-94F3-25223ECFCF43}" name="2021" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2607,15 +2851,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{010BDDA1-0210-42C8-BA1E-98C8F4E39148}" name="CL2023_Consolidated_Statements_Of_Changes_In_Equity" displayName="CL2023_Consolidated_Statements_Of_Changes_In_Equity" ref="A108:I119" totalsRowShown="0">
   <autoFilter ref="A108:I119" xr:uid="{010BDDA1-0210-42C8-BA1E-98C8F4E39148}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{12AD67BC-57B1-41C3-A7A2-ECD190ADFB8A}" name="Consolidated Statements of Changes in Equity (in Canadian $ millions)" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{D69CD2BD-7405-43A8-B2F6-D33B29AE7319}" name="Share capital" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{D7419A9F-70E7-4602-A940-77D76211462A}" name="Contributed surplus" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{6F1EC460-0E36-4BAA-BD61-804EA1A7B604}" name="Accumulated surplus" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{ECC52595-0035-4144-8E9B-C830D055A87F}" name="Accumulated other comprehensive income (loss)" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{DD90BFCF-0719-4732-B663-A0F6DDCBB014}" name="Total shareholders' equity" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{45A80F18-CA21-485E-9774-7188CBDBD23A}" name="Non-controlling interests" dataDxfId="19"/>
-    <tableColumn id="13" xr3:uid="{5EFFD87C-8A6F-4E32-BC35-2981FB121A78}" name="Participating account surplus" dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{E2F54086-E050-49D8-8244-5234819E6F63}" name="Total equity" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{12AD67BC-57B1-41C3-A7A2-ECD190ADFB8A}" name="Consolidated Statements of Changes in Equity (in Canadian $ millions)" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{D69CD2BD-7405-43A8-B2F6-D33B29AE7319}" name="Share capital" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{D7419A9F-70E7-4602-A940-77D76211462A}" name="Contributed surplus" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{6F1EC460-0E36-4BAA-BD61-804EA1A7B604}" name="Accumulated surplus" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{ECC52595-0035-4144-8E9B-C830D055A87F}" name="Accumulated other comprehensive income (loss)" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{DD90BFCF-0719-4732-B663-A0F6DDCBB014}" name="Total shareholders' equity" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{45A80F18-CA21-485E-9774-7188CBDBD23A}" name="Non-controlling interests" dataDxfId="27"/>
+    <tableColumn id="13" xr3:uid="{5EFFD87C-8A6F-4E32-BC35-2981FB121A78}" name="Participating account surplus" dataDxfId="26"/>
+    <tableColumn id="15" xr3:uid="{E2F54086-E050-49D8-8244-5234819E6F63}" name="Total equity" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2625,7 +2869,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{070ABDE2-BBC3-4908-AB0F-44D6EF66AED5}" name="CL2023_Consolidated_Statements_Of_Cash_Flows" displayName="CL2023_Consolidated_Statements_Of_Cash_Flows" ref="A122:C152" totalsRowShown="0">
   <autoFilter ref="A122:C152" xr:uid="{070ABDE2-BBC3-4908-AB0F-44D6EF66AED5}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{7B75C2BC-A013-41C7-861B-9EDA9E0AE1BA}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{7B75C2BC-A013-41C7-861B-9EDA9E0AE1BA}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="24"/>
     <tableColumn id="5" xr3:uid="{D08EF108-C608-416D-A0FA-78700D08B198}" name="2023"/>
     <tableColumn id="7" xr3:uid="{0A748248-90C6-42D4-A30D-90D2E6522606}" name="2022"/>
   </tableColumns>
@@ -2637,7 +2881,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{DA35DAB2-1EB1-4099-B43A-7BBB210BD1B2}" name="CL2022_Financial_Highlight" displayName="CL2022_Financial_Highlight" ref="A2:C26" totalsRowShown="0">
   <autoFilter ref="A2:C26" xr:uid="{DA35DAB2-1EB1-4099-B43A-7BBB210BD1B2}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{742648AB-0CC3-4711-89DE-BEA31617073E}" name="Financial Highlight (unaudited)  (in Canadian $ millions)" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{742648AB-0CC3-4711-89DE-BEA31617073E}" name="Financial Highlight (unaudited)  (in Canadian $ millions)" dataDxfId="23"/>
     <tableColumn id="4" xr3:uid="{8EFD586F-8504-433C-ACA7-A80E443245D8}" name="2022"/>
     <tableColumn id="6" xr3:uid="{F3762B59-FF64-4412-994B-4F79CC8C4273}" name="2021"/>
   </tableColumns>
@@ -2649,8 +2893,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{D352CFDF-76E1-4D3C-8C7B-7F57348B216F}" name="CL2022_Consolidated_Statements_Of_Earnings" displayName="CL2022_Consolidated_Statements_Of_Earnings" ref="A29:C63" totalsRowShown="0">
   <autoFilter ref="A29:C63" xr:uid="{D352CFDF-76E1-4D3C-8C7B-7F57348B216F}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E02CB553-D5D4-402A-8C54-8DE755972EFF}" name="Consolidated Statements of Earnings  (in Canadian $ millions)" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{63FC9382-AFA6-415E-82F8-8CF40DE991D2}" name="2022" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{E02CB553-D5D4-402A-8C54-8DE755972EFF}" name="Consolidated Statements of Earnings  (in Canadian $ millions)" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{63FC9382-AFA6-415E-82F8-8CF40DE991D2}" name="2022" dataDxfId="21"/>
     <tableColumn id="6" xr3:uid="{75F17EC1-69D4-4F5D-8315-089CA34D666C}" name="2021"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2661,7 +2905,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{BB04493A-D9FF-4D74-A5D0-111BD2A4656C}" name="CL2022_Consolidated_Balance_Sheets" displayName="CL2022_Consolidated_Balance_Sheets" ref="A66:C112" totalsRowShown="0">
   <autoFilter ref="A66:C112" xr:uid="{BB04493A-D9FF-4D74-A5D0-111BD2A4656C}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{893DB4C7-64EE-4ADA-8217-9192AD5B689E}" name="Consolidated Balance Sheets" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{893DB4C7-64EE-4ADA-8217-9192AD5B689E}" name="Consolidated Balance Sheets" dataDxfId="20"/>
     <tableColumn id="4" xr3:uid="{DFF048A5-755F-448B-87C0-4E919F682AF0}" name="2022"/>
     <tableColumn id="6" xr3:uid="{5DD01DB6-24AF-4D26-80A0-169FFD04A979}" name="2021"/>
   </tableColumns>
@@ -2673,15 +2917,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{215DB435-83EB-4E91-B08B-67EC402A3AFF}" name="CL2022_Consolidated_Statements_Of_Changes_In_Equity" displayName="CL2022_Consolidated_Statements_Of_Changes_In_Equity" ref="A115:I124" totalsRowShown="0">
   <autoFilter ref="A115:I124" xr:uid="{215DB435-83EB-4E91-B08B-67EC402A3AFF}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{09504AB0-770E-4D43-ACD1-DE5F040CED87}" name="Consolidated Statements of Changes in Equity" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{BFA1FFA7-6E3B-4F23-85D7-277A408FB401}" name="Share capital" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{701F6E9A-D8E6-4794-950B-B6C0DCDFFB6C}" name="Contributed surplus" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{C6BCA9CA-AA5E-4ECD-A8ED-3425059521DC}" name="Accumulated surplus" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{C387DAE6-44DC-4C88-B247-97FF4BBC177F}" name="Accumulated other comprehensive loss comprehensive loss" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{3D9F6865-2163-45E5-9E9F-FE1EFA6E0A4E}" name="Total shareholders’ equity" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{A62F3586-FEAD-4757-955C-167BA489C2DA}" name="Non-controlling interests" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{5EC6C0BE-4B74-4A04-B001-36C6B2FE1058}" name="Participating account surplus" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{63AE17E1-9D3F-402A-8E50-6A25D991559F}" name="Total equity" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{09504AB0-770E-4D43-ACD1-DE5F040CED87}" name="Consolidated Statements of Changes in Equity" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{BFA1FFA7-6E3B-4F23-85D7-277A408FB401}" name="Share capital" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{701F6E9A-D8E6-4794-950B-B6C0DCDFFB6C}" name="Contributed surplus" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{C6BCA9CA-AA5E-4ECD-A8ED-3425059521DC}" name="Accumulated surplus" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{C387DAE6-44DC-4C88-B247-97FF4BBC177F}" name="Accumulated other comprehensive loss comprehensive loss" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{3D9F6865-2163-45E5-9E9F-FE1EFA6E0A4E}" name="Total shareholders’ equity" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{A62F3586-FEAD-4757-955C-167BA489C2DA}" name="Non-controlling interests" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{5EC6C0BE-4B74-4A04-B001-36C6B2FE1058}" name="Participating account surplus" dataDxfId="12"/>
+    <tableColumn id="17" xr3:uid="{63AE17E1-9D3F-402A-8E50-6A25D991559F}" name="Total equity" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2691,9 +2935,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{34C03A14-B5FE-4A4C-A2DD-6F7C99CBB8B6}" name="CL2025_Consolidated_Statements_Of_Earnings" displayName="CL2025_Consolidated_Statements_Of_Earnings" ref="A24:C54" totalsRowShown="0">
   <autoFilter ref="A24:C54" xr:uid="{34C03A14-B5FE-4A4C-A2DD-6F7C99CBB8B6}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{AF140A9C-2544-462A-8D05-83FCA92FCC29}" name="Consolidated Statements Of Earnings (in Canadian $ Million)" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{16B7134F-532D-42E5-B2C1-83A349FA9ED6}" name="2025" dataDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{A04CC424-6000-4365-8CE5-358C2FA21877}" name="2024" dataDxfId="65"/>
+    <tableColumn id="1" xr3:uid="{AF140A9C-2544-462A-8D05-83FCA92FCC29}" name="Consolidated Statements Of Earnings (in Canadian $ Million)" dataDxfId="75"/>
+    <tableColumn id="3" xr3:uid="{16B7134F-532D-42E5-B2C1-83A349FA9ED6}" name="2025" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{A04CC424-6000-4365-8CE5-358C2FA21877}" name="2024" dataDxfId="73"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2703,9 +2947,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{395EA000-7795-40F0-80C9-309E26D34DB3}" name="CL2022_Consolidated_Statements_Of_Cash_Flows" displayName="CL2022_Consolidated_Statements_Of_Cash_Flows" ref="A127:C161" totalsRowShown="0">
   <autoFilter ref="A127:C161" xr:uid="{395EA000-7795-40F0-80C9-309E26D34DB3}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D9D5A221-D279-446F-84E7-045892C71C4C}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{0B41E5F3-DDED-491F-B3FE-F07FAA1FC2F1}" name="2022" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{597E5080-187F-4732-87DD-297275C991F1}" name="2021" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D9D5A221-D279-446F-84E7-045892C71C4C}" name="Consolidated Statements of Cash Flows (in Canadian $ millions)" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{0B41E5F3-DDED-491F-B3FE-F07FAA1FC2F1}" name="2022" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{597E5080-187F-4732-87DD-297275C991F1}" name="2021" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2716,18 +2960,45 @@
   <autoFilter ref="A3:E18" xr:uid="{62B2A73A-1EEC-46AC-91EE-7CD6FB19EA63}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C65EBD19-CB55-4FE0-9E64-CCC55F3C53D5}" name="Financial item (CAD $ millions)"/>
-    <tableColumn id="2" xr3:uid="{64F0E65D-5B27-41C2-9D64-A1370C90CAE6}" name="2022" dataDxfId="74">
+    <tableColumn id="2" xr3:uid="{64F0E65D-5B27-41C2-9D64-A1370C90CAE6}" name="2022" dataDxfId="82">
       <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A4,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2022]],"Not Found",0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5DB1D296-8814-4B6A-9833-E4A1CCA5D2FA}" name="2023" dataDxfId="73">
+    <tableColumn id="3" xr3:uid="{5DB1D296-8814-4B6A-9833-E4A1CCA5D2FA}" name="2023" dataDxfId="81">
       <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A4,CL2023_Financial_Highlights[[#All],[Financial Highlights (unaudited) (in Canadian $ millions)]],CL2023_Financial_Highlights[[#All],[2023]],"Not Found",0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{59F5E5CB-387A-45BC-B330-F894B4F6DE82}" name="2024" dataDxfId="72">
+    <tableColumn id="4" xr3:uid="{59F5E5CB-387A-45BC-B330-F894B4F6DE82}" name="2024" dataDxfId="80">
       <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A4,CL2024_Financial_Highlights[[#All],[Financial Highlights (in Canadian $ millions)]],CL2024_Financial_Highlights[[#All],[2024]],"Not Found",0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{553985D8-0F6B-4CAB-A4A1-B67873C194FD}" name="2025" dataDxfId="71">
+    <tableColumn id="5" xr3:uid="{553985D8-0F6B-4CAB-A4A1-B67873C194FD}" name="2025" dataDxfId="79">
       <calculatedColumnFormula array="1">_xlfn.XLOOKUP(A4,CL2025_Financial_Highlights[[#All],[Financial Highlights (Unaudited) (in Canadian $ Million)]],CL2025_Financial_Highlights[[#All],[2025]],"Not Found",0)</calculatedColumnFormula>
     </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5C57C70A-01BE-438F-8D7F-3AE081FD9F79}" name="Table7" displayName="Table7" ref="A21:E47" totalsRowShown="0" dataDxfId="3" dataCellStyle="Percent">
+  <autoFilter ref="A21:E47" xr:uid="{5C57C70A-01BE-438F-8D7F-3AE081FD9F79}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{A5CDB5B9-AA55-48F1-BBB2-B4F31C6B2002}" name="Financial ratio analysis"/>
+    <tableColumn id="2" xr3:uid="{9B707378-8E34-47AF-BB9A-3D689820CEF1}" name="2022" dataDxfId="7" dataCellStyle="Percent"/>
+    <tableColumn id="3" xr3:uid="{2E29553D-D312-4469-AD4D-0059041D417E}" name="2023" dataDxfId="6" dataCellStyle="Percent"/>
+    <tableColumn id="4" xr3:uid="{AA250AA3-4986-4332-A95F-290238E3A631}" name="2024" dataDxfId="5" dataCellStyle="Percent"/>
+    <tableColumn id="5" xr3:uid="{0D5C7698-38B0-4143-8BF5-03EF0E414E62}" name="2025" dataDxfId="4" dataCellStyle="Percent"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{E1F03AA7-AA19-4471-8938-F03EC3340909}" name="Table8" displayName="Table8" ref="A50:D76" totalsRowShown="0">
+  <autoFilter ref="A50:D76" xr:uid="{E1F03AA7-AA19-4471-8938-F03EC3340909}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{6A05C4AA-297B-4AF0-B69A-F8164C52B2D7}" name="Year-over-Year Financial Ratio Analysis, 2022–2025"/>
+    <tableColumn id="2" xr3:uid="{9D5DF401-665C-4DA9-BB4D-042458497723}" name="2023 vs 2022" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{289FEDB2-3B89-4EDB-A42C-C61D6AB6CADC}" name="2024 vs 2023" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{16D11D77-95B8-40DA-9EE7-33B737358C59}" name="2025 vs 2024" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2737,8 +3008,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FABD7B52-E650-435A-863F-F68E89A607E8}" name="CL2025_Consolidated_Balance_Sheet" displayName="CL2025_Consolidated_Balance_Sheet" ref="A58:C106" totalsRowShown="0">
   <autoFilter ref="A58:C106" xr:uid="{FABD7B52-E650-435A-863F-F68E89A607E8}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D6729C5B-6996-4AD6-921A-4FCB66DC5B45}" name="Consolidated Balance Sheet  (in Canadian $ Million)" dataDxfId="64"/>
-    <tableColumn id="3" xr3:uid="{1B220B5B-DEB0-4054-AD07-3C5B3F8AACD1}" name="2025" dataDxfId="63"/>
+    <tableColumn id="1" xr3:uid="{D6729C5B-6996-4AD6-921A-4FCB66DC5B45}" name="Consolidated Balance Sheet  (in Canadian $ Million)" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{1B220B5B-DEB0-4054-AD07-3C5B3F8AACD1}" name="2025" dataDxfId="71"/>
     <tableColumn id="5" xr3:uid="{E50E6906-CAA9-42F6-9EB9-A1F697BB2F20}" name="2024"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2749,15 +3020,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CF654234-2B8F-4830-BE0E-554991835BD9}" name="CL2025_Consolidated_Statements_Of_Change_In_Equity" displayName="CL2025_Consolidated_Statements_Of_Change_In_Equity" ref="A109:I117" totalsRowShown="0">
   <autoFilter ref="A109:I117" xr:uid="{CF654234-2B8F-4830-BE0E-554991835BD9}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C372BC7B-EDAA-425F-B029-CC348E8759F1}" name="Consolidated Statements of Change in Equity" dataDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{87A431C1-44DD-4CAE-8CF0-67ED9C3536FA}" name="Share Capital" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{1ACAEC2D-550E-4F1E-899C-D23FDA3C7A2F}" name="Contributed Surplus" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{DA9BD253-8ABA-4C4C-90D8-B886FCF7BB0C}" name="Accumulated Surplus" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{35415082-274B-4DFF-B6E0-53920A2A9F6D}" name="Accumulated Other Comprehensive Income" dataDxfId="58"/>
-    <tableColumn id="10" xr3:uid="{2F102C70-C964-49EB-A16F-A1842CC2B96F}" name="Total Shareholder's Equity" dataDxfId="57"/>
-    <tableColumn id="12" xr3:uid="{ECFC45BF-2FD7-4257-A71D-CD62160491EA}" name="Non-controlling Interest" dataDxfId="56"/>
-    <tableColumn id="14" xr3:uid="{E959836E-9965-4D14-BCC3-3BCC273F49C9}" name="Participating Account Surplus" dataDxfId="55"/>
-    <tableColumn id="16" xr3:uid="{C57C220A-153E-480B-8F20-BD9766EBCC5D}" name="Total Equity" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{C372BC7B-EDAA-425F-B029-CC348E8759F1}" name="Consolidated Statements of Change in Equity" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{87A431C1-44DD-4CAE-8CF0-67ED9C3536FA}" name="Share Capital" dataDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{1ACAEC2D-550E-4F1E-899C-D23FDA3C7A2F}" name="Contributed Surplus" dataDxfId="68"/>
+    <tableColumn id="6" xr3:uid="{DA9BD253-8ABA-4C4C-90D8-B886FCF7BB0C}" name="Accumulated Surplus" dataDxfId="67"/>
+    <tableColumn id="8" xr3:uid="{35415082-274B-4DFF-B6E0-53920A2A9F6D}" name="Accumulated Other Comprehensive Income" dataDxfId="66"/>
+    <tableColumn id="10" xr3:uid="{2F102C70-C964-49EB-A16F-A1842CC2B96F}" name="Total Shareholder's Equity" dataDxfId="65"/>
+    <tableColumn id="12" xr3:uid="{ECFC45BF-2FD7-4257-A71D-CD62160491EA}" name="Non-controlling Interest" dataDxfId="64"/>
+    <tableColumn id="14" xr3:uid="{E959836E-9965-4D14-BCC3-3BCC273F49C9}" name="Participating Account Surplus" dataDxfId="63"/>
+    <tableColumn id="16" xr3:uid="{C57C220A-153E-480B-8F20-BD9766EBCC5D}" name="Total Equity" dataDxfId="62"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2767,7 +3038,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3AAC487E-DBF0-4C56-AF4F-056F3601ED72}" name="CL2025_Consolidated_Statements_Of_Cash_Flow" displayName="CL2025_Consolidated_Statements_Of_Cash_Flow" ref="A121:C149" totalsRowShown="0">
   <autoFilter ref="A121:C149" xr:uid="{3AAC487E-DBF0-4C56-AF4F-056F3601ED72}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2F45C01F-02D6-4CB5-9364-F722A27B3859}" name="Consolidated Statements of Cash Flow" dataDxfId="53"/>
+    <tableColumn id="1" xr3:uid="{2F45C01F-02D6-4CB5-9364-F722A27B3859}" name="Consolidated Statements of Cash Flow" dataDxfId="61"/>
     <tableColumn id="3" xr3:uid="{712741C7-204F-4298-8050-873B208D5060}" name="2025"/>
     <tableColumn id="5" xr3:uid="{2534FEF1-3F52-460C-AB74-977F2325376E}" name="2024"/>
   </tableColumns>
@@ -2779,8 +3050,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{80062148-2C94-44FA-AA84-D3AF2950CAE1}" name="CL2024_Financial_Highlights" displayName="CL2024_Financial_Highlights" ref="A2:C21" totalsRowShown="0">
   <autoFilter ref="A2:C21" xr:uid="{80062148-2C94-44FA-AA84-D3AF2950CAE1}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A504AF7D-4077-4F75-AD8E-F00D66A4E1EB}" name="Financial Highlights (in Canadian $ millions)" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{6DE21333-8B6D-493E-A3FB-12219341B858}" name="2024" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{A504AF7D-4077-4F75-AD8E-F00D66A4E1EB}" name="Financial Highlights (in Canadian $ millions)" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{6DE21333-8B6D-493E-A3FB-12219341B858}" name="2024" dataDxfId="59"/>
     <tableColumn id="7" xr3:uid="{1D1F864D-619C-4D8B-BDCB-F9F994AD3F85}" name="2023"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2791,9 +3062,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{F2E5B2C2-C7D4-4C68-B8DF-B451C6AD2FA5}" name="CL2024_Consolidated_Statement_Of_Earnings" displayName="CL2024_Consolidated_Statement_Of_Earnings" ref="A24:C54" totalsRowShown="0">
   <autoFilter ref="A24:C54" xr:uid="{F2E5B2C2-C7D4-4C68-B8DF-B451C6AD2FA5}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B00DF7C4-46F0-426A-99DA-8CD1485C8167}" name="Consolidated Statements of Earnings (in Canadian $ millions)" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{6DBC8D88-3782-41F5-8C7F-4912F53C3845}" name="2024" dataDxfId="49"/>
-    <tableColumn id="5" xr3:uid="{0DA8B320-B9A4-43AB-B84E-C184D12EEBCE}" name="2023" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{B00DF7C4-46F0-426A-99DA-8CD1485C8167}" name="Consolidated Statements of Earnings (in Canadian $ millions)" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{6DBC8D88-3782-41F5-8C7F-4912F53C3845}" name="2024" dataDxfId="57"/>
+    <tableColumn id="5" xr3:uid="{0DA8B320-B9A4-43AB-B84E-C184D12EEBCE}" name="2023" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2803,7 +3074,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{09288B11-3956-44BF-B015-CDD67BF6122B}" name="CL2024_Consolidated_Balance_Sheet" displayName="CL2024_Consolidated_Balance_Sheet" ref="A57:C104" totalsRowShown="0">
   <autoFilter ref="A57:C104" xr:uid="{09288B11-3956-44BF-B015-CDD67BF6122B}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{9A2A315A-17C4-44C5-839B-27077EDAFBE8}" name="Consolidated Balance Sheet  (in Canadian $ millions)" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{9A2A315A-17C4-44C5-839B-27077EDAFBE8}" name="Consolidated Balance Sheet  (in Canadian $ millions)" dataDxfId="55"/>
     <tableColumn id="3" xr3:uid="{AC35110F-0BC5-4C19-B333-64D500DD652D}" name="2024"/>
     <tableColumn id="5" xr3:uid="{FC18CAD8-EF52-4B84-B287-4440BF8988D1}" name="2023"/>
   </tableColumns>
@@ -2815,15 +3086,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{95B36E1D-5C8B-415A-8BB2-72AC852DFE1F}" name="CL2024_Consolidated_Statements_Of_Changes_In_Equity" displayName="CL2024_Consolidated_Statements_Of_Changes_In_Equity" ref="A107:I115" totalsRowShown="0">
   <autoFilter ref="A107:I115" xr:uid="{95B36E1D-5C8B-415A-8BB2-72AC852DFE1F}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{346EBBBA-D3E8-43C4-B112-84CFBA884811}" name="Consolidated Statements of Changes in Equity  (in Canadian $ millions)" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{A3F2222E-550B-4C91-822F-4D93B86D0518}" name="Share capital" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{5DE7CF1E-A17D-4E32-B7FB-FD3FCA7A27C6}" name="Contributed surplus" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{7CD3F9B9-2C9F-423A-9B10-5566ED617B23}" name="Accumulated surplus" dataDxfId="43"/>
-    <tableColumn id="8" xr3:uid="{81A55F20-6E2D-49CB-A777-7EA2FA186E54}" name="Accumulated other comprehensive income (loss)" dataDxfId="42"/>
-    <tableColumn id="10" xr3:uid="{436743AE-2B63-4A1B-B86F-48A200522D06}" name="Total shareholder's equity" dataDxfId="41"/>
-    <tableColumn id="12" xr3:uid="{185E9850-C6B0-4386-B196-713B0971812A}" name="Non-controlling interests" dataDxfId="40"/>
-    <tableColumn id="14" xr3:uid="{F07A79B8-D988-4A89-BC52-58700AEF495C}" name="Participating account surplus" dataDxfId="39"/>
-    <tableColumn id="16" xr3:uid="{DAC2842E-0699-4DFF-A5A2-CA0460B0936F}" name="Total equity" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{346EBBBA-D3E8-43C4-B112-84CFBA884811}" name="Consolidated Statements of Changes in Equity  (in Canadian $ millions)" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{A3F2222E-550B-4C91-822F-4D93B86D0518}" name="Share capital" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{5DE7CF1E-A17D-4E32-B7FB-FD3FCA7A27C6}" name="Contributed surplus" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{7CD3F9B9-2C9F-423A-9B10-5566ED617B23}" name="Accumulated surplus" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{81A55F20-6E2D-49CB-A777-7EA2FA186E54}" name="Accumulated other comprehensive income (loss)" dataDxfId="50"/>
+    <tableColumn id="10" xr3:uid="{436743AE-2B63-4A1B-B86F-48A200522D06}" name="Total shareholder's equity" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{185E9850-C6B0-4386-B196-713B0971812A}" name="Non-controlling interests" dataDxfId="48"/>
+    <tableColumn id="14" xr3:uid="{F07A79B8-D988-4A89-BC52-58700AEF495C}" name="Participating account surplus" dataDxfId="47"/>
+    <tableColumn id="16" xr3:uid="{DAC2842E-0699-4DFF-A5A2-CA0460B0936F}" name="Total equity" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9851,18 +10122,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB2D2CB0-3C74-48F6-A0FC-1C79BE7E1C5C}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="47.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="13.36328125" customWidth="1"/>
     <col min="3" max="3" width="14.453125" customWidth="1"/>
     <col min="4" max="4" width="15.6328125" customWidth="1"/>
-    <col min="5" max="5" width="16.90625" customWidth="1"/>
+    <col min="5" max="5" width="48.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="31" x14ac:dyDescent="0.7">
+      <c r="A1" s="26" t="s">
         <v>247</v>
       </c>
     </row>
@@ -10202,36 +10473,36 @@
       <c r="A21" t="s">
         <v>248</v>
       </c>
-      <c r="B21">
-        <v>2022</v>
-      </c>
-      <c r="C21">
-        <v>2023</v>
-      </c>
-      <c r="D21">
-        <v>2024</v>
-      </c>
-      <c r="E21">
-        <v>2025</v>
+      <c r="B21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" t="s">
+        <v>183</v>
+      </c>
+      <c r="E21" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>249</v>
       </c>
-      <c r="B22" s="22">
+      <c r="B22" s="21">
         <f>B8/B4</f>
         <v>0.16917215815485998</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="21">
         <f t="shared" ref="C22:E22" si="0">C8/C4</f>
         <v>0.11977412324152963</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="21">
         <f t="shared" si="0"/>
         <v>0.1545675251106774</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="21">
         <f t="shared" si="0"/>
         <v>0.12498305544259183</v>
       </c>
@@ -10240,19 +10511,19 @@
       <c r="A23" t="s">
         <v>250</v>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="21">
         <f>B8/((B9+416689)/2)</f>
         <v>8.2631015800730002E-3</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="21">
         <f>C8/AVERAGE(B9:C9)</f>
         <v>6.127180812649664E-3</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="21">
         <f t="shared" ref="D23:E23" si="1">D8/AVERAGE(C9:D9)</f>
         <v>7.4487852997178316E-3</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="21">
         <f t="shared" si="1"/>
         <v>5.7216379688392067E-3</v>
       </c>
@@ -10261,19 +10532,19 @@
       <c r="A24" t="s">
         <v>251</v>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="21">
         <f>B8/((B11+18719)/2)</f>
         <v>0.16971825530046741</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="21">
         <f>C8/((C11+19973)/2)</f>
         <v>0.12155029407329211</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="21">
         <f>D8/AVERAGE(C11:D11)</f>
         <v>0.15947153872599579</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="21">
         <f>E8/AVERAGE(D11:E11)</f>
         <v>0.13219585633378736</v>
       </c>
@@ -10282,19 +10553,19 @@
       <c r="A25" t="s">
         <v>252</v>
       </c>
-      <c r="B25" s="22">
+      <c r="B25" s="21">
         <f>B8/((B16+21730)/2)</f>
         <v>0.14762567950042679</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="21">
         <f>C8/((C16+22757)/2)</f>
         <v>0.10644948272066916</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="21">
         <f>D8/AVERAGE(C16:D16)</f>
         <v>0.13925163503806154</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="21">
         <f>E8/AVERAGE(D16:E16)</f>
         <v>0.11529323496311117</v>
       </c>
@@ -10303,19 +10574,19 @@
       <c r="A26" t="s">
         <v>253</v>
       </c>
-      <c r="B26" s="22">
+      <c r="B26" s="21">
         <f>B6/B4</f>
         <v>0.14240115321252059</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="21">
         <f t="shared" ref="C26:E26" si="2">C6/C4</f>
         <v>0.14870219932633247</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="21">
         <f t="shared" si="2"/>
         <v>0.15509116008949397</v>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="21">
         <f t="shared" si="2"/>
         <v>0.1558899281550766</v>
       </c>
@@ -10324,19 +10595,19 @@
       <c r="A27" t="s">
         <v>254</v>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="21">
         <f>ABS(B5)/B4</f>
         <v>0.77790362438220761</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="21">
         <f t="shared" ref="C27:E27" si="3">ABS(C5)/C4</f>
         <v>0.77382603526847638</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="21">
         <f t="shared" si="3"/>
         <v>0.76950540296091774</v>
       </c>
-      <c r="E27" s="22">
+      <c r="E27" s="21">
         <f t="shared" si="3"/>
         <v>0.76824364014278612</v>
       </c>
@@ -10345,19 +10616,19 @@
       <c r="A28" t="s">
         <v>255</v>
       </c>
-      <c r="B28" s="22">
+      <c r="B28" s="21">
         <f>(B4-ABS(B5)-B6)/B4</f>
         <v>7.9695222405271826E-2</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="21">
         <f t="shared" ref="C28:E28" si="4">(C4-ABS(C5)-C6)/C4</f>
         <v>7.7471765405191198E-2</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="21">
         <f t="shared" si="4"/>
         <v>7.5403436949588232E-2</v>
       </c>
-      <c r="E28" s="22">
+      <c r="E28" s="21">
         <f t="shared" si="4"/>
         <v>7.5866431702137277E-2</v>
       </c>
@@ -10366,96 +10637,935 @@
       <c r="A29" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B29" s="21">
+        <f>ABS(B7)/B4</f>
+        <v>0.11434308072487644</v>
+      </c>
+      <c r="C29" s="21">
+        <f t="shared" ref="C29:E29" si="5">ABS(C7)/C4</f>
+        <v>0.13052308301961563</v>
+      </c>
+      <c r="D29" s="21">
+        <f t="shared" si="5"/>
+        <v>0.14699861950778312</v>
+      </c>
+      <c r="E29" s="21">
+        <f t="shared" si="5"/>
+        <v>0.1539921377253626</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="21">
+        <f>(ABS(B5)+ABS(B7))/B4</f>
+        <v>0.89224670510708404</v>
+      </c>
+      <c r="C30" s="21">
+        <f t="shared" ref="C30:E30" si="6">(ABS(C5)+ABS(C7))/C4</f>
+        <v>0.90434911828809195</v>
+      </c>
+      <c r="D30" s="21">
+        <f t="shared" si="6"/>
+        <v>0.91650402246870089</v>
+      </c>
+      <c r="E30" s="21">
+        <f t="shared" si="6"/>
+        <v>0.9222357778681487</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>258</v>
       </c>
-      <c r="B31" s="21"/>
+      <c r="B31" s="21">
+        <f>B10/B9</f>
+        <v>0.93981840941862493</v>
+      </c>
+      <c r="C31" s="21">
+        <f t="shared" ref="C31:E31" si="7">C10/C9</f>
+        <v>0.94478296023535369</v>
+      </c>
+      <c r="D31" s="21">
+        <f t="shared" si="7"/>
+        <v>0.94804468304698142</v>
+      </c>
+      <c r="E31" s="21">
+        <f t="shared" si="7"/>
+        <v>0.95249697420360246</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B32" s="21">
+        <f>B16/B9</f>
+        <v>6.018159058137508E-2</v>
+      </c>
+      <c r="C32" s="21">
+        <f t="shared" ref="C32:E32" si="8">C16/C9</f>
+        <v>5.5217039764646286E-2</v>
+      </c>
+      <c r="D32" s="21">
+        <f t="shared" si="8"/>
+        <v>5.1955316953018624E-2</v>
+      </c>
+      <c r="E32" s="21">
+        <f t="shared" si="8"/>
+        <v>4.7503025796397522E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B33" s="21">
+        <f>B13/B11</f>
+        <v>3.7342531493701259E-2</v>
+      </c>
+      <c r="C33" s="21">
+        <f t="shared" ref="C33:E33" si="9">C13/C11</f>
+        <v>3.7752990460808558E-2</v>
+      </c>
+      <c r="D33" s="21">
+        <f t="shared" si="9"/>
+        <v>3.8595819981826006E-2</v>
+      </c>
+      <c r="E33" s="21">
+        <f t="shared" si="9"/>
+        <v>3.9497564237271944E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B34" s="21">
+        <f>B13/B16</f>
+        <v>3.2780410742496054E-2</v>
+      </c>
+      <c r="C34" s="21">
+        <f t="shared" ref="C34:E34" si="10">C13/C16</f>
+        <v>3.2990781987385878E-2</v>
+      </c>
+      <c r="D34" s="21">
+        <f t="shared" si="10"/>
+        <v>3.3678324013020615E-2</v>
+      </c>
+      <c r="E34" s="21">
+        <f t="shared" si="10"/>
+        <v>3.4429641965029144E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B35" s="23">
+        <f>B9/B11</f>
+        <v>18.928914217156567</v>
+      </c>
+      <c r="C35" s="23">
+        <f t="shared" ref="C35:E35" si="11">C9/C11</f>
+        <v>20.72457477413819</v>
+      </c>
+      <c r="D35" s="23">
+        <f t="shared" si="11"/>
+        <v>22.057678511645701</v>
+      </c>
+      <c r="E35" s="23">
+        <f t="shared" si="11"/>
+        <v>24.149966567962554</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B36" s="21">
+        <f>B12/B9</f>
+        <v>9.9325505606701631E-3</v>
+      </c>
+      <c r="C36" s="21">
+        <f t="shared" ref="C36:E36" si="12">C12/C9</f>
+        <v>9.6050811463752016E-3</v>
+      </c>
+      <c r="D36" s="21">
+        <f t="shared" si="12"/>
+        <v>9.8047718580064353E-3</v>
+      </c>
+      <c r="E36" s="21">
+        <f t="shared" si="12"/>
+        <v>9.2533995712466288E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B37" s="24">
+        <f>B12/B13</f>
+        <v>5.0348058902275774</v>
+      </c>
+      <c r="C37" s="24">
+        <f t="shared" ref="C37:E37" si="13">C12/C13</f>
+        <v>5.2727272727272725</v>
+      </c>
+      <c r="D37" s="24">
+        <f t="shared" si="13"/>
+        <v>5.603469640644362</v>
+      </c>
+      <c r="E37" s="24">
+        <f t="shared" si="13"/>
+        <v>5.6577992744860941</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B38" s="21">
+        <f>B14/B4</f>
+        <v>0.12062397034596375</v>
+      </c>
+      <c r="C38" s="21">
+        <f t="shared" ref="C38:E38" si="14">C14/C4</f>
+        <v>0.19001386962552011</v>
+      </c>
+      <c r="D38" s="21">
+        <f t="shared" si="14"/>
+        <v>0.15932784309991907</v>
+      </c>
+      <c r="E38" s="21">
+        <f t="shared" si="14"/>
+        <v>0.14689801635714608</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B39" s="24">
+        <f>B14/B8</f>
+        <v>0.71302495435179547</v>
+      </c>
+      <c r="C39" s="24">
+        <f t="shared" ref="C39:E39" si="15">C14/C8</f>
+        <v>1.5864350703060381</v>
+      </c>
+      <c r="D39" s="24">
+        <f t="shared" si="15"/>
+        <v>1.0307976593778874</v>
+      </c>
+      <c r="E39" s="24">
+        <f t="shared" si="15"/>
+        <v>1.1753434562545191</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B40" s="21">
+        <f>B14/B9</f>
+        <v>6.1877069831561271E-3</v>
+      </c>
+      <c r="C40" s="21">
+        <f t="shared" ref="C40:E40" si="16">C14/C9</f>
+        <v>9.342061682934907E-3</v>
+      </c>
+      <c r="D40" s="21">
+        <f t="shared" si="16"/>
+        <v>7.2570923062245775E-3</v>
+      </c>
+      <c r="E40" s="21">
+        <f t="shared" si="16"/>
+        <v>6.4293229335590481E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B41" s="21">
+        <f>ABS(B17)/B8</f>
+        <v>0.53864881314668289</v>
+      </c>
+      <c r="C41" s="21">
+        <f t="shared" ref="C41:E41" si="17">ABS(C17)/C8</f>
+        <v>1.2133995037220844</v>
+      </c>
+      <c r="D41" s="21">
+        <f t="shared" si="17"/>
+        <v>0.87403757314444097</v>
+      </c>
+      <c r="E41" s="21">
+        <f t="shared" si="17"/>
+        <v>1.1388286334056399</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B42" s="24">
+        <f>B14/ABS(B17)</f>
+        <v>1.3237288135593219</v>
+      </c>
+      <c r="C42" s="24">
+        <f t="shared" ref="C42:E42" si="18">C14/ABS(C17)</f>
+        <v>1.3074301295160191</v>
+      </c>
+      <c r="D42" s="24">
+        <f t="shared" si="18"/>
+        <v>1.1793516560958421</v>
+      </c>
+      <c r="E42" s="24">
+        <f t="shared" si="18"/>
+        <v>1.0320634920634921</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B43" s="21">
+        <f>ABS(B17)/B16</f>
+        <v>7.7672459189046861E-2</v>
+      </c>
+      <c r="C43" s="21">
+        <f t="shared" ref="C43:E43" si="19">ABS(C17)/C16</f>
+        <v>0.12940501918581573</v>
+      </c>
+      <c r="D43" s="21">
+        <f t="shared" si="19"/>
+        <v>0.11843752608296469</v>
+      </c>
+      <c r="E43" s="21">
+        <f t="shared" si="19"/>
+        <v>0.13114071606994171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B44" s="21">
+        <f>B15/B4</f>
+        <v>0.64332784184514002</v>
+      </c>
+      <c r="C44" s="21">
+        <f t="shared" ref="C44:E44" si="20">C15/C4</f>
+        <v>0.61709926689122252</v>
+      </c>
+      <c r="D44" s="21">
+        <f t="shared" si="20"/>
+        <v>0.63040891131527588</v>
+      </c>
+      <c r="E44" s="21">
+        <f t="shared" si="20"/>
+        <v>0.60973295377524739</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B45" s="21">
+        <f>B15/B16</f>
+        <v>0.54835878532561</v>
+      </c>
+      <c r="C45" s="21">
+        <f t="shared" ref="C45:E45" si="21">C15/C16</f>
+        <v>0.54946412031932257</v>
+      </c>
+      <c r="D45" s="21">
+        <f t="shared" si="21"/>
+        <v>0.55266672231032465</v>
+      </c>
+      <c r="E45" s="21">
+        <f t="shared" si="21"/>
+        <v>0.56178184845961698</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B46" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="C46" s="21">
+        <f>(C15-B15)/B15</f>
+        <v>-3.0409731113956468E-3</v>
+      </c>
+      <c r="D46" s="21">
+        <f t="shared" ref="D46:E46" si="22">(D15-C15)/C15</f>
+        <v>6.3011719377107075E-2</v>
+      </c>
+      <c r="E46" s="21">
+        <f t="shared" si="22"/>
+        <v>1.8953409348334969E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>274</v>
+      </c>
+      <c r="B47" s="21">
+        <f>B18-'CL 2022 (Original)'!C26</f>
+        <v>-4.0000000000000036E-2</v>
+      </c>
+      <c r="C47" s="21">
+        <f>C18-B18</f>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="D47" s="21">
+        <f t="shared" ref="D47:E47" si="23">D18-C18</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="E47" s="21">
+        <f t="shared" si="23"/>
+        <v>-2.0000000000000018E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>279</v>
+      </c>
+      <c r="B50" t="s">
+        <v>276</v>
+      </c>
+      <c r="C50" t="s">
+        <v>277</v>
+      </c>
+      <c r="D50" t="s">
+        <v>278</v>
+      </c>
+      <c r="E50" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>249</v>
+      </c>
+      <c r="B51" s="19">
+        <f>C22-B22</f>
+        <v>-4.9398034913330349E-2</v>
+      </c>
+      <c r="C51" s="19">
+        <f t="shared" ref="C51:D51" si="24">D22-C22</f>
+        <v>3.4793401869147769E-2</v>
+      </c>
+      <c r="D51" s="19">
+        <f t="shared" si="24"/>
+        <v>-2.9584469668085561E-2</v>
+      </c>
+      <c r="E51" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>250</v>
+      </c>
+      <c r="B52" s="19">
+        <f>C23-B23</f>
+        <v>-2.1359207674233362E-3</v>
+      </c>
+      <c r="C52" s="19">
+        <f t="shared" ref="C52:D59" si="25">D23-C23</f>
+        <v>1.3216044870681676E-3</v>
+      </c>
+      <c r="D52" s="19">
+        <f t="shared" si="25"/>
+        <v>-1.7271473308786249E-3</v>
+      </c>
+      <c r="E52" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>251</v>
+      </c>
+      <c r="B53" s="19">
+        <f>C24-B24</f>
+        <v>-4.8167961227175302E-2</v>
+      </c>
+      <c r="C53" s="19">
+        <f t="shared" si="25"/>
+        <v>3.7921244652703676E-2</v>
+      </c>
+      <c r="D53" s="19">
+        <f t="shared" si="25"/>
+        <v>-2.7275682392208428E-2</v>
+      </c>
+      <c r="E53" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="B54" s="19">
+        <f>C25-B25</f>
+        <v>-4.1176196779757632E-2</v>
+      </c>
+      <c r="C54" s="19">
+        <f t="shared" si="25"/>
+        <v>3.2802152317392377E-2</v>
+      </c>
+      <c r="D54" s="19">
+        <f t="shared" si="25"/>
+        <v>-2.395840007495037E-2</v>
+      </c>
+      <c r="E54" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>253</v>
+      </c>
+      <c r="B55" s="19">
+        <f>C26-B26</f>
+        <v>6.3010461138118812E-3</v>
+      </c>
+      <c r="C55" s="19">
+        <f t="shared" si="25"/>
+        <v>6.3889607631615053E-3</v>
+      </c>
+      <c r="D55" s="19">
+        <f t="shared" si="25"/>
+        <v>7.9876806558262792E-4</v>
+      </c>
+      <c r="E55" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>254</v>
+      </c>
+      <c r="B56" s="19">
+        <f>C27-B27</f>
+        <v>-4.0775891137312392E-3</v>
+      </c>
+      <c r="C56" s="19">
+        <f t="shared" si="25"/>
+        <v>-4.3206323075586361E-3</v>
+      </c>
+      <c r="D56" s="19">
+        <f t="shared" si="25"/>
+        <v>-1.2617628181316176E-3</v>
+      </c>
+      <c r="E56" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>255</v>
+      </c>
+      <c r="B57" s="19">
+        <f>C28-B28</f>
+        <v>-2.2234570000806281E-3</v>
+      </c>
+      <c r="C57" s="19">
+        <f t="shared" si="25"/>
+        <v>-2.0683284556029663E-3</v>
+      </c>
+      <c r="D57" s="19">
+        <f t="shared" si="25"/>
+        <v>4.6299475254904521E-4</v>
+      </c>
+      <c r="E57" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>256</v>
+      </c>
+      <c r="B58" s="19">
+        <f>C29-B29</f>
+        <v>1.618000229473919E-2</v>
+      </c>
+      <c r="C58" s="19">
+        <f t="shared" si="25"/>
+        <v>1.6475536488167492E-2</v>
+      </c>
+      <c r="D58" s="19">
+        <f t="shared" si="25"/>
+        <v>6.9935182175794863E-3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>257</v>
+      </c>
+      <c r="B59" s="19">
+        <f>C30-B30</f>
+        <v>1.2102413181007909E-2</v>
+      </c>
+      <c r="C59" s="19">
+        <f t="shared" si="25"/>
+        <v>1.2154904180608939E-2</v>
+      </c>
+      <c r="D59" s="19">
+        <f t="shared" si="25"/>
+        <v>5.7317553994478132E-3</v>
+      </c>
+      <c r="E59" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>258</v>
+      </c>
+      <c r="B60" s="19">
+        <f t="shared" ref="B60:D60" si="26">C31-B31</f>
+        <v>4.9645508167287522E-3</v>
+      </c>
+      <c r="C60" s="19">
+        <f t="shared" si="26"/>
+        <v>3.2617228116277319E-3</v>
+      </c>
+      <c r="D60" s="19">
+        <f t="shared" si="26"/>
+        <v>4.4522911566210466E-3</v>
+      </c>
+      <c r="E60" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>259</v>
+      </c>
+      <c r="B61" s="19">
+        <f t="shared" ref="B61:D61" si="27">C32-B32</f>
+        <v>-4.9645508167287938E-3</v>
+      </c>
+      <c r="C61" s="19">
+        <f t="shared" si="27"/>
+        <v>-3.2617228116276625E-3</v>
+      </c>
+      <c r="D61" s="19">
+        <f t="shared" si="27"/>
+        <v>-4.4522911566211021E-3</v>
+      </c>
+      <c r="E61" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>260</v>
+      </c>
+      <c r="B62" s="19">
+        <f t="shared" ref="B62:D62" si="28">C33-B33</f>
+        <v>4.1045896710729946E-4</v>
+      </c>
+      <c r="C62" s="19">
+        <f t="shared" si="28"/>
+        <v>8.4282952101744774E-4</v>
+      </c>
+      <c r="D62" s="19">
+        <f t="shared" si="28"/>
+        <v>9.0174425544593817E-4</v>
+      </c>
+      <c r="E62" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>261</v>
+      </c>
+      <c r="B63" s="19">
+        <f t="shared" ref="B63:D63" si="29">C34-B34</f>
+        <v>2.1037124488982456E-4</v>
+      </c>
+      <c r="C63" s="19">
+        <f t="shared" si="29"/>
+        <v>6.8754202563473671E-4</v>
+      </c>
+      <c r="D63" s="19">
+        <f t="shared" si="29"/>
+        <v>7.5131795200852891E-4</v>
+      </c>
+      <c r="E63" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>262</v>
+      </c>
+      <c r="B64" s="24">
+        <f t="shared" ref="B64:D64" si="30">C35-B35</f>
+        <v>1.7956605569816233</v>
+      </c>
+      <c r="C64" s="24">
+        <f t="shared" si="30"/>
+        <v>1.3331037375075105</v>
+      </c>
+      <c r="D64" s="24">
+        <f t="shared" si="30"/>
+        <v>2.0922880563168533</v>
+      </c>
+      <c r="E64" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>263</v>
+      </c>
+      <c r="B65" s="19">
+        <f t="shared" ref="B65:D65" si="31">C36-B36</f>
+        <v>-3.2746941429496156E-4</v>
+      </c>
+      <c r="C65" s="19">
+        <f t="shared" si="31"/>
+        <v>1.9969071163123374E-4</v>
+      </c>
+      <c r="D65" s="19">
+        <f t="shared" si="31"/>
+        <v>-5.513722867598065E-4</v>
+      </c>
+      <c r="E65" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>264</v>
+      </c>
+      <c r="B66" s="24">
+        <f t="shared" ref="B66:D66" si="32">C37-B37</f>
+        <v>0.23792138249969508</v>
+      </c>
+      <c r="C66" s="24">
+        <f t="shared" si="32"/>
+        <v>0.33074236791708955</v>
+      </c>
+      <c r="D66" s="24">
+        <f t="shared" si="32"/>
+        <v>5.4329633841732061E-2</v>
+      </c>
+      <c r="E66" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>265</v>
+      </c>
+      <c r="B67" s="19">
+        <f t="shared" ref="B67:D67" si="33">C38-B38</f>
+        <v>6.9389899279556355E-2</v>
+      </c>
+      <c r="C67" s="19">
+        <f t="shared" si="33"/>
+        <v>-3.068602652560104E-2</v>
+      </c>
+      <c r="D67" s="19">
+        <f t="shared" si="33"/>
+        <v>-1.2429826742772987E-2</v>
+      </c>
+      <c r="E67" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>266</v>
+      </c>
+      <c r="B68" s="24">
+        <f t="shared" ref="B68:D68" si="34">C39-B39</f>
+        <v>0.87341011595424267</v>
+      </c>
+      <c r="C68" s="24">
+        <f t="shared" si="34"/>
+        <v>-0.55563741092815078</v>
+      </c>
+      <c r="D68" s="24">
+        <f t="shared" si="34"/>
+        <v>0.14454579687663172</v>
+      </c>
+      <c r="E68" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>267</v>
+      </c>
+      <c r="B69" s="19">
+        <f t="shared" ref="B69:D69" si="35">C40-B40</f>
+        <v>3.1543546997787799E-3</v>
+      </c>
+      <c r="C69" s="19">
+        <f t="shared" si="35"/>
+        <v>-2.0849693767103295E-3</v>
+      </c>
+      <c r="D69" s="19">
+        <f t="shared" si="35"/>
+        <v>-8.2776937266552941E-4</v>
+      </c>
+      <c r="E69" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>268</v>
+      </c>
+      <c r="B70" s="19">
+        <f t="shared" ref="B70:D70" si="36">C41-B41</f>
+        <v>0.67475069057540149</v>
+      </c>
+      <c r="C70" s="19">
+        <f t="shared" si="36"/>
+        <v>-0.33936193057764341</v>
+      </c>
+      <c r="D70" s="19">
+        <f t="shared" si="36"/>
+        <v>0.26479106026119892</v>
+      </c>
+      <c r="E70" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>269</v>
+      </c>
+      <c r="B71" s="24">
+        <f t="shared" ref="B71:D71" si="37">C42-B42</f>
+        <v>-1.6298684043302814E-2</v>
+      </c>
+      <c r="C71" s="24">
+        <f t="shared" si="37"/>
+        <v>-0.12807847342017697</v>
+      </c>
+      <c r="D71" s="24">
+        <f t="shared" si="37"/>
+        <v>-0.14728816403235001</v>
+      </c>
+      <c r="E71" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>270</v>
+      </c>
+      <c r="B72" s="19">
+        <f t="shared" ref="B72:D72" si="38">C43-B43</f>
+        <v>5.1732559996768873E-2</v>
+      </c>
+      <c r="C72" s="19">
+        <f t="shared" si="38"/>
+        <v>-1.0967493102851042E-2</v>
+      </c>
+      <c r="D72" s="19">
+        <f t="shared" si="38"/>
+        <v>1.2703189986977018E-2</v>
+      </c>
+      <c r="E72" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>271</v>
+      </c>
+      <c r="B73" s="19">
+        <f t="shared" ref="B73:D73" si="39">C44-B44</f>
+        <v>-2.6228574953917505E-2</v>
+      </c>
+      <c r="C73" s="19">
+        <f t="shared" si="39"/>
+        <v>1.3309644424053357E-2</v>
+      </c>
+      <c r="D73" s="19">
+        <f t="shared" si="39"/>
+        <v>-2.0675957540028489E-2</v>
+      </c>
+      <c r="E73" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>272</v>
+      </c>
+      <c r="B74" s="19">
+        <f t="shared" ref="B74:D74" si="40">C45-B45</f>
+        <v>1.10533499371257E-3</v>
+      </c>
+      <c r="C74" s="19">
+        <f t="shared" si="40"/>
+        <v>3.2026019910020853E-3</v>
+      </c>
+      <c r="D74" s="19">
+        <f t="shared" si="40"/>
+        <v>9.1151261492923297E-3</v>
+      </c>
+      <c r="E74" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>273</v>
+      </c>
+      <c r="B75" s="19" t="e">
+        <f t="shared" ref="B75:D75" si="41">C46-B46</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C75" s="19">
+        <f t="shared" si="41"/>
+        <v>6.6052692488502721E-2</v>
+      </c>
+      <c r="D75" s="19">
+        <f t="shared" si="41"/>
+        <v>-4.4058310028772106E-2</v>
+      </c>
+      <c r="E75" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>274</v>
+      </c>
+      <c r="B76" s="19">
+        <f>C47</f>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="C76" s="19">
+        <f>D47</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="D76" s="19">
+        <f>E47</f>
+        <v>-2.0000000000000018E-2</v>
+      </c>
+      <c r="E76" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -10464,8 +11574,10 @@
     <ignoredError sqref="C8" calculatedColumn="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
-  <tableParts count="1">
+  <tableParts count="3">
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
